--- a/MSFT.xlsx
+++ b/MSFT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5D2826-4AC8-45C2-85AE-5F06A19D459E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7561D949-E254-493F-91F3-15CBC9890A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18910" yWindow="6660" windowWidth="19170" windowHeight="13220" xr2:uid="{AF5D6250-CC2E-478D-A72E-6EAEA79B8F65}"/>
+    <workbookView xWindow="500" yWindow="1650" windowWidth="20990" windowHeight="18600" activeTab="1" xr2:uid="{AF5D6250-CC2E-478D-A72E-6EAEA79B8F65}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -124,6 +124,8 @@
     <author>tc={672EF133-CF99-4F62-BC53-D74F59EFAF45}</author>
     <author>tc={35883118-41B9-4E5B-B10B-13A3DA011BA4}</author>
     <author>tc={7F4F4845-E039-4FA5-97EA-E3560B883DA3}</author>
+    <author>tc={DDB58997-AB3C-43A9-A0DF-C556750A118E}</author>
+    <author>tc={1F4B5306-92C3-44C1-B004-9003A1E5AD5D}</author>
     <author>tc={5ABABD65-6006-454E-8377-B6AC9472B498}</author>
     <author>tc={667BC7EE-5E86-47FC-B964-2C031A25E303}</author>
     <author>tc={4CE52B0D-7FB3-47B3-B571-475342092488}</author>
@@ -133,6 +135,8 @@
     <author>tc={48518769-DF2C-4CE7-8344-8EDB6814ABC3}</author>
     <author>tc={EA740F5A-2BED-4510-A7C4-E95F65795F3A}</author>
     <author>tc={7F99F30D-CC1F-42AF-8158-A4F78646B952}</author>
+    <author>tc={687ABF38-51F2-40F9-9AE2-B6220F2B495E}</author>
+    <author>tc={BCA82E16-9ED6-4D55-B1DE-C3D01B114639}</author>
     <author>tc={0B1C80B2-A99F-49BC-9191-A0A5F60188E6}</author>
     <author>tc={885AFC63-6D78-4BB2-A861-4B904F8487BB}</author>
     <author>tc={5CB2A726-6A99-4883-BF78-BAC1241A440D}</author>
@@ -682,7 +686,23 @@
 Q1 guidance: 79.5-80.6B</t>
       </text>
     </comment>
-    <comment ref="BT33" authorId="64" shapeId="0" xr:uid="{5ABABD65-6006-454E-8377-B6AC9472B498}">
+    <comment ref="AH33" authorId="64" shapeId="0" xr:uid="{DDB58997-AB3C-43A9-A0DF-C556750A118E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    7/28/26 consensus: 87620</t>
+      </text>
+    </comment>
+    <comment ref="AI33" authorId="65" shapeId="0" xr:uid="{1F4B5306-92C3-44C1-B004-9003A1E5AD5D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    7/28/26 consensus: 89690</t>
+      </text>
+    </comment>
+    <comment ref="BT33" authorId="66" shapeId="0" xr:uid="{5ABABD65-6006-454E-8377-B6AC9472B498}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -690,7 +710,7 @@
     March 2022 - Nuance deal closes</t>
       </text>
     </comment>
-    <comment ref="W36" authorId="65" shapeId="0" xr:uid="{667BC7EE-5E86-47FC-B964-2C031A25E303}">
+    <comment ref="W36" authorId="67" shapeId="0" xr:uid="{667BC7EE-5E86-47FC-B964-2C031A25E303}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -698,7 +718,7 @@
     16.6-16.8B - Q423</t>
       </text>
     </comment>
-    <comment ref="BW38" authorId="66" shapeId="0" xr:uid="{4CE52B0D-7FB3-47B3-B571-475342092488}">
+    <comment ref="BW38" authorId="68" shapeId="0" xr:uid="{4CE52B0D-7FB3-47B3-B571-475342092488}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -706,7 +726,7 @@
     300m on quantum -- WSJ</t>
       </text>
     </comment>
-    <comment ref="AB41" authorId="67" shapeId="0" xr:uid="{E1D462E3-FE87-45D3-BF08-737DAD82C45D}">
+    <comment ref="AB41" authorId="69" shapeId="0" xr:uid="{E1D462E3-FE87-45D3-BF08-737DAD82C45D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -714,7 +734,7 @@
     Q1 guidance: 16.4-16.5B</t>
       </text>
     </comment>
-    <comment ref="BW42" authorId="68" shapeId="0" xr:uid="{7492A336-ABB9-4529-8350-AF762E5855FF}">
+    <comment ref="BW42" authorId="70" shapeId="0" xr:uid="{7492A336-ABB9-4529-8350-AF762E5855FF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -722,7 +742,7 @@
     Expect flat OM% y/y</t>
       </text>
     </comment>
-    <comment ref="AE43" authorId="69" shapeId="0" xr:uid="{4E294EC4-BE43-4E60-A4B5-9C95B46B99AF}">
+    <comment ref="AE43" authorId="71" shapeId="0" xr:uid="{4E294EC4-BE43-4E60-A4B5-9C95B46B99AF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -730,7 +750,7 @@
     Equity method losses in OpenAI</t>
       </text>
     </comment>
-    <comment ref="V47" authorId="70" shapeId="0" xr:uid="{48518769-DF2C-4CE7-8344-8EDB6814ABC3}">
+    <comment ref="V47" authorId="72" shapeId="0" xr:uid="{48518769-DF2C-4CE7-8344-8EDB6814ABC3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -738,7 +758,7 @@
     2.69 +23% cc</t>
       </text>
     </comment>
-    <comment ref="AE47" authorId="71" shapeId="0" xr:uid="{EA740F5A-2BED-4510-A7C4-E95F65795F3A}">
+    <comment ref="AE47" authorId="73" shapeId="0" xr:uid="{EA740F5A-2BED-4510-A7C4-E95F65795F3A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -746,7 +766,7 @@
     3.68 consensus 10/29</t>
       </text>
     </comment>
-    <comment ref="AF47" authorId="72" shapeId="0" xr:uid="{7F99F30D-CC1F-42AF-8158-A4F78646B952}">
+    <comment ref="AF47" authorId="74" shapeId="0" xr:uid="{7F99F30D-CC1F-42AF-8158-A4F78646B952}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -754,7 +774,23 @@
     3.83 consensus 10/29/25</t>
       </text>
     </comment>
-    <comment ref="BX47" authorId="73" shapeId="0" xr:uid="{0B1C80B2-A99F-49BC-9191-A0A5F60188E6}">
+    <comment ref="AH47" authorId="75" shapeId="0" xr:uid="{687ABF38-51F2-40F9-9AE2-B6220F2B495E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    7/28/26 consensus: 4.24</t>
+      </text>
+    </comment>
+    <comment ref="AI47" authorId="76" shapeId="0" xr:uid="{BCA82E16-9ED6-4D55-B1DE-C3D01B114639}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    7/28/26 consensus: 4.63</t>
+      </text>
+    </comment>
+    <comment ref="BX47" authorId="77" shapeId="0" xr:uid="{0B1C80B2-A99F-49BC-9191-A0A5F60188E6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -762,7 +798,7 @@
     13.39 7/7/25</t>
       </text>
     </comment>
-    <comment ref="BY47" authorId="74" shapeId="0" xr:uid="{885AFC63-6D78-4BB2-A861-4B904F8487BB}">
+    <comment ref="BY47" authorId="78" shapeId="0" xr:uid="{885AFC63-6D78-4BB2-A861-4B904F8487BB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -770,7 +806,7 @@
     15.16 consensus 7-7-25</t>
       </text>
     </comment>
-    <comment ref="BZ47" authorId="75" shapeId="0" xr:uid="{5CB2A726-6A99-4883-BF78-BAC1241A440D}">
+    <comment ref="BZ47" authorId="79" shapeId="0" xr:uid="{5CB2A726-6A99-4883-BF78-BAC1241A440D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -802,7 +838,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T51" authorId="76" shapeId="0" xr:uid="{207240C6-AA0E-47C1-A8DC-C70F3CF7F6CF}">
+    <comment ref="T51" authorId="80" shapeId="0" xr:uid="{207240C6-AA0E-47C1-A8DC-C70F3CF7F6CF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -810,7 +846,7 @@
     Bookings +4% y/y</t>
       </text>
     </comment>
-    <comment ref="V53" authorId="77" shapeId="0" xr:uid="{615EEB63-0CBB-48DD-AEFA-DCC9511390CB}">
+    <comment ref="V53" authorId="81" shapeId="0" xr:uid="{615EEB63-0CBB-48DD-AEFA-DCC9511390CB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -823,7 +859,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="488">
   <si>
     <t>Price</t>
   </si>
@@ -2238,9 +2274,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>365 Products &amp; Cloud</t>
-  </si>
-  <si>
     <t>365 Consumer &amp; Cloud</t>
   </si>
   <si>
@@ -2284,6 +2317,12 @@
   </si>
   <si>
     <t>Q126</t>
+  </si>
+  <si>
+    <t>Windows &amp; Devices</t>
+  </si>
+  <si>
+    <t>365 Commercial &amp; Cloud</t>
   </si>
 </sst>
 </file>
@@ -2532,16 +2571,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>34888</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>40409</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>5522</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>34888</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>40409</xdr:colOff>
       <xdr:row>121</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>34097</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2556,7 +2595,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23121279" y="0"/>
+          <a:off x="23811496" y="5522"/>
           <a:ext cx="0" cy="19603140"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -3147,6 +3186,12 @@
     <text>80222 consensus 10/29
 Q1 guidance: 79.5-80.6B</text>
   </threadedComment>
+  <threadedComment ref="AH33" dT="2026-07-28T17:00:34.84" personId="{2ADAC7E3-86EF-4E60-96A3-ED0BEE011F1E}" id="{DDB58997-AB3C-43A9-A0DF-C556750A118E}">
+    <text>7/28/26 consensus: 87620</text>
+  </threadedComment>
+  <threadedComment ref="AI33" dT="2026-07-28T17:00:56.96" personId="{2ADAC7E3-86EF-4E60-96A3-ED0BEE011F1E}" id="{1F4B5306-92C3-44C1-B004-9003A1E5AD5D}">
+    <text>7/28/26 consensus: 89690</text>
+  </threadedComment>
   <threadedComment ref="BT33" dT="2024-09-28T03:46:02.83" personId="{2ADAC7E3-86EF-4E60-96A3-ED0BEE011F1E}" id="{5ABABD65-6006-454E-8377-B6AC9472B498}">
     <text>March 2022 - Nuance deal closes</text>
   </threadedComment>
@@ -3173,6 +3218,12 @@
   </threadedComment>
   <threadedComment ref="AF47" dT="2025-10-29T16:47:34.37" personId="{2ADAC7E3-86EF-4E60-96A3-ED0BEE011F1E}" id="{7F99F30D-CC1F-42AF-8158-A4F78646B952}">
     <text>3.83 consensus 10/29/25</text>
+  </threadedComment>
+  <threadedComment ref="AH47" dT="2026-07-28T16:59:56.26" personId="{2ADAC7E3-86EF-4E60-96A3-ED0BEE011F1E}" id="{687ABF38-51F2-40F9-9AE2-B6220F2B495E}">
+    <text>7/28/26 consensus: 4.24</text>
+  </threadedComment>
+  <threadedComment ref="AI47" dT="2026-07-28T17:00:06.54" personId="{2ADAC7E3-86EF-4E60-96A3-ED0BEE011F1E}" id="{BCA82E16-9ED6-4D55-B1DE-C3D01B114639}">
+    <text>7/28/26 consensus: 4.63</text>
   </threadedComment>
   <threadedComment ref="BX47" dT="2025-07-07T14:16:09.59" personId="{2ADAC7E3-86EF-4E60-96A3-ED0BEE011F1E}" id="{0B1C80B2-A99F-49BC-9191-A0A5F60188E6}">
     <text>13.39 7/7/25</text>
@@ -3210,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>416</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="2:13">
@@ -3228,7 +3279,7 @@
         <v>7445</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="2:13">
@@ -3243,7 +3294,7 @@
       </c>
       <c r="L4" s="4">
         <f>L2*L3</f>
-        <v>3097120</v>
+        <v>2970555</v>
       </c>
     </row>
     <row r="5" spans="2:13">
@@ -3258,7 +3309,7 @@
         <v>111955</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="2:13">
@@ -3273,7 +3324,7 @@
         <v>40262</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" spans="2:13">
@@ -3282,7 +3333,7 @@
       </c>
       <c r="L7" s="4">
         <f>L4-L5+L6</f>
-        <v>3025427</v>
+        <v>2898862</v>
       </c>
     </row>
     <row r="8" spans="2:13">
@@ -3794,16 +3845,16 @@
     </row>
     <row r="3" spans="1:81">
       <c r="C3" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>81</v>
@@ -3878,28 +3929,28 @@
         <v>468</v>
       </c>
       <c r="AE3" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="AF3" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AG3" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AH3" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AI3" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AJ3" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AK3" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="AK3" s="2" t="s">
+      <c r="AL3" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="AN3" s="2"/>
       <c r="AO3" s="2" t="s">
@@ -4293,7 +4344,7 @@
     </row>
     <row r="7" spans="1:81" ht="13">
       <c r="B7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
@@ -4416,18 +4467,9 @@
       <c r="AE8" s="7">
         <v>49100</v>
       </c>
-      <c r="AF8" s="7">
-        <f>+AB8*1.2</f>
-        <v>49080</v>
-      </c>
-      <c r="AG8" s="7">
-        <f>+AC8*1.2</f>
-        <v>50880</v>
-      </c>
-      <c r="AH8" s="7">
-        <f>+AD8*1.2</f>
-        <v>56040</v>
-      </c>
+      <c r="AF8" s="7"/>
+      <c r="AG8" s="7"/>
+      <c r="AH8" s="7"/>
       <c r="AI8" s="7"/>
       <c r="AJ8" s="7"/>
       <c r="AK8" s="7"/>
@@ -4558,19 +4600,25 @@
         <v>23641</v>
       </c>
       <c r="AC9" s="5">
-        <f>+Y9*1.1</f>
-        <v>27315.200000000001</v>
+        <v>24761</v>
       </c>
       <c r="AD9" s="5">
-        <f t="shared" ref="AD9:AD19" si="3">+Z9*1.1</f>
-        <v>38758.5</v>
+        <f>98435-AC9-AB9-AA9</f>
+        <v>27878</v>
       </c>
       <c r="AE9" s="5">
         <v>28872</v>
       </c>
-      <c r="AF9" s="5"/>
-      <c r="AG9" s="5"/>
-      <c r="AH9" s="5"/>
+      <c r="AF9" s="5">
+        <v>30865</v>
+      </c>
+      <c r="AG9" s="5">
+        <v>32592</v>
+      </c>
+      <c r="AH9" s="5">
+        <f>129425-AG9-AF9-AE9</f>
+        <v>37096</v>
+      </c>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="5"/>
       <c r="AK9" s="5"/>
@@ -4616,7 +4664,7 @@
       </c>
       <c r="BX9" s="5">
         <f>SUM(AA9:AD9)</f>
-        <v>111869.7</v>
+        <v>98435</v>
       </c>
       <c r="BY9" s="20"/>
       <c r="BZ9" s="20"/>
@@ -4626,7 +4674,7 @@
     </row>
     <row r="10" spans="1:81" s="19" customFormat="1" ht="13">
       <c r="B10" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -4642,7 +4690,7 @@
         <v>8920</v>
       </c>
       <c r="J10" s="5">
-        <f t="shared" ref="J10:J19" si="4">+BS10-I10-H10-G10</f>
+        <f t="shared" ref="J10:J19" si="3">+BS10-I10-H10-G10</f>
         <v>8947</v>
       </c>
       <c r="K10" s="5">
@@ -4655,7 +4703,7 @@
         <v>10016</v>
       </c>
       <c r="N10" s="5">
-        <f t="shared" ref="N10:N19" si="5">+BT10-M10-L10-K10</f>
+        <f t="shared" ref="N10:N19" si="4">+BT10-M10-L10-K10</f>
         <v>10697</v>
       </c>
       <c r="O10" s="5">
@@ -4668,7 +4716,7 @@
         <v>11164</v>
       </c>
       <c r="R10" s="5">
-        <f t="shared" ref="R10:R19" si="6">+BU10-Q10-P10-O10</f>
+        <f t="shared" ref="R10:R19" si="5">+BU10-Q10-P10-O10</f>
         <v>11639</v>
       </c>
       <c r="S10" s="5">
@@ -4681,7 +4729,7 @@
         <v>12468</v>
       </c>
       <c r="V10" s="5">
-        <f t="shared" ref="V10:V19" si="7">+BV10-U10-T10-S10</f>
+        <f t="shared" ref="V10:V19" si="6">+BV10-U10-T10-S10</f>
         <v>12816</v>
       </c>
       <c r="W10" s="5">
@@ -4704,19 +4752,25 @@
         <v>21117</v>
       </c>
       <c r="AC10" s="5">
-        <f t="shared" ref="AC10:AC19" si="8">+Y10*1.1</f>
-        <v>15302.1</v>
+        <v>21883</v>
       </c>
       <c r="AD10" s="5">
-        <f t="shared" si="3"/>
-        <v>5058.9000000000005</v>
+        <f>87767-AC10-AB10-AA10</f>
+        <v>24318</v>
       </c>
       <c r="AE10" s="5">
         <v>23966</v>
       </c>
-      <c r="AF10" s="5"/>
-      <c r="AG10" s="5"/>
-      <c r="AH10" s="5"/>
+      <c r="AF10" s="5">
+        <v>24524</v>
+      </c>
+      <c r="AG10" s="5">
+        <v>25593</v>
+      </c>
+      <c r="AH10" s="5">
+        <f>101997-AG10-AF10-AE10</f>
+        <v>27914</v>
+      </c>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="5"/>
       <c r="AK10" s="5"/>
@@ -4761,8 +4815,8 @@
         <v>54875</v>
       </c>
       <c r="BX10" s="5">
-        <f t="shared" ref="BX10:BX19" si="9">SUM(AA10:AD10)</f>
-        <v>61927</v>
+        <f t="shared" ref="BX10:BX19" si="7">SUM(AA10:AD10)</f>
+        <v>87767</v>
       </c>
       <c r="BY10" s="20"/>
       <c r="BZ10" s="20"/>
@@ -4772,7 +4826,7 @@
     </row>
     <row r="11" spans="1:81" s="19" customFormat="1" ht="13">
       <c r="B11" t="s">
-        <v>110</v>
+        <v>486</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -4788,7 +4842,7 @@
         <v>5220</v>
       </c>
       <c r="J11" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>6128</v>
       </c>
       <c r="K11" s="5">
@@ -4801,7 +4855,7 @@
         <v>5463</v>
       </c>
       <c r="N11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6360</v>
       </c>
       <c r="O11" s="5">
@@ -4814,7 +4868,7 @@
         <v>6069</v>
       </c>
       <c r="R11" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6389</v>
       </c>
       <c r="S11" s="5">
@@ -4827,7 +4881,7 @@
         <v>5328</v>
       </c>
       <c r="V11" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>6058</v>
       </c>
       <c r="W11" s="5">
@@ -4850,19 +4904,25 @@
         <v>4512</v>
       </c>
       <c r="AC11" s="5">
-        <f t="shared" si="8"/>
-        <v>6521.9000000000005</v>
+        <v>4144</v>
       </c>
       <c r="AD11" s="5">
-        <f t="shared" si="3"/>
-        <v>9473.2000000000007</v>
+        <f>17314-AC11-AB11-AA11</f>
+        <v>4329</v>
       </c>
       <c r="AE11" s="5">
         <v>4551</v>
       </c>
-      <c r="AF11" s="5"/>
-      <c r="AG11" s="5"/>
-      <c r="AH11" s="5"/>
+      <c r="AF11" s="5">
+        <v>4479</v>
+      </c>
+      <c r="AG11" s="5">
+        <v>4041</v>
+      </c>
+      <c r="AH11" s="5">
+        <f>17084-AG11-AF11-AE11</f>
+        <v>4013</v>
+      </c>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="5"/>
       <c r="AK11" s="5"/>
@@ -4907,8 +4967,8 @@
         <v>23244</v>
       </c>
       <c r="BX11" s="5">
-        <f t="shared" si="9"/>
-        <v>24836.100000000002</v>
+        <f t="shared" si="7"/>
+        <v>17314</v>
       </c>
       <c r="BY11" s="20"/>
       <c r="BZ11" s="20"/>
@@ -4934,7 +4994,7 @@
         <v>2349</v>
       </c>
       <c r="J12" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3357</v>
       </c>
       <c r="K12" s="5">
@@ -4947,7 +5007,7 @@
         <v>3533</v>
       </c>
       <c r="N12" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3714</v>
       </c>
       <c r="O12" s="5">
@@ -4960,7 +5020,7 @@
         <v>3740</v>
       </c>
       <c r="R12" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3455</v>
       </c>
       <c r="S12" s="5">
@@ -4973,7 +5033,7 @@
         <v>3607</v>
       </c>
       <c r="V12" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3491</v>
       </c>
       <c r="W12" s="5">
@@ -4996,19 +5056,25 @@
         <v>6581</v>
       </c>
       <c r="AC12" s="5">
-        <f t="shared" si="8"/>
-        <v>5996.1</v>
+        <v>5721</v>
       </c>
       <c r="AD12" s="5">
-        <f t="shared" si="3"/>
-        <v>5524.2000000000007</v>
+        <f>23455-AC12-AB12-AA12</f>
+        <v>5532</v>
       </c>
       <c r="AE12" s="5">
         <v>5508</v>
       </c>
-      <c r="AF12" s="5"/>
-      <c r="AG12" s="5"/>
-      <c r="AH12" s="5"/>
+      <c r="AF12" s="5">
+        <v>5958</v>
+      </c>
+      <c r="AG12" s="5">
+        <v>5341</v>
+      </c>
+      <c r="AH12" s="5">
+        <f>21790-AG12-AF12-AE12</f>
+        <v>4983</v>
+      </c>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="5"/>
       <c r="AK12" s="5"/>
@@ -5053,8 +5119,8 @@
         <v>21503</v>
       </c>
       <c r="BX12" s="5">
-        <f t="shared" si="9"/>
-        <v>23722.3</v>
+        <f t="shared" si="7"/>
+        <v>23455</v>
       </c>
       <c r="BY12" s="20"/>
       <c r="BZ12" s="20"/>
@@ -5080,7 +5146,7 @@
         <v>2050</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2016</v>
       </c>
       <c r="K13" s="5">
@@ -5093,7 +5159,7 @@
         <v>2562</v>
       </c>
       <c r="N13" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2944</v>
       </c>
       <c r="O13" s="5">
@@ -5106,7 +5172,7 @@
         <v>3437</v>
       </c>
       <c r="R13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3712</v>
       </c>
       <c r="S13" s="5">
@@ -5119,7 +5185,7 @@
         <v>3659</v>
       </c>
       <c r="V13" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4025</v>
       </c>
       <c r="W13" s="5">
@@ -5142,19 +5208,25 @@
         <v>4587</v>
       </c>
       <c r="AC13" s="5">
-        <f t="shared" si="8"/>
-        <v>4414.3</v>
+        <v>4311</v>
       </c>
       <c r="AD13" s="5">
-        <f t="shared" si="3"/>
-        <v>4676.1000000000004</v>
+        <f>17812-AC13-AB13-AA13</f>
+        <v>4622</v>
       </c>
       <c r="AE13" s="5">
         <v>4714</v>
       </c>
-      <c r="AF13" s="5"/>
-      <c r="AG13" s="5"/>
-      <c r="AH13" s="5"/>
+      <c r="AF13" s="5">
+        <v>5082</v>
+      </c>
+      <c r="AG13" s="5">
+        <v>4832</v>
+      </c>
+      <c r="AH13" s="5">
+        <f>19817-AG13-AF13-AE13</f>
+        <v>5189</v>
+      </c>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="5"/>
       <c r="AK13" s="5"/>
@@ -5199,8 +5271,8 @@
         <v>16372</v>
       </c>
       <c r="BX13" s="5">
-        <f t="shared" si="9"/>
-        <v>17969.400000000001</v>
+        <f t="shared" si="7"/>
+        <v>17812</v>
       </c>
       <c r="BY13" s="20"/>
       <c r="BZ13" s="20"/>
@@ -5226,7 +5298,7 @@
         <v>1986</v>
       </c>
       <c r="J14" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1600</v>
       </c>
       <c r="K14" s="5">
@@ -5239,7 +5311,7 @@
         <v>2401</v>
       </c>
       <c r="N14" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2537</v>
       </c>
       <c r="O14" s="5">
@@ -5252,7 +5324,7 @@
         <v>2945</v>
       </c>
       <c r="R14" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2926</v>
       </c>
       <c r="S14" s="5">
@@ -5265,7 +5337,7 @@
         <v>3036</v>
       </c>
       <c r="V14" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3050</v>
       </c>
       <c r="W14" s="5">
@@ -5288,19 +5360,25 @@
         <v>3558</v>
       </c>
       <c r="AC14" s="5">
-        <f t="shared" si="8"/>
-        <v>3447.4</v>
+        <v>3504</v>
       </c>
       <c r="AD14" s="5">
-        <f t="shared" si="3"/>
-        <v>3581.6000000000004</v>
+        <f>13878-AC14-AB14-AA14</f>
+        <v>3591</v>
       </c>
       <c r="AE14" s="5">
         <v>3697</v>
       </c>
-      <c r="AF14" s="5"/>
-      <c r="AG14" s="5"/>
-      <c r="AH14" s="5"/>
+      <c r="AF14" s="5">
+        <v>3812</v>
+      </c>
+      <c r="AG14" s="5">
+        <v>3808</v>
+      </c>
+      <c r="AH14" s="5">
+        <f>15176-AG14-AF14-AE14</f>
+        <v>3859</v>
+      </c>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="5"/>
       <c r="AK14" s="5"/>
@@ -5341,8 +5419,8 @@
         <v>12576</v>
       </c>
       <c r="BX14" s="5">
-        <f t="shared" si="9"/>
-        <v>13812</v>
+        <f t="shared" si="7"/>
+        <v>13878</v>
       </c>
       <c r="BY14" s="20"/>
       <c r="BZ14" s="20"/>
@@ -5368,7 +5446,7 @@
         <v>1633</v>
       </c>
       <c r="J15" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1619</v>
       </c>
       <c r="K15" s="5">
@@ -5381,7 +5459,7 @@
         <v>1803</v>
       </c>
       <c r="N15" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1808</v>
       </c>
       <c r="O15" s="5">
@@ -5394,7 +5472,7 @@
         <v>1891</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1902</v>
       </c>
       <c r="S15" s="5">
@@ -5407,7 +5485,7 @@
         <v>2047</v>
       </c>
       <c r="V15" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1839</v>
       </c>
       <c r="W15" s="5">
@@ -5430,19 +5508,25 @@
         <v>1892</v>
       </c>
       <c r="AC15" s="5">
-        <f t="shared" si="8"/>
-        <v>2047.1000000000001</v>
+        <v>1946</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" si="3"/>
-        <v>2059.2000000000003</v>
+        <f>7760-AC15-AB15-AA15</f>
+        <v>1994</v>
       </c>
       <c r="AE15" s="5">
         <v>2022</v>
       </c>
-      <c r="AF15" s="5"/>
-      <c r="AG15" s="5"/>
-      <c r="AH15" s="5"/>
+      <c r="AF15" s="5">
+        <v>2038</v>
+      </c>
+      <c r="AG15" s="5">
+        <v>2087</v>
+      </c>
+      <c r="AH15" s="5">
+        <f>8260-AG15-AF15-AE15</f>
+        <v>2113</v>
+      </c>
       <c r="AI15" s="5"/>
       <c r="AJ15" s="5"/>
       <c r="AK15" s="5"/>
@@ -5481,8 +5565,8 @@
         <v>7594</v>
       </c>
       <c r="BX15" s="5">
-        <f t="shared" si="9"/>
-        <v>7926.3000000000011</v>
+        <f t="shared" si="7"/>
+        <v>7760</v>
       </c>
       <c r="BY15" s="20"/>
       <c r="BZ15" s="20"/>
@@ -5508,7 +5592,7 @@
         <v>961</v>
       </c>
       <c r="J16" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>993</v>
       </c>
       <c r="K16" s="5">
@@ -5521,7 +5605,7 @@
         <v>1125</v>
       </c>
       <c r="N16" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3843</v>
       </c>
       <c r="O16" s="5">
@@ -5534,7 +5618,7 @@
         <v>1233</v>
       </c>
       <c r="R16" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3541</v>
       </c>
       <c r="S16" s="5">
@@ -5547,7 +5631,7 @@
         <v>1389</v>
       </c>
       <c r="V16" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1570</v>
       </c>
       <c r="W16" s="5">
@@ -5570,19 +5654,25 @@
         <v>1913</v>
       </c>
       <c r="AC16" s="5">
-        <f t="shared" si="8"/>
-        <v>1810.6000000000001</v>
+        <v>1929</v>
       </c>
       <c r="AD16" s="5">
-        <f t="shared" si="3"/>
-        <v>1705.0000000000002</v>
+        <f>7827-AC16-AB16-AA16</f>
+        <v>2136</v>
       </c>
       <c r="AE16" s="5">
         <v>2136</v>
       </c>
-      <c r="AF16" s="5"/>
-      <c r="AG16" s="5"/>
-      <c r="AH16" s="5"/>
+      <c r="AF16" s="5">
+        <v>2204</v>
+      </c>
+      <c r="AG16" s="5">
+        <v>2292</v>
+      </c>
+      <c r="AH16" s="5">
+        <f>9006-AG16-AF16-AE16</f>
+        <v>2374</v>
+      </c>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="5"/>
       <c r="AK16" s="5"/>
@@ -5615,8 +5705,8 @@
         <v>6481</v>
       </c>
       <c r="BX16" s="5">
-        <f t="shared" si="9"/>
-        <v>7277.6</v>
+        <f t="shared" si="7"/>
+        <v>7827</v>
       </c>
       <c r="BY16" s="20"/>
       <c r="BZ16" s="20"/>
@@ -5642,7 +5732,7 @@
         <v>1412</v>
       </c>
       <c r="J17" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1795</v>
       </c>
       <c r="K17" s="5">
@@ -5655,7 +5745,7 @@
         <v>1599</v>
       </c>
       <c r="N17" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-1585</v>
       </c>
       <c r="O17" s="5">
@@ -5681,7 +5771,7 @@
         <v>1282</v>
       </c>
       <c r="V17" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1277</v>
       </c>
       <c r="W17" s="5" t="s">
@@ -5701,14 +5791,8 @@
         <v>470</v>
       </c>
       <c r="AB17" s="20"/>
-      <c r="AC17" s="5">
-        <f t="shared" si="8"/>
-        <v>1173.7</v>
-      </c>
-      <c r="AD17" s="5">
-        <f t="shared" si="3"/>
-        <v>2575.1000000000004</v>
-      </c>
+      <c r="AC17" s="5"/>
+      <c r="AD17" s="5"/>
       <c r="AE17" s="5"/>
       <c r="AF17" s="5"/>
       <c r="AG17" s="5"/>
@@ -5757,8 +5841,8 @@
         <v>4706</v>
       </c>
       <c r="BX17" s="5">
-        <f t="shared" si="9"/>
-        <v>3748.8</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="BY17" s="20"/>
       <c r="BZ17" s="20"/>
@@ -5768,7 +5852,7 @@
     </row>
     <row r="18" spans="2:81" s="19" customFormat="1" ht="13">
       <c r="B18" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -5805,19 +5889,25 @@
         <v>1821</v>
       </c>
       <c r="AC18" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1821</v>
       </c>
       <c r="AD18" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>7404-AC18-AB18-AA18</f>
+        <v>2035</v>
       </c>
       <c r="AE18" s="5">
         <v>2204</v>
       </c>
-      <c r="AF18" s="5"/>
-      <c r="AG18" s="5"/>
-      <c r="AH18" s="5"/>
+      <c r="AF18" s="5">
+        <v>2305</v>
+      </c>
+      <c r="AG18" s="5">
+        <v>2297</v>
+      </c>
+      <c r="AH18" s="5">
+        <f>9175-AG18-AF18-AE18</f>
+        <v>2369</v>
+      </c>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="5"/>
       <c r="AK18" s="5"/>
@@ -5838,8 +5928,8 @@
       <c r="BV18" s="5"/>
       <c r="BW18" s="20"/>
       <c r="BX18" s="5">
-        <f t="shared" si="9"/>
-        <v>3548</v>
+        <f t="shared" si="7"/>
+        <v>7404</v>
       </c>
       <c r="BY18" s="20"/>
       <c r="BZ18" s="20"/>
@@ -5865,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K19" s="5">
@@ -5878,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>373</v>
       </c>
       <c r="O19" s="5">
@@ -5891,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="R19" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>289</v>
       </c>
       <c r="S19" s="5">
@@ -5904,7 +5994,7 @@
         <v>16</v>
       </c>
       <c r="V19" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="W19" s="5">
@@ -5927,19 +6017,25 @@
         <v>10</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" si="8"/>
-        <v>15.400000000000002</v>
+        <v>46</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="3"/>
-        <v>14.3</v>
+        <f>72-AC19-AB19-AA19</f>
+        <v>6</v>
       </c>
       <c r="AE19" s="5">
         <v>3</v>
       </c>
-      <c r="AF19" s="5"/>
-      <c r="AG19" s="5"/>
-      <c r="AH19" s="5"/>
+      <c r="AF19" s="5">
+        <v>6</v>
+      </c>
+      <c r="AG19" s="5">
+        <v>3</v>
+      </c>
+      <c r="AH19" s="5">
+        <f>109-AG19-AF19-AE19</f>
+        <v>97</v>
+      </c>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="5"/>
       <c r="AK19" s="5"/>
@@ -5972,8 +6068,8 @@
         <v>45</v>
       </c>
       <c r="BX19" s="5">
-        <f t="shared" si="9"/>
-        <v>49.7</v>
+        <f t="shared" si="7"/>
+        <v>72</v>
       </c>
       <c r="BY19" s="20"/>
       <c r="BZ19" s="20"/>
@@ -6063,43 +6159,43 @@
       <c r="R21" s="21"/>
       <c r="S21" s="21"/>
       <c r="T21" s="21">
-        <f t="shared" ref="T21:AC21" si="10">T8/P8-1</f>
+        <f t="shared" ref="T21:AC21" si="8">T8/P8-1</f>
         <v>0.2262443438914028</v>
       </c>
       <c r="U21" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.21794871794871784</v>
       </c>
       <c r="V21" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.20717131474103589</v>
       </c>
       <c r="W21" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.23735408560311289</v>
       </c>
       <c r="X21" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.24354243542435428</v>
       </c>
       <c r="Y21" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.23157894736842111</v>
       </c>
       <c r="Z21" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.21452145214521456</v>
       </c>
       <c r="AA21" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.22327044025157239</v>
       </c>
       <c r="AB21" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.21364985163204753</v>
       </c>
       <c r="AC21" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.20797720797720798</v>
       </c>
       <c r="AD21" s="21">
@@ -6110,9 +6206,18 @@
         <f>AE8/AA8-1</f>
         <v>0.26221079691516702</v>
       </c>
-      <c r="AF21" s="20"/>
-      <c r="AG21" s="20"/>
-      <c r="AH21" s="20"/>
+      <c r="AF21" s="21">
+        <f>AF8/AB8-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AG21" s="21">
+        <f>AG8/AC8-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AH21" s="21">
+        <f>AH8/AD8-1</f>
+        <v>-1</v>
+      </c>
       <c r="AI21" s="20"/>
       <c r="AJ21" s="20"/>
       <c r="AK21" s="20"/>
@@ -6125,31 +6230,31 @@
       <c r="BN21" s="38"/>
       <c r="BO21" s="38"/>
       <c r="BP21" s="21">
-        <f t="shared" ref="BP21:BV21" si="11">BP8/BO8-1</f>
+        <f t="shared" ref="BP21:BV21" si="9">BP8/BO8-1</f>
         <v>0.70526315789473681</v>
       </c>
       <c r="BQ21" s="21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0.64197530864197527</v>
       </c>
       <c r="BR21" s="21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0.43233082706766912</v>
       </c>
       <c r="BS21" s="21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0.35695538057742793</v>
       </c>
       <c r="BT21" s="21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0.33655705996131524</v>
       </c>
       <c r="BU21" s="21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0.32127351664254711</v>
       </c>
       <c r="BV21" s="21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0.22234392113910184</v>
       </c>
       <c r="BW21" s="21">
@@ -6429,7 +6534,13 @@
         <v>33020</v>
       </c>
       <c r="AF27" s="4">
-        <v>33450</v>
+        <v>34116</v>
+      </c>
+      <c r="AG27" s="4">
+        <v>35013</v>
+      </c>
+      <c r="AH27" s="4">
+        <v>37847</v>
       </c>
       <c r="AQ27" s="4">
         <v>1401</v>
@@ -6546,7 +6657,13 @@
         <v>30897</v>
       </c>
       <c r="AF28" s="4">
-        <v>32400</v>
+        <v>32907</v>
+      </c>
+      <c r="AG28" s="4">
+        <v>34681</v>
+      </c>
+      <c r="AH28" s="4">
+        <v>39306</v>
       </c>
       <c r="BS28" s="5"/>
       <c r="BT28" s="5">
@@ -6554,7 +6671,7 @@
         <v>60080</v>
       </c>
       <c r="BU28" s="5">
-        <f t="shared" ref="BU28:BU35" si="12">SUM(O28:R28)</f>
+        <f t="shared" ref="BU28:BU35" si="10">SUM(O28:R28)</f>
         <v>75030</v>
       </c>
       <c r="BV28" s="5">
@@ -6654,7 +6771,13 @@
         <v>13756</v>
       </c>
       <c r="AF29" s="4">
-        <v>14200</v>
+        <v>14250</v>
+      </c>
+      <c r="AG29" s="4">
+        <v>13192</v>
+      </c>
+      <c r="AH29" s="4">
+        <v>12854</v>
       </c>
       <c r="AQ29" s="4">
         <v>1104</v>
@@ -6671,7 +6794,7 @@
         <v>54093</v>
       </c>
       <c r="BU29" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>59876</v>
       </c>
       <c r="BV29" s="5">
@@ -6785,8 +6908,23 @@
         <v>15089</v>
       </c>
       <c r="AH31" s="4">
-        <f t="shared" ref="AH31:AH32" si="13">+AD31*1.1</f>
-        <v>18849.600000000002</v>
+        <v>17234</v>
+      </c>
+      <c r="AI31" s="4">
+        <f>+AE31*1.15</f>
+        <v>18310.3</v>
+      </c>
+      <c r="AJ31" s="4">
+        <f t="shared" ref="AJ31:AJ32" si="11">+AF31*1.1</f>
+        <v>18096.100000000002</v>
+      </c>
+      <c r="AK31" s="4">
+        <f t="shared" ref="AK31:AK32" si="12">+AG31*1.1</f>
+        <v>16597.900000000001</v>
+      </c>
+      <c r="AL31" s="4">
+        <f t="shared" ref="AL31:AL32" si="13">+AH31*1.1</f>
+        <v>18957.400000000001</v>
       </c>
       <c r="BO31" s="4">
         <v>61502</v>
@@ -6808,7 +6946,7 @@
         <v>71074</v>
       </c>
       <c r="BU31" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>72732</v>
       </c>
       <c r="BV31" s="5">
@@ -6942,8 +7080,23 @@
         <v>67797</v>
       </c>
       <c r="AH32" s="4">
+        <v>72773</v>
+      </c>
+      <c r="AI32" s="4">
+        <f>+AE32*1.15</f>
+        <v>71013.649999999994</v>
+      </c>
+      <c r="AJ32" s="4">
+        <f t="shared" si="11"/>
+        <v>71304.200000000012</v>
+      </c>
+      <c r="AK32" s="4">
+        <f t="shared" si="12"/>
+        <v>74576.700000000012</v>
+      </c>
+      <c r="AL32" s="4">
         <f t="shared" si="13"/>
-        <v>65235.500000000007</v>
+        <v>80050.3</v>
       </c>
       <c r="BO32" s="4">
         <v>23818</v>
@@ -6965,7 +7118,7 @@
         <v>97014</v>
       </c>
       <c r="BU32" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>125538</v>
       </c>
       <c r="BV32" s="5">
@@ -7131,23 +7284,23 @@
       </c>
       <c r="AH33" s="7">
         <f t="shared" si="22"/>
-        <v>84085.1</v>
+        <v>90007</v>
       </c>
       <c r="AI33" s="7">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>89323.95</v>
       </c>
       <c r="AJ33" s="7">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>89400.300000000017</v>
       </c>
       <c r="AK33" s="7">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>91174.6</v>
       </c>
       <c r="AL33" s="7">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>99007.700000000012</v>
       </c>
       <c r="AO33" s="6">
         <v>1183</v>
@@ -7385,6 +7538,9 @@
       <c r="AG34" s="4">
         <v>2733</v>
       </c>
+      <c r="AH34" s="4">
+        <v>2938</v>
+      </c>
       <c r="BO34" s="4">
         <v>17880</v>
       </c>
@@ -7405,7 +7561,7 @@
         <v>18219</v>
       </c>
       <c r="BU34" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>19064</v>
       </c>
       <c r="BV34" s="5">
@@ -7538,6 +7694,9 @@
       <c r="AG35" s="4">
         <v>24095</v>
       </c>
+      <c r="AH35" s="4">
+        <v>26587</v>
+      </c>
       <c r="BO35" s="4">
         <v>14900</v>
       </c>
@@ -7558,7 +7717,7 @@
         <v>34013</v>
       </c>
       <c r="BU35" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>43586</v>
       </c>
       <c r="BV35" s="5">
@@ -7723,24 +7882,24 @@
         <v>26828</v>
       </c>
       <c r="AH36" s="4">
-        <f>+AH33-AH37</f>
-        <v>25225.530000000006</v>
+        <f t="shared" ref="AH36" si="34">+AH34+AH35</f>
+        <v>29525</v>
       </c>
       <c r="AI36" s="4">
-        <f t="shared" ref="AI36:AL36" si="34">+AI33-AI37</f>
-        <v>0</v>
+        <f t="shared" ref="AI36:AL36" si="35">+AI33-AI37</f>
+        <v>26797.185000000005</v>
       </c>
       <c r="AJ36" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>26820.090000000011</v>
       </c>
       <c r="AK36" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>27352.380000000005</v>
       </c>
       <c r="AL36" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>29702.310000000012</v>
       </c>
       <c r="AO36" s="4">
         <v>253</v>
@@ -7821,31 +7980,31 @@
         <v>33038</v>
       </c>
       <c r="BO36" s="5">
-        <f t="shared" ref="BO36" si="35">BO34+BO35</f>
+        <f t="shared" ref="BO36" si="36">BO34+BO35</f>
         <v>32780</v>
       </c>
       <c r="BP36" s="5">
-        <f t="shared" ref="BP36:BQ36" si="36">BP34+BP35</f>
+        <f t="shared" ref="BP36:BQ36" si="37">BP34+BP35</f>
         <v>34261</v>
       </c>
       <c r="BQ36" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>38353</v>
       </c>
       <c r="BR36" s="5">
-        <f t="shared" ref="BR36:BS36" si="37">BR34+BR35</f>
+        <f t="shared" ref="BR36:BS36" si="38">BR34+BR35</f>
         <v>42910</v>
       </c>
       <c r="BS36" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>46078</v>
       </c>
       <c r="BT36" s="5">
-        <f t="shared" ref="BT36:BU36" si="38">BT34+BT35</f>
+        <f t="shared" ref="BT36:BU36" si="39">BT34+BT35</f>
         <v>52232</v>
       </c>
       <c r="BU36" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>62650</v>
       </c>
       <c r="BV36" s="5">
@@ -7861,23 +8020,23 @@
         <v>87831</v>
       </c>
       <c r="BY36" s="5">
-        <f t="shared" ref="BY36:CC36" si="39">+BY33-BY37</f>
+        <f t="shared" ref="BY36:CC36" si="40">+BY33-BY37</f>
         <v>108819.42059999998</v>
       </c>
       <c r="BZ36" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>127647.99148199995</v>
       </c>
       <c r="CA36" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>143896.00389845995</v>
       </c>
       <c r="CB36" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>156543.67651621375</v>
       </c>
       <c r="CC36" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>170403.85856258019</v>
       </c>
     </row>
@@ -7886,43 +8045,43 @@
         <v>22</v>
       </c>
       <c r="C37" s="5">
-        <f t="shared" ref="C37:I37" si="40">+C33-C36</f>
+        <f t="shared" ref="C37:I37" si="41">+C33-C36</f>
         <v>19179</v>
       </c>
       <c r="D37" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>20048</v>
       </c>
       <c r="E37" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>20401</v>
       </c>
       <c r="F37" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>23305</v>
       </c>
       <c r="G37" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>22649</v>
       </c>
       <c r="H37" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>24548</v>
       </c>
       <c r="I37" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>24046</v>
       </c>
       <c r="J37" s="5">
-        <f t="shared" ref="J37" si="41">J33-J36</f>
+        <f t="shared" ref="J37" si="42">J33-J36</f>
         <v>25694</v>
       </c>
       <c r="K37" s="5">
-        <f t="shared" ref="K37:L37" si="42">K33-K36</f>
+        <f t="shared" ref="K37:L37" si="43">K33-K36</f>
         <v>26152</v>
       </c>
       <c r="L37" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>28882</v>
       </c>
       <c r="M37" s="5">
@@ -7930,23 +8089,23 @@
         <v>28661</v>
       </c>
       <c r="N37" s="5">
-        <f t="shared" ref="N37:Q37" si="43">N33-N36</f>
+        <f t="shared" ref="N37:Q37" si="44">N33-N36</f>
         <v>32161</v>
       </c>
       <c r="O37" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>31671</v>
       </c>
       <c r="P37" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>34768</v>
       </c>
       <c r="Q37" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>33745</v>
       </c>
       <c r="R37" s="5">
-        <f t="shared" ref="R37" si="44">R33-R36</f>
+        <f t="shared" ref="R37" si="45">R33-R36</f>
         <v>35436</v>
       </c>
       <c r="S37" s="5">
@@ -7966,199 +8125,199 @@
         <v>39394</v>
       </c>
       <c r="W37" s="4">
-        <f t="shared" ref="W37:AD37" si="45">+W33-W36</f>
+        <f t="shared" ref="W37:AD37" si="46">+W33-W36</f>
         <v>40215</v>
       </c>
       <c r="X37" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>42397</v>
       </c>
       <c r="Y37" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>43353</v>
       </c>
       <c r="Z37" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>45043</v>
       </c>
       <c r="AA37" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>45486</v>
       </c>
       <c r="AB37" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>47833</v>
       </c>
       <c r="AC37" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>48147</v>
       </c>
       <c r="AD37" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>52427</v>
       </c>
       <c r="AE37" s="4">
-        <f t="shared" ref="AE37:AG37" si="46">+AE33-AE36</f>
+        <f t="shared" ref="AE37:AG37" si="47">+AE33-AE36</f>
         <v>53630</v>
       </c>
       <c r="AF37" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>55295</v>
       </c>
       <c r="AG37" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>56058</v>
       </c>
       <c r="AH37" s="4">
-        <f>+AH33*0.7</f>
-        <v>58859.57</v>
+        <f t="shared" ref="AH37" si="48">+AH33-AH36</f>
+        <v>60482</v>
       </c>
       <c r="AI37" s="4">
-        <f t="shared" ref="AI37:AL37" si="47">+AI33*0.7</f>
-        <v>0</v>
+        <f t="shared" ref="AI37:AL37" si="49">+AI33*0.7</f>
+        <v>62526.764999999992</v>
       </c>
       <c r="AJ37" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f t="shared" si="49"/>
+        <v>62580.210000000006</v>
       </c>
       <c r="AK37" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f t="shared" si="49"/>
+        <v>63822.22</v>
       </c>
       <c r="AL37" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f t="shared" si="49"/>
+        <v>69305.39</v>
       </c>
       <c r="AO37" s="4">
-        <f t="shared" ref="AO37:AU37" si="48">AO33-AO36</f>
+        <f t="shared" ref="AO37:AU37" si="50">AO33-AO36</f>
         <v>930</v>
       </c>
       <c r="AP37" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>1481</v>
       </c>
       <c r="AQ37" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>2292</v>
       </c>
       <c r="AR37" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>3120</v>
       </c>
       <c r="AS37" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>3886</v>
       </c>
       <c r="AT37" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>5060</v>
       </c>
       <c r="AU37" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>7483</v>
       </c>
       <c r="AV37" s="4">
-        <f t="shared" ref="AV37" si="49">AV33-AV36</f>
+        <f t="shared" ref="AV37" si="51">AV33-AV36</f>
         <v>10273</v>
       </c>
       <c r="AW37" s="4">
-        <f t="shared" ref="AW37:BN37" si="50">AW33-AW36</f>
+        <f t="shared" ref="AW37:BN37" si="52">AW33-AW36</f>
         <v>13287</v>
       </c>
       <c r="AX37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>16933</v>
       </c>
       <c r="AY37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>19954</v>
       </c>
       <c r="AZ37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>21841</v>
       </c>
       <c r="BA37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>23174</v>
       </c>
       <c r="BB37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>26501</v>
       </c>
       <c r="BC37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>30119</v>
       </c>
       <c r="BD37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>33588</v>
       </c>
       <c r="BE37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>36632</v>
       </c>
       <c r="BF37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>40429</v>
       </c>
       <c r="BG37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>48822</v>
       </c>
       <c r="BH37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>46282</v>
       </c>
       <c r="BI37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>50089</v>
       </c>
       <c r="BJ37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>54366</v>
       </c>
       <c r="BK37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>56193</v>
       </c>
       <c r="BL37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>57600</v>
       </c>
       <c r="BM37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>59899</v>
       </c>
       <c r="BN37" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>60542</v>
       </c>
       <c r="BO37" s="5">
-        <f t="shared" ref="BO37" si="51">BO33-BO36</f>
+        <f t="shared" ref="BO37" si="53">BO33-BO36</f>
         <v>52540</v>
       </c>
       <c r="BP37" s="5">
-        <f t="shared" ref="BP37:BQ37" si="52">BP33-BP36</f>
+        <f t="shared" ref="BP37:BQ37" si="54">BP33-BP36</f>
         <v>62310</v>
       </c>
       <c r="BQ37" s="5">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>72007</v>
       </c>
       <c r="BR37" s="5">
-        <f t="shared" ref="BR37:BS37" si="53">BR33-BR36</f>
+        <f t="shared" ref="BR37:BS37" si="55">BR33-BR36</f>
         <v>82933</v>
       </c>
       <c r="BS37" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>96937</v>
       </c>
       <c r="BT37" s="5">
-        <f t="shared" ref="BT37:BU37" si="54">BT33-BT36</f>
+        <f t="shared" ref="BT37:BU37" si="56">BT33-BT36</f>
         <v>115856</v>
       </c>
       <c r="BU37" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>135620</v>
       </c>
       <c r="BV37" s="5">
@@ -8174,23 +8333,23 @@
         <v>193893</v>
       </c>
       <c r="BY37" s="5">
-        <f t="shared" ref="BY37:CC37" si="55">+BY33*0.67</f>
+        <f t="shared" ref="BY37:CC37" si="57">+BY33*0.67</f>
         <v>220936.39939999997</v>
       </c>
       <c r="BZ37" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>259164.10391799998</v>
       </c>
       <c r="CA37" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>292152.49276353995</v>
       </c>
       <c r="CB37" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>317831.10080564616</v>
       </c>
       <c r="CC37" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>345971.47041493555</v>
       </c>
     </row>
@@ -8292,8 +8451,23 @@
         <v>8915</v>
       </c>
       <c r="AH38" s="4">
-        <f t="shared" ref="AH38:AH40" si="56">+AD38*1.1</f>
-        <v>9711.9000000000015</v>
+        <v>9997</v>
+      </c>
+      <c r="AI38" s="4">
+        <f t="shared" ref="AI38:AI40" si="58">+AE38*1.1</f>
+        <v>8960.6</v>
+      </c>
+      <c r="AJ38" s="4">
+        <f t="shared" ref="AJ38:AJ40" si="59">+AF38*1.1</f>
+        <v>9354.4000000000015</v>
+      </c>
+      <c r="AK38" s="4">
+        <f t="shared" ref="AK38:AK40" si="60">+AG38*1.1</f>
+        <v>9806.5</v>
+      </c>
+      <c r="AL38" s="4">
+        <f t="shared" ref="AL38:AL40" si="61">+AH38*1.1</f>
+        <v>10996.7</v>
       </c>
       <c r="AO38" s="4">
         <v>181</v>
@@ -8393,11 +8567,11 @@
         <v>20716</v>
       </c>
       <c r="BU38" s="5">
-        <f t="shared" ref="BU38:BU40" si="57">SUM(O38:R38)</f>
+        <f t="shared" ref="BU38:BU40" si="62">SUM(O38:R38)</f>
         <v>24512</v>
       </c>
       <c r="BV38" s="5">
-        <f t="shared" ref="BV38:BV40" si="58">SUM(S38:V38)</f>
+        <f t="shared" ref="BV38:BV40" si="63">SUM(S38:V38)</f>
         <v>27195</v>
       </c>
       <c r="BW38" s="5">
@@ -8409,23 +8583,23 @@
         <v>32488</v>
       </c>
       <c r="BY38" s="5">
-        <f t="shared" ref="BY38:CC38" si="59">+BX38*1.03</f>
+        <f t="shared" ref="BY38:CC38" si="64">+BX38*1.03</f>
         <v>33462.639999999999</v>
       </c>
       <c r="BZ38" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>34466.519200000002</v>
       </c>
       <c r="CA38" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>35500.514776000004</v>
       </c>
       <c r="CB38" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>36565.530219280008</v>
       </c>
       <c r="CC38" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>37662.496125858408</v>
       </c>
     </row>
@@ -8527,8 +8701,23 @@
         <v>6814</v>
       </c>
       <c r="AH39" s="4">
-        <f t="shared" si="56"/>
-        <v>8013.5000000000009</v>
+        <v>7595</v>
+      </c>
+      <c r="AI39" s="4">
+        <f t="shared" si="58"/>
+        <v>6288.7000000000007</v>
+      </c>
+      <c r="AJ39" s="4">
+        <f t="shared" si="59"/>
+        <v>7242.4000000000005</v>
+      </c>
+      <c r="AK39" s="4">
+        <f t="shared" si="60"/>
+        <v>7495.4000000000005</v>
+      </c>
+      <c r="AL39" s="4">
+        <f t="shared" si="61"/>
+        <v>8354.5</v>
       </c>
       <c r="AO39" s="4">
         <v>317</v>
@@ -8628,11 +8817,11 @@
         <v>20117</v>
       </c>
       <c r="BU39" s="5">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>21825</v>
       </c>
       <c r="BV39" s="5">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>22759</v>
       </c>
       <c r="BW39" s="5">
@@ -8644,23 +8833,23 @@
         <v>25654</v>
       </c>
       <c r="BY39" s="5">
-        <f t="shared" ref="BY39:CC39" si="60">+BX39*1.03</f>
+        <f t="shared" ref="BY39:CC39" si="65">+BX39*1.03</f>
         <v>26423.62</v>
       </c>
       <c r="BZ39" s="5">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>27216.328600000001</v>
       </c>
       <c r="CA39" s="5">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>28032.818458000002</v>
       </c>
       <c r="CB39" s="5">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>28873.803011740001</v>
       </c>
       <c r="CC39" s="5">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>29740.017102092203</v>
       </c>
     </row>
@@ -8762,8 +8951,23 @@
         <v>1931</v>
       </c>
       <c r="AH40" s="4">
-        <f t="shared" si="56"/>
-        <v>2189</v>
+        <v>2287</v>
+      </c>
+      <c r="AI40" s="4">
+        <f t="shared" si="58"/>
+        <v>1986.6000000000001</v>
+      </c>
+      <c r="AJ40" s="4">
+        <f t="shared" si="59"/>
+        <v>2125.2000000000003</v>
+      </c>
+      <c r="AK40" s="4">
+        <f t="shared" si="60"/>
+        <v>2124.1000000000004</v>
+      </c>
+      <c r="AL40" s="4">
+        <f t="shared" si="61"/>
+        <v>2515.7000000000003</v>
       </c>
       <c r="AO40" s="4">
         <v>39</v>
@@ -8863,11 +9067,11 @@
         <v>5107</v>
       </c>
       <c r="BU40" s="5">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>5900</v>
       </c>
       <c r="BV40" s="5">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>7575</v>
       </c>
       <c r="BW40" s="5">
@@ -8879,23 +9083,23 @@
         <v>7223</v>
       </c>
       <c r="BY40" s="5">
-        <f t="shared" ref="BY40:CC40" si="61">+BX40*1.03</f>
+        <f t="shared" ref="BY40:CC40" si="66">+BX40*1.03</f>
         <v>7439.6900000000005</v>
       </c>
       <c r="BZ40" s="5">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>7662.8807000000006</v>
       </c>
       <c r="CA40" s="5">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>7892.7671210000008</v>
       </c>
       <c r="CB40" s="5">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>8129.5501346300007</v>
       </c>
       <c r="CC40" s="5">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>8373.4366386689017</v>
       </c>
     </row>
@@ -8904,59 +9108,59 @@
         <v>23</v>
       </c>
       <c r="C41" s="5">
-        <f t="shared" ref="C41:D41" si="62">SUM(C38:C40)</f>
+        <f t="shared" ref="C41:D41" si="67">SUM(C38:C40)</f>
         <v>9224</v>
       </c>
       <c r="D41" s="5">
-        <f t="shared" si="62"/>
+        <f t="shared" si="67"/>
         <v>9790</v>
       </c>
       <c r="E41" s="5">
-        <f t="shared" ref="E41:F41" si="63">SUM(E38:E40)</f>
+        <f t="shared" ref="E41:F41" si="68">SUM(E38:E40)</f>
         <v>10060</v>
       </c>
       <c r="F41" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="68"/>
         <v>10900</v>
       </c>
       <c r="G41" s="5">
-        <f t="shared" ref="G41:H41" si="64">SUM(G38:G40)</f>
+        <f t="shared" ref="G41:H41" si="69">SUM(G38:G40)</f>
         <v>9963</v>
       </c>
       <c r="H41" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>10657</v>
       </c>
       <c r="I41" s="5">
-        <f t="shared" ref="I41:J41" si="65">SUM(I38:I40)</f>
+        <f t="shared" ref="I41:J41" si="70">SUM(I38:I40)</f>
         <v>11071</v>
       </c>
       <c r="J41" s="5">
-        <f t="shared" si="65"/>
+        <f t="shared" si="70"/>
         <v>12287</v>
       </c>
       <c r="K41" s="5">
-        <f t="shared" ref="K41:P41" si="66">SUM(K38:K40)</f>
+        <f t="shared" ref="K41:P41" si="71">SUM(K38:K40)</f>
         <v>10276</v>
       </c>
       <c r="L41" s="5">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>10985</v>
       </c>
       <c r="M41" s="5">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>11613</v>
       </c>
       <c r="N41" s="5">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>13066</v>
       </c>
       <c r="O41" s="5">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>11433</v>
       </c>
       <c r="P41" s="5">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>12521</v>
       </c>
       <c r="Q41" s="5">
@@ -8964,11 +9168,11 @@
         <v>13381</v>
       </c>
       <c r="R41" s="5">
-        <f t="shared" ref="R41:S41" si="67">SUM(R38:R40)</f>
+        <f t="shared" ref="R41:S41" si="72">SUM(R38:R40)</f>
         <v>14902</v>
       </c>
       <c r="S41" s="5">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>13152</v>
       </c>
       <c r="T41" s="5">
@@ -8976,85 +9180,85 @@
         <v>14860</v>
       </c>
       <c r="U41" s="5">
-        <f t="shared" ref="U41:V41" si="68">SUM(U38:U40)</f>
+        <f t="shared" ref="U41:V41" si="73">SUM(U38:U40)</f>
         <v>14377</v>
       </c>
       <c r="V41" s="5">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>15140</v>
       </c>
       <c r="W41" s="5">
-        <f t="shared" ref="W41:Y41" si="69">SUM(W38:W40)</f>
+        <f t="shared" ref="W41:Y41" si="74">SUM(W38:W40)</f>
         <v>13320</v>
       </c>
       <c r="X41" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="74"/>
         <v>15365</v>
       </c>
       <c r="Y41" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="74"/>
         <v>15772</v>
       </c>
       <c r="Z41" s="5">
-        <f t="shared" ref="Z41:AE41" si="70">SUM(Z38:Z40)</f>
+        <f t="shared" ref="Z41:AE41" si="75">SUM(Z38:Z40)</f>
         <v>17118</v>
       </c>
       <c r="AA41" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>14934</v>
       </c>
       <c r="AB41" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>16180</v>
       </c>
       <c r="AC41" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>16147</v>
       </c>
       <c r="AD41" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>18104</v>
       </c>
       <c r="AE41" s="5">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>15669</v>
       </c>
       <c r="AF41" s="5">
-        <f t="shared" ref="AF41:AH41" si="71">SUM(AF38:AF40)</f>
+        <f t="shared" ref="AF41:AH41" si="76">SUM(AF38:AF40)</f>
         <v>17020</v>
       </c>
       <c r="AG41" s="5">
-        <f t="shared" si="71"/>
+        <f t="shared" si="76"/>
         <v>17660</v>
       </c>
       <c r="AH41" s="5">
-        <f t="shared" si="71"/>
-        <v>19914.400000000001</v>
+        <f t="shared" si="76"/>
+        <v>19879</v>
       </c>
       <c r="AI41" s="5">
-        <f t="shared" ref="AI41:AL41" si="72">SUM(AI38:AI40)</f>
-        <v>0</v>
+        <f t="shared" ref="AI41:AL41" si="77">SUM(AI38:AI40)</f>
+        <v>17235.900000000001</v>
       </c>
       <c r="AJ41" s="5">
-        <f t="shared" si="72"/>
-        <v>0</v>
+        <f t="shared" si="77"/>
+        <v>18722.000000000004</v>
       </c>
       <c r="AK41" s="5">
-        <f t="shared" si="72"/>
-        <v>0</v>
+        <f t="shared" si="77"/>
+        <v>19426</v>
       </c>
       <c r="AL41" s="5">
-        <f t="shared" si="72"/>
-        <v>0</v>
+        <f t="shared" si="77"/>
+        <v>21866.9</v>
       </c>
       <c r="AM41" s="5"/>
       <c r="AN41" s="5"/>
       <c r="AO41" s="5">
-        <f t="shared" ref="AO41:AP41" si="73">AO38+AO39+AO40</f>
+        <f t="shared" ref="AO41:AP41" si="78">AO38+AO39+AO40</f>
         <v>537</v>
       </c>
       <c r="AP41" s="5">
-        <f t="shared" si="73"/>
+        <f t="shared" si="78"/>
         <v>831</v>
       </c>
       <c r="AQ41" s="5">
@@ -9078,115 +9282,115 @@
         <v>4405</v>
       </c>
       <c r="AV41" s="5">
-        <f t="shared" ref="AV41" si="74">AV38+AV39+AV40</f>
+        <f t="shared" ref="AV41" si="79">AV38+AV39+AV40</f>
         <v>5143</v>
       </c>
       <c r="AW41" s="5">
-        <f t="shared" ref="AW41:BN41" si="75">AW38+AW39+AW40</f>
+        <f t="shared" ref="AW41:BN41" si="80">AW38+AW39+AW40</f>
         <v>6347</v>
       </c>
       <c r="AX41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>6890</v>
       </c>
       <c r="AY41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>8925</v>
       </c>
       <c r="AZ41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>10121</v>
       </c>
       <c r="BA41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>11264</v>
       </c>
       <c r="BB41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>13284</v>
       </c>
       <c r="BC41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>21085</v>
       </c>
       <c r="BD41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>19027</v>
       </c>
       <c r="BE41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>20160</v>
       </c>
       <c r="BF41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>21905</v>
       </c>
       <c r="BG41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>26330</v>
       </c>
       <c r="BH41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>25589</v>
       </c>
       <c r="BI41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>25932</v>
       </c>
       <c r="BJ41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>27205</v>
       </c>
       <c r="BK41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>28237</v>
       </c>
       <c r="BL41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>30836</v>
       </c>
       <c r="BM41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>32013</v>
       </c>
       <c r="BN41" s="5">
-        <f t="shared" si="75"/>
+        <f t="shared" si="80"/>
         <v>32370</v>
       </c>
       <c r="BO41" s="5">
-        <f t="shared" ref="BO41:BP41" si="76">SUM(BO38:BO40)</f>
+        <f t="shared" ref="BO41:BP41" si="81">SUM(BO38:BO40)</f>
         <v>31248</v>
       </c>
       <c r="BP41" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" si="81"/>
         <v>32979</v>
       </c>
       <c r="BQ41" s="5">
-        <f t="shared" ref="BQ41:BR41" si="77">SUM(BQ38:BQ40)</f>
+        <f t="shared" ref="BQ41:BR41" si="82">SUM(BQ38:BQ40)</f>
         <v>36949</v>
       </c>
       <c r="BR41" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>39974</v>
       </c>
       <c r="BS41" s="5">
-        <f t="shared" ref="BS41" si="78">SUM(BS38:BS40)</f>
+        <f t="shared" ref="BS41" si="83">SUM(BS38:BS40)</f>
         <v>43978</v>
       </c>
       <c r="BT41" s="5">
-        <f t="shared" ref="BT41:BV41" si="79">SUM(BT38:BT40)</f>
+        <f t="shared" ref="BT41:BV41" si="84">SUM(BT38:BT40)</f>
         <v>45940</v>
       </c>
       <c r="BU41" s="5">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>52237</v>
       </c>
       <c r="BV41" s="5">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>57529</v>
       </c>
       <c r="BW41" s="5">
-        <f t="shared" ref="BW41" si="80">SUM(BW38:BW40)</f>
+        <f t="shared" ref="BW41" si="85">SUM(BW38:BW40)</f>
         <v>61575</v>
       </c>
       <c r="BX41" s="5">
@@ -9194,23 +9398,23 @@
         <v>65365</v>
       </c>
       <c r="BY41" s="5">
-        <f t="shared" ref="BY41" si="81">SUM(BY38:BY40)</f>
+        <f t="shared" ref="BY41" si="86">SUM(BY38:BY40)</f>
         <v>67325.95</v>
       </c>
       <c r="BZ41" s="5">
-        <f t="shared" ref="BZ41" si="82">SUM(BZ38:BZ40)</f>
+        <f t="shared" ref="BZ41" si="87">SUM(BZ38:BZ40)</f>
         <v>69345.728499999997</v>
       </c>
       <c r="CA41" s="5">
-        <f t="shared" ref="CA41" si="83">SUM(CA38:CA40)</f>
+        <f t="shared" ref="CA41" si="88">SUM(CA38:CA40)</f>
         <v>71426.100355000002</v>
       </c>
       <c r="CB41" s="5">
-        <f t="shared" ref="CB41" si="84">SUM(CB38:CB40)</f>
+        <f t="shared" ref="CB41" si="89">SUM(CB38:CB40)</f>
         <v>73568.883365650006</v>
       </c>
       <c r="CC41" s="5">
-        <f t="shared" ref="CC41" si="85">SUM(CC38:CC40)</f>
+        <f t="shared" ref="CC41" si="90">SUM(CC38:CC40)</f>
         <v>75775.949866619514</v>
       </c>
     </row>
@@ -9219,59 +9423,59 @@
         <v>24</v>
       </c>
       <c r="C42" s="5">
-        <f t="shared" ref="C42:D42" si="86">C37-C41</f>
+        <f t="shared" ref="C42:D42" si="91">C37-C41</f>
         <v>9955</v>
       </c>
       <c r="D42" s="5">
-        <f t="shared" si="86"/>
+        <f t="shared" si="91"/>
         <v>10258</v>
       </c>
       <c r="E42" s="5">
-        <f t="shared" ref="E42:F42" si="87">E37-E41</f>
+        <f t="shared" ref="E42:F42" si="92">E37-E41</f>
         <v>10341</v>
       </c>
       <c r="F42" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="92"/>
         <v>12405</v>
       </c>
       <c r="G42" s="5">
-        <f t="shared" ref="G42:H42" si="88">G37-G41</f>
+        <f t="shared" ref="G42:H42" si="93">G37-G41</f>
         <v>12686</v>
       </c>
       <c r="H42" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>13891</v>
       </c>
       <c r="I42" s="5">
-        <f t="shared" ref="I42:J42" si="89">I37-I41</f>
+        <f t="shared" ref="I42:J42" si="94">I37-I41</f>
         <v>12975</v>
       </c>
       <c r="J42" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="94"/>
         <v>13407</v>
       </c>
       <c r="K42" s="5">
-        <f t="shared" ref="K42:P42" si="90">K37-K41</f>
+        <f t="shared" ref="K42:P42" si="95">K37-K41</f>
         <v>15876</v>
       </c>
       <c r="L42" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>17897</v>
       </c>
       <c r="M42" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>17048</v>
       </c>
       <c r="N42" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>19095</v>
       </c>
       <c r="O42" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>20238</v>
       </c>
       <c r="P42" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>22247</v>
       </c>
       <c r="Q42" s="5">
@@ -9279,11 +9483,11 @@
         <v>20364</v>
       </c>
       <c r="R42" s="5">
-        <f t="shared" ref="R42:S42" si="91">R37-R41</f>
+        <f t="shared" ref="R42:S42" si="96">R37-R41</f>
         <v>20534</v>
       </c>
       <c r="S42" s="5">
-        <f t="shared" si="91"/>
+        <f t="shared" si="96"/>
         <v>21518</v>
       </c>
       <c r="T42" s="5">
@@ -9295,81 +9499,81 @@
         <v>22352</v>
       </c>
       <c r="V42" s="5">
-        <f t="shared" ref="V42:Y42" si="92">V37-V41</f>
+        <f t="shared" ref="V42:Y42" si="97">V37-V41</f>
         <v>24254</v>
       </c>
       <c r="W42" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="97"/>
         <v>26895</v>
       </c>
       <c r="X42" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="97"/>
         <v>27032</v>
       </c>
       <c r="Y42" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="97"/>
         <v>27581</v>
       </c>
       <c r="Z42" s="5">
-        <f t="shared" ref="Z42:AE42" si="93">Z37-Z41</f>
+        <f t="shared" ref="Z42:AE42" si="98">Z37-Z41</f>
         <v>27925</v>
       </c>
       <c r="AA42" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="98"/>
         <v>30552</v>
       </c>
       <c r="AB42" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="98"/>
         <v>31653</v>
       </c>
       <c r="AC42" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="98"/>
         <v>32000</v>
       </c>
       <c r="AD42" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="98"/>
         <v>34323</v>
       </c>
       <c r="AE42" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="98"/>
         <v>37961</v>
       </c>
       <c r="AF42" s="5">
-        <f t="shared" ref="AF42:AH42" si="94">AF37-AF41</f>
+        <f t="shared" ref="AF42:AH42" si="99">AF37-AF41</f>
         <v>38275</v>
       </c>
       <c r="AG42" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="99"/>
         <v>38398</v>
       </c>
       <c r="AH42" s="5">
-        <f t="shared" si="94"/>
-        <v>38945.17</v>
+        <f t="shared" si="99"/>
+        <v>40603</v>
       </c>
       <c r="AI42" s="5">
-        <f t="shared" ref="AI42:AL42" si="95">AI37-AI41</f>
-        <v>0</v>
+        <f t="shared" ref="AI42:AL42" si="100">AI37-AI41</f>
+        <v>45290.864999999991</v>
       </c>
       <c r="AJ42" s="5">
-        <f t="shared" si="95"/>
-        <v>0</v>
+        <f t="shared" si="100"/>
+        <v>43858.210000000006</v>
       </c>
       <c r="AK42" s="5">
-        <f t="shared" si="95"/>
-        <v>0</v>
+        <f t="shared" si="100"/>
+        <v>44396.22</v>
       </c>
       <c r="AL42" s="5">
-        <f t="shared" si="95"/>
-        <v>0</v>
+        <f t="shared" si="100"/>
+        <v>47438.49</v>
       </c>
       <c r="AM42" s="5"/>
       <c r="AN42" s="5"/>
       <c r="AO42" s="5">
-        <f t="shared" ref="AO42:AP42" si="96">AO37-AO41</f>
+        <f t="shared" ref="AO42:AP42" si="101">AO37-AO41</f>
         <v>393</v>
       </c>
       <c r="AP42" s="5">
-        <f t="shared" si="96"/>
+        <f t="shared" si="101"/>
         <v>650</v>
       </c>
       <c r="AQ42" s="5">
@@ -9393,115 +9597,115 @@
         <v>3078</v>
       </c>
       <c r="AV42" s="5">
-        <f t="shared" ref="AV42" si="97">AV37-AV41</f>
+        <f t="shared" ref="AV42" si="102">AV37-AV41</f>
         <v>5130</v>
       </c>
       <c r="AW42" s="5">
-        <f t="shared" ref="AW42:BN42" si="98">AW37-AW41</f>
+        <f t="shared" ref="AW42:BN42" si="103">AW37-AW41</f>
         <v>6940</v>
       </c>
       <c r="AX42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>10043</v>
       </c>
       <c r="AY42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>11029</v>
       </c>
       <c r="AZ42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>11720</v>
       </c>
       <c r="BA42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>11910</v>
       </c>
       <c r="BB42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>13217</v>
       </c>
       <c r="BC42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>9034</v>
       </c>
       <c r="BD42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>14561</v>
       </c>
       <c r="BE42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>16472</v>
       </c>
       <c r="BF42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>18524</v>
       </c>
       <c r="BG42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>22492</v>
       </c>
       <c r="BH42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>20693</v>
       </c>
       <c r="BI42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>24157</v>
       </c>
       <c r="BJ42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>27161</v>
       </c>
       <c r="BK42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>27956</v>
       </c>
       <c r="BL42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>26764</v>
       </c>
       <c r="BM42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>27886</v>
       </c>
       <c r="BN42" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="103"/>
         <v>28172</v>
       </c>
       <c r="BO42" s="5">
-        <f t="shared" ref="BO42:BP42" si="99">BO37-BO41</f>
+        <f t="shared" ref="BO42:BP42" si="104">BO37-BO41</f>
         <v>21292</v>
       </c>
       <c r="BP42" s="5">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>29331</v>
       </c>
       <c r="BQ42" s="5">
-        <f t="shared" ref="BQ42:BR42" si="100">BQ37-BQ41</f>
+        <f t="shared" ref="BQ42:BR42" si="105">BQ37-BQ41</f>
         <v>35058</v>
       </c>
       <c r="BR42" s="5">
-        <f t="shared" si="100"/>
+        <f t="shared" si="105"/>
         <v>42959</v>
       </c>
       <c r="BS42" s="5">
-        <f t="shared" ref="BS42" si="101">BS37-BS41</f>
+        <f t="shared" ref="BS42" si="106">BS37-BS41</f>
         <v>52959</v>
       </c>
       <c r="BT42" s="5">
-        <f t="shared" ref="BT42:BV42" si="102">BT37-BT41</f>
+        <f t="shared" ref="BT42:BV42" si="107">BT37-BT41</f>
         <v>69916</v>
       </c>
       <c r="BU42" s="5">
-        <f t="shared" si="102"/>
+        <f t="shared" si="107"/>
         <v>83383</v>
       </c>
       <c r="BV42" s="5">
-        <f t="shared" si="102"/>
+        <f t="shared" si="107"/>
         <v>88523</v>
       </c>
       <c r="BW42" s="5">
-        <f t="shared" ref="BW42" si="103">BW37-BW41</f>
+        <f t="shared" ref="BW42" si="108">BW37-BW41</f>
         <v>109433</v>
       </c>
       <c r="BX42" s="5">
@@ -9509,23 +9713,23 @@
         <v>128528</v>
       </c>
       <c r="BY42" s="5">
-        <f t="shared" ref="BY42" si="104">BY37-BY41</f>
+        <f t="shared" ref="BY42" si="109">BY37-BY41</f>
         <v>153610.44939999998</v>
       </c>
       <c r="BZ42" s="5">
-        <f t="shared" ref="BZ42" si="105">BZ37-BZ41</f>
+        <f t="shared" ref="BZ42" si="110">BZ37-BZ41</f>
         <v>189818.37541799998</v>
       </c>
       <c r="CA42" s="5">
-        <f t="shared" ref="CA42" si="106">CA37-CA41</f>
+        <f t="shared" ref="CA42" si="111">CA37-CA41</f>
         <v>220726.39240853995</v>
       </c>
       <c r="CB42" s="5">
-        <f t="shared" ref="CB42" si="107">CB37-CB41</f>
+        <f t="shared" ref="CB42" si="112">CB37-CB41</f>
         <v>244262.21743999614</v>
       </c>
       <c r="CC42" s="5">
-        <f t="shared" ref="CC42" si="108">CC37-CC41</f>
+        <f t="shared" ref="CC42" si="113">CC37-CC41</f>
         <v>270195.52054831607</v>
       </c>
     </row>
@@ -9624,7 +9828,9 @@
       <c r="AG43" s="4">
         <v>942</v>
       </c>
-      <c r="AH43" s="4"/>
+      <c r="AH43" s="4">
+        <v>3444</v>
+      </c>
       <c r="AI43" s="4"/>
       <c r="AJ43" s="4"/>
       <c r="AK43" s="4"/>
@@ -9738,11 +9944,11 @@
         <v>1186</v>
       </c>
       <c r="BU43" s="5">
-        <f t="shared" ref="BU43" si="109">SUM(O43:R43)</f>
+        <f t="shared" ref="BU43" si="114">SUM(O43:R43)</f>
         <v>333</v>
       </c>
       <c r="BV43" s="5">
-        <f t="shared" ref="BV43" si="110">SUM(S43:V43)</f>
+        <f t="shared" ref="BV43" si="115">SUM(S43:V43)</f>
         <v>788</v>
       </c>
       <c r="BW43" s="5">
@@ -9779,35 +9985,35 @@
         <v>29</v>
       </c>
       <c r="C44" s="5">
-        <f t="shared" ref="C44:D44" si="111">C42+C43</f>
+        <f t="shared" ref="C44:D44" si="116">C42+C43</f>
         <v>10221</v>
       </c>
       <c r="D44" s="5">
-        <f t="shared" si="111"/>
+        <f t="shared" si="116"/>
         <v>10385</v>
       </c>
       <c r="E44" s="5">
-        <f t="shared" ref="E44:F44" si="112">E42+E43</f>
+        <f t="shared" ref="E44:F44" si="117">E42+E43</f>
         <v>10486</v>
       </c>
       <c r="F44" s="5">
-        <f t="shared" si="112"/>
+        <f t="shared" si="117"/>
         <v>12596</v>
       </c>
       <c r="G44" s="5">
-        <f t="shared" ref="G44:H44" si="113">G42+G43</f>
+        <f t="shared" ref="G44:H44" si="118">G42+G43</f>
         <v>12686</v>
       </c>
       <c r="H44" s="5">
-        <f t="shared" si="113"/>
+        <f t="shared" si="118"/>
         <v>14085</v>
       </c>
       <c r="I44" s="5">
-        <f t="shared" ref="I44:J44" si="114">I42+I43</f>
+        <f t="shared" ref="I44:J44" si="119">I42+I43</f>
         <v>12843</v>
       </c>
       <c r="J44" s="5">
-        <f t="shared" si="114"/>
+        <f t="shared" si="119"/>
         <v>13422</v>
       </c>
       <c r="K44" s="5">
@@ -9815,119 +10021,119 @@
         <v>16124</v>
       </c>
       <c r="L44" s="5">
-        <f t="shared" ref="L44:AL44" si="115">L42+L43</f>
+        <f t="shared" ref="L44:AL44" si="120">L42+L43</f>
         <v>18337</v>
       </c>
       <c r="M44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>17236</v>
       </c>
       <c r="N44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>19405</v>
       </c>
       <c r="O44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>20524</v>
       </c>
       <c r="P44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>22515</v>
       </c>
       <c r="Q44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>20190</v>
       </c>
       <c r="R44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>20487</v>
       </c>
       <c r="S44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>21572</v>
       </c>
       <c r="T44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>20339</v>
       </c>
       <c r="U44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>22673</v>
       </c>
       <c r="V44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>24727</v>
       </c>
       <c r="W44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>27284</v>
       </c>
       <c r="X44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>26526</v>
       </c>
       <c r="Y44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>26727</v>
       </c>
       <c r="Z44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>27250</v>
       </c>
       <c r="AA44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>30269</v>
       </c>
       <c r="AB44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>29365</v>
       </c>
       <c r="AC44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>31377</v>
       </c>
       <c r="AD44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>32616</v>
       </c>
       <c r="AE44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>34301</v>
       </c>
       <c r="AF44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>38275</v>
       </c>
       <c r="AG44" s="5">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>39340</v>
       </c>
       <c r="AH44" s="5">
-        <f t="shared" si="115"/>
-        <v>38945.17</v>
+        <f t="shared" si="120"/>
+        <v>44047</v>
       </c>
       <c r="AI44" s="5">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="120"/>
+        <v>45290.864999999991</v>
       </c>
       <c r="AJ44" s="5">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="120"/>
+        <v>43858.210000000006</v>
       </c>
       <c r="AK44" s="5">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="120"/>
+        <v>44396.22</v>
       </c>
       <c r="AL44" s="5">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="120"/>
+        <v>47438.49</v>
       </c>
       <c r="AO44" s="4">
-        <f t="shared" ref="AO44:AP44" si="116">AO43+AO42</f>
+        <f t="shared" ref="AO44:AP44" si="121">AO43+AO42</f>
         <v>410</v>
       </c>
       <c r="AP44" s="4">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>671</v>
       </c>
       <c r="AQ44" s="4">
@@ -9951,79 +10157,79 @@
         <v>3379</v>
       </c>
       <c r="AV44" s="4">
-        <f t="shared" ref="AV44" si="117">AV43+AV42</f>
+        <f t="shared" ref="AV44" si="122">AV43+AV42</f>
         <v>5314</v>
       </c>
       <c r="AW44" s="4">
-        <f t="shared" ref="AW44:BN44" si="118">AW43+AW42</f>
+        <f t="shared" ref="AW44:BN44" si="123">AW43+AW42</f>
         <v>7413</v>
       </c>
       <c r="AX44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>11731</v>
       </c>
       <c r="AY44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>14119</v>
       </c>
       <c r="AZ44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>11684</v>
       </c>
       <c r="BA44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>11605</v>
       </c>
       <c r="BB44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>14794</v>
       </c>
       <c r="BC44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>12221</v>
       </c>
       <c r="BD44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>16628</v>
       </c>
       <c r="BE44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>18262</v>
       </c>
       <c r="BF44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>20101</v>
       </c>
       <c r="BG44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>23814</v>
       </c>
       <c r="BH44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>20151</v>
       </c>
       <c r="BI44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>25072</v>
       </c>
       <c r="BJ44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>28071</v>
       </c>
       <c r="BK44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>28460</v>
       </c>
       <c r="BL44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>27052</v>
       </c>
       <c r="BM44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>27947</v>
       </c>
       <c r="BN44" s="4">
-        <f t="shared" si="118"/>
+        <f t="shared" si="123"/>
         <v>28518</v>
       </c>
       <c r="BO44" s="4">
@@ -10047,19 +10253,19 @@
         <v>53036</v>
       </c>
       <c r="BT44" s="5">
-        <f t="shared" ref="BT44:BV44" si="119">+BT42+BT43</f>
+        <f t="shared" ref="BT44:BV44" si="124">+BT42+BT43</f>
         <v>71102</v>
       </c>
       <c r="BU44" s="5">
-        <f t="shared" si="119"/>
+        <f t="shared" si="124"/>
         <v>83716</v>
       </c>
       <c r="BV44" s="5">
-        <f t="shared" si="119"/>
+        <f t="shared" si="124"/>
         <v>89311</v>
       </c>
       <c r="BW44" s="5">
-        <f t="shared" ref="BW44" si="120">+BW42+BW43</f>
+        <f t="shared" ref="BW44" si="125">+BW42+BW43</f>
         <v>107787</v>
       </c>
       <c r="BX44" s="5">
@@ -10067,23 +10273,23 @@
         <v>123627</v>
       </c>
       <c r="BY44" s="5">
-        <f t="shared" ref="BY44" si="121">+BY42+BY43</f>
+        <f t="shared" ref="BY44" si="126">+BY42+BY43</f>
         <v>148709.44939999998</v>
       </c>
       <c r="BZ44" s="5">
-        <f t="shared" ref="BZ44" si="122">+BZ42+BZ43</f>
+        <f t="shared" ref="BZ44" si="127">+BZ42+BZ43</f>
         <v>184917.37541799998</v>
       </c>
       <c r="CA44" s="5">
-        <f t="shared" ref="CA44" si="123">+CA42+CA43</f>
+        <f t="shared" ref="CA44" si="128">+CA42+CA43</f>
         <v>220726.39240853995</v>
       </c>
       <c r="CB44" s="5">
-        <f t="shared" ref="CB44" si="124">+CB42+CB43</f>
+        <f t="shared" ref="CB44" si="129">+CB42+CB43</f>
         <v>244262.21743999614</v>
       </c>
       <c r="CC44" s="5">
-        <f t="shared" ref="CC44" si="125">+CC42+CC43</f>
+        <f t="shared" ref="CC44" si="130">+CC42+CC43</f>
         <v>270195.52054831607</v>
       </c>
     </row>
@@ -10185,8 +10391,23 @@
         <v>7562</v>
       </c>
       <c r="AH45" s="4">
-        <f>+AH44*0.18</f>
-        <v>7010.1305999999995</v>
+        <v>8281</v>
+      </c>
+      <c r="AI45" s="4">
+        <f t="shared" ref="AI45:AL45" si="131">+AI44*0.18</f>
+        <v>8152.3556999999983</v>
+      </c>
+      <c r="AJ45" s="4">
+        <f t="shared" si="131"/>
+        <v>7894.4778000000006</v>
+      </c>
+      <c r="AK45" s="4">
+        <f t="shared" si="131"/>
+        <v>7991.3195999999998</v>
+      </c>
+      <c r="AL45" s="4">
+        <f t="shared" si="131"/>
+        <v>8538.9281999999985</v>
       </c>
       <c r="AO45" s="4">
         <v>131</v>
@@ -10287,11 +10508,11 @@
         <v>9831</v>
       </c>
       <c r="BU45" s="5">
-        <f t="shared" ref="BU45" si="126">SUM(O45:R45)</f>
+        <f t="shared" ref="BU45" si="132">SUM(O45:R45)</f>
         <v>10978</v>
       </c>
       <c r="BV45" s="5">
-        <f t="shared" ref="BV45" si="127">SUM(S45:V45)</f>
+        <f t="shared" ref="BV45" si="133">SUM(S45:V45)</f>
         <v>16950</v>
       </c>
       <c r="BW45" s="5">
@@ -10311,15 +10532,15 @@
         <v>33285.127575239996</v>
       </c>
       <c r="CA45" s="5">
-        <f t="shared" ref="CA45:CC45" si="128">+CA44*0.15</f>
+        <f t="shared" ref="CA45:CC45" si="134">+CA44*0.15</f>
         <v>33108.958861280989</v>
       </c>
       <c r="CB45" s="5">
-        <f t="shared" si="128"/>
+        <f t="shared" si="134"/>
         <v>36639.332615999418</v>
       </c>
       <c r="CC45" s="5">
-        <f t="shared" si="128"/>
+        <f t="shared" si="134"/>
         <v>40529.328082247412</v>
       </c>
     </row>
@@ -10328,35 +10549,35 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <f t="shared" ref="C46:D46" si="129">C44-C45</f>
+        <f t="shared" ref="C46:D46" si="135">C44-C45</f>
         <v>8824</v>
       </c>
       <c r="D46" s="5">
-        <f t="shared" si="129"/>
+        <f t="shared" si="135"/>
         <v>8420</v>
       </c>
       <c r="E46" s="5">
-        <f t="shared" ref="E46:F46" si="130">E44-E45</f>
+        <f t="shared" ref="E46:F46" si="136">E44-E45</f>
         <v>8809</v>
       </c>
       <c r="F46" s="5">
-        <f t="shared" si="130"/>
+        <f t="shared" si="136"/>
         <v>13187</v>
       </c>
       <c r="G46" s="5">
-        <f t="shared" ref="G46:H46" si="131">G44-G45</f>
+        <f t="shared" ref="G46:H46" si="137">G44-G45</f>
         <v>10678</v>
       </c>
       <c r="H46" s="5">
-        <f t="shared" si="131"/>
+        <f t="shared" si="137"/>
         <v>11649</v>
       </c>
       <c r="I46" s="5">
-        <f t="shared" ref="I46:J46" si="132">I44-I45</f>
+        <f t="shared" ref="I46:J46" si="138">I44-I45</f>
         <v>10752</v>
       </c>
       <c r="J46" s="5">
-        <f t="shared" si="132"/>
+        <f t="shared" si="138"/>
         <v>11202</v>
       </c>
       <c r="K46" s="5">
@@ -10364,39 +10585,39 @@
         <v>13893</v>
       </c>
       <c r="L46" s="5">
-        <f t="shared" ref="L46:AH46" si="133">L44-L45</f>
+        <f t="shared" ref="L46:AH46" si="139">L44-L45</f>
         <v>15463</v>
       </c>
       <c r="M46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>15457</v>
       </c>
       <c r="N46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>16458</v>
       </c>
       <c r="O46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>20505</v>
       </c>
       <c r="P46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>18765</v>
       </c>
       <c r="Q46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>16728</v>
       </c>
       <c r="R46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>16740</v>
       </c>
       <c r="S46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>17556</v>
       </c>
       <c r="T46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>16425</v>
       </c>
       <c r="U46" s="5">
@@ -10404,79 +10625,79 @@
         <v>18299</v>
       </c>
       <c r="V46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>20081</v>
       </c>
       <c r="W46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>22291</v>
       </c>
       <c r="X46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>21870</v>
       </c>
       <c r="Y46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>21939</v>
       </c>
       <c r="Z46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>22036</v>
       </c>
       <c r="AA46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>24667</v>
       </c>
       <c r="AB46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>24108</v>
       </c>
       <c r="AC46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>25824</v>
       </c>
       <c r="AD46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>27233</v>
       </c>
       <c r="AE46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>27747</v>
       </c>
       <c r="AF46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>28487</v>
       </c>
       <c r="AG46" s="5">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>31778</v>
       </c>
       <c r="AH46" s="5">
-        <f t="shared" si="133"/>
-        <v>31935.039399999998</v>
+        <f t="shared" si="139"/>
+        <v>35766</v>
       </c>
       <c r="AI46" s="5">
-        <f t="shared" ref="AI46:AL46" si="134">AI44-AI45</f>
-        <v>0</v>
+        <f t="shared" ref="AI46:AL46" si="140">AI44-AI45</f>
+        <v>37138.509299999991</v>
       </c>
       <c r="AJ46" s="5">
-        <f t="shared" si="134"/>
-        <v>0</v>
+        <f t="shared" si="140"/>
+        <v>35963.732200000006</v>
       </c>
       <c r="AK46" s="5">
-        <f t="shared" si="134"/>
-        <v>0</v>
+        <f t="shared" si="140"/>
+        <v>36404.900399999999</v>
       </c>
       <c r="AL46" s="5">
-        <f t="shared" si="134"/>
-        <v>0</v>
+        <f t="shared" si="140"/>
+        <v>38899.561799999996</v>
       </c>
       <c r="AO46" s="4">
-        <f t="shared" ref="AO46:AP46" si="135">AO44-AO45</f>
+        <f t="shared" ref="AO46:AP46" si="141">AO44-AO45</f>
         <v>279</v>
       </c>
       <c r="AP46" s="4">
-        <f t="shared" si="135"/>
+        <f t="shared" si="141"/>
         <v>463</v>
       </c>
       <c r="AQ46" s="4">
@@ -10500,79 +10721,79 @@
         <v>2195</v>
       </c>
       <c r="AV46" s="4">
-        <f t="shared" ref="AV46" si="136">AV44-AV45</f>
+        <f t="shared" ref="AV46" si="142">AV44-AV45</f>
         <v>3454</v>
       </c>
       <c r="AW46" s="4">
-        <f t="shared" ref="AW46:BN46" si="137">AW44-AW45</f>
+        <f t="shared" ref="AW46:BN46" si="143">AW44-AW45</f>
         <v>4758</v>
       </c>
       <c r="AX46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>7625</v>
       </c>
       <c r="AY46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>9265</v>
       </c>
       <c r="AZ46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>7880</v>
       </c>
       <c r="BA46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>7921</v>
       </c>
       <c r="BB46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>10061</v>
       </c>
       <c r="BC46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>8193</v>
       </c>
       <c r="BD46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>12254</v>
       </c>
       <c r="BE46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>12599</v>
       </c>
       <c r="BF46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>14065</v>
       </c>
       <c r="BG46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>17681</v>
       </c>
       <c r="BH46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>14899</v>
       </c>
       <c r="BI46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>18819</v>
       </c>
       <c r="BJ46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>23150</v>
       </c>
       <c r="BK46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>23171</v>
       </c>
       <c r="BL46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>21863</v>
       </c>
       <c r="BM46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>22201</v>
       </c>
       <c r="BN46" s="4">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>22204</v>
       </c>
       <c r="BO46" s="4">
@@ -10596,19 +10817,19 @@
         <v>44281</v>
       </c>
       <c r="BT46" s="4">
-        <f t="shared" ref="BT46:BV46" si="138">+BT44-BT45</f>
+        <f t="shared" ref="BT46:BV46" si="144">+BT44-BT45</f>
         <v>61271</v>
       </c>
       <c r="BU46" s="4">
-        <f t="shared" si="138"/>
+        <f t="shared" si="144"/>
         <v>72738</v>
       </c>
       <c r="BV46" s="4">
-        <f t="shared" si="138"/>
+        <f t="shared" si="144"/>
         <v>72361</v>
       </c>
       <c r="BW46" s="4">
-        <f t="shared" ref="BW46" si="139">+BW44-BW45</f>
+        <f t="shared" ref="BW46" si="145">+BW44-BW45</f>
         <v>88136</v>
       </c>
       <c r="BX46" s="4">
@@ -10616,255 +10837,255 @@
         <v>101832</v>
       </c>
       <c r="BY46" s="4">
-        <f t="shared" ref="BY46" si="140">+BY44-BY45</f>
+        <f t="shared" ref="BY46" si="146">+BY44-BY45</f>
         <v>121941.74850799999</v>
       </c>
       <c r="BZ46" s="4">
-        <f t="shared" ref="BZ46" si="141">+BZ44-BZ45</f>
+        <f t="shared" ref="BZ46" si="147">+BZ44-BZ45</f>
         <v>151632.24784276</v>
       </c>
       <c r="CA46" s="4">
-        <f t="shared" ref="CA46" si="142">+CA44-CA45</f>
+        <f t="shared" ref="CA46" si="148">+CA44-CA45</f>
         <v>187617.43354725896</v>
       </c>
       <c r="CB46" s="4">
-        <f t="shared" ref="CB46" si="143">+CB44-CB45</f>
+        <f t="shared" ref="CB46" si="149">+CB44-CB45</f>
         <v>207622.88482399672</v>
       </c>
       <c r="CC46" s="4">
-        <f t="shared" ref="CC46" si="144">+CC44-CC45</f>
+        <f t="shared" ref="CC46" si="150">+CC44-CC45</f>
         <v>229666.19246606866</v>
       </c>
       <c r="CD46" s="4">
-        <f t="shared" ref="CD46:DI46" si="145">+CC46*(1+$CH$50)</f>
+        <f t="shared" ref="CD46:DI46" si="151">+CC46*(1+$CH$50)</f>
         <v>234259.51631539004</v>
       </c>
       <c r="CE46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>238944.70664169785</v>
       </c>
       <c r="CF46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>243723.60077453181</v>
       </c>
       <c r="CG46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>248598.07279002244</v>
       </c>
       <c r="CH46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>253570.0342458229</v>
       </c>
       <c r="CI46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>258641.43493073937</v>
       </c>
       <c r="CJ46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>263814.26362935419</v>
       </c>
       <c r="CK46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>269090.54890194128</v>
       </c>
       <c r="CL46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>274472.3598799801</v>
       </c>
       <c r="CM46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>279961.80707757972</v>
       </c>
       <c r="CN46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>285561.0432191313</v>
       </c>
       <c r="CO46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>291272.26408351393</v>
       </c>
       <c r="CP46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>297097.70936518424</v>
       </c>
       <c r="CQ46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>303039.66355248791</v>
       </c>
       <c r="CR46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>309100.45682353765</v>
       </c>
       <c r="CS46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>315282.46596000838</v>
       </c>
       <c r="CT46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>321588.11527920858</v>
       </c>
       <c r="CU46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>328019.87758479273</v>
       </c>
       <c r="CV46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>334580.27513648861</v>
       </c>
       <c r="CW46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>341271.88063921838</v>
       </c>
       <c r="CX46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>348097.31825200276</v>
       </c>
       <c r="CY46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>355059.26461704285</v>
       </c>
       <c r="CZ46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>362160.44990938372</v>
       </c>
       <c r="DA46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>369403.6589075714</v>
       </c>
       <c r="DB46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>376791.73208572285</v>
       </c>
       <c r="DC46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>384327.56672743731</v>
       </c>
       <c r="DD46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>392014.11806198605</v>
       </c>
       <c r="DE46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>399854.40042322577</v>
       </c>
       <c r="DF46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>407851.48843169032</v>
       </c>
       <c r="DG46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>416008.51820032415</v>
       </c>
       <c r="DH46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>424328.68856433063</v>
       </c>
       <c r="DI46" s="4">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>432815.26233561727</v>
       </c>
       <c r="DJ46" s="4">
-        <f t="shared" ref="DJ46:EI46" si="146">+DI46*(1+$CH$50)</f>
+        <f t="shared" ref="DJ46:EI46" si="152">+DI46*(1+$CH$50)</f>
         <v>441471.56758232962</v>
       </c>
       <c r="DK46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>450300.99893397623</v>
       </c>
       <c r="DL46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>459307.01891265577</v>
       </c>
       <c r="DM46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>468493.15929090889</v>
       </c>
       <c r="DN46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>477863.02247672708</v>
       </c>
       <c r="DO46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>487420.28292626166</v>
       </c>
       <c r="DP46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>497168.6885847869</v>
       </c>
       <c r="DQ46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>507112.06235648267</v>
       </c>
       <c r="DR46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>517254.30360361235</v>
       </c>
       <c r="DS46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>527599.38967568462</v>
       </c>
       <c r="DT46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>538151.37746919831</v>
       </c>
       <c r="DU46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>548914.40501858224</v>
       </c>
       <c r="DV46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>559892.69311895384</v>
       </c>
       <c r="DW46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>571090.54698133294</v>
       </c>
       <c r="DX46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>582512.35792095959</v>
       </c>
       <c r="DY46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>594162.60507937882</v>
       </c>
       <c r="DZ46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>606045.85718096641</v>
       </c>
       <c r="EA46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>618166.7743245858</v>
       </c>
       <c r="EB46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>630530.10981107748</v>
       </c>
       <c r="EC46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>643140.71200729907</v>
       </c>
       <c r="ED46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>656003.52624744503</v>
       </c>
       <c r="EE46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>669123.59677239391</v>
       </c>
       <c r="EF46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>682506.0687078418</v>
       </c>
       <c r="EG46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>696156.19008199859</v>
       </c>
       <c r="EH46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>710079.31388363859</v>
       </c>
       <c r="EI46" s="4">
-        <f t="shared" si="146"/>
+        <f t="shared" si="152"/>
         <v>724280.90016131138</v>
       </c>
     </row>
@@ -10873,59 +11094,59 @@
         <v>33</v>
       </c>
       <c r="C47" s="8">
-        <f t="shared" ref="C47:D47" si="147">C46/C48</f>
+        <f t="shared" ref="C47:D47" si="153">C46/C48</f>
         <v>1.1362348699459182</v>
       </c>
       <c r="D47" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="153"/>
         <v>1.0839340885684861</v>
       </c>
       <c r="E47" s="8">
-        <f t="shared" ref="E47:F47" si="148">E46/E48</f>
+        <f t="shared" ref="E47:F47" si="154">E46/E48</f>
         <v>1.1375258264462811</v>
       </c>
       <c r="F47" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="154"/>
         <v>1.7059508408796895</v>
       </c>
       <c r="G47" s="8">
-        <f t="shared" ref="G47:H47" si="149">G46/G48</f>
+        <f t="shared" ref="G47:H47" si="155">G46/G48</f>
         <v>1.3849546044098573</v>
       </c>
       <c r="H47" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="155"/>
         <v>1.5146274866727343</v>
       </c>
       <c r="I47" s="8">
-        <f t="shared" ref="I47:J47" si="150">I46/I48</f>
+        <f t="shared" ref="I47:J47" si="156">I46/I48</f>
         <v>1.4009120521172638</v>
       </c>
       <c r="J47" s="8">
-        <f t="shared" si="150"/>
+        <f t="shared" si="156"/>
         <v>1.4643137254901961</v>
       </c>
       <c r="K47" s="8">
-        <f t="shared" ref="K47:P47" si="151">K46/K48</f>
+        <f t="shared" ref="K47:P47" si="157">K46/K48</f>
         <v>1.8191698310855047</v>
       </c>
       <c r="L47" s="8">
-        <f t="shared" si="151"/>
+        <f t="shared" si="157"/>
         <v>2.0303308823529411</v>
       </c>
       <c r="M47" s="8">
-        <f t="shared" si="151"/>
+        <f t="shared" si="157"/>
         <v>2.0346189285244174</v>
       </c>
       <c r="N47" s="8">
-        <f t="shared" si="151"/>
+        <f t="shared" si="157"/>
         <v>2.1709537000395724</v>
       </c>
       <c r="O47" s="8">
-        <f t="shared" si="151"/>
+        <f t="shared" si="157"/>
         <v>2.7097925201532971</v>
       </c>
       <c r="P47" s="8">
-        <f t="shared" si="151"/>
+        <f t="shared" si="157"/>
         <v>2.4837855724685638</v>
       </c>
       <c r="Q47" s="8">
@@ -10941,7 +11162,7 @@
         <v>2.3454909819639278</v>
       </c>
       <c r="T47" s="8">
-        <f t="shared" ref="T47:AH47" si="152">T46/T48</f>
+        <f t="shared" ref="T47:AH47" si="158">T46/T48</f>
         <v>2.1979124849458049</v>
       </c>
       <c r="U47" s="8">
@@ -10949,79 +11170,79 @@
         <v>2.4516345123258305</v>
       </c>
       <c r="V47" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>2.6892995848399623</v>
       </c>
       <c r="W47" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>2.9872688287322435</v>
       </c>
       <c r="X47" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>2.9284949116229244</v>
       </c>
       <c r="Y47" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>2.936161670235546</v>
       </c>
       <c r="Z47" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>2.9503280224929709</v>
       </c>
       <c r="AA47" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>3.3021419009370816</v>
       </c>
       <c r="AB47" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>3.2281735404392071</v>
       </c>
       <c r="AC47" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>3.4611982308001608</v>
       </c>
       <c r="AD47" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>3.6500469106017959</v>
       </c>
       <c r="AE47" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>3.7164478971336727</v>
       </c>
       <c r="AF47" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>3.8186327077747988</v>
       </c>
       <c r="AG47" s="8">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>4.2683680322363999</v>
       </c>
       <c r="AH47" s="8">
-        <f t="shared" si="152"/>
-        <v>4.2894613028878439</v>
-      </c>
-      <c r="AI47" s="8" t="e">
-        <f t="shared" ref="AI47:AL47" si="153">AI46/AI48</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ47" s="8" t="e">
-        <f t="shared" si="153"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK47" s="8" t="e">
-        <f t="shared" si="153"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL47" s="8" t="e">
-        <f t="shared" si="153"/>
-        <v>#DIV/0!</v>
+        <f t="shared" si="158"/>
+        <v>4.8053204353083432</v>
+      </c>
+      <c r="AI47" s="8">
+        <f t="shared" ref="AI47:AL47" si="159">AI46/AI48</f>
+        <v>4.9897231358323246</v>
+      </c>
+      <c r="AJ47" s="8">
+        <f t="shared" si="159"/>
+        <v>4.8318866317345162</v>
+      </c>
+      <c r="AK47" s="8">
+        <f t="shared" si="159"/>
+        <v>4.8911595324465935</v>
+      </c>
+      <c r="AL47" s="8">
+        <f t="shared" si="159"/>
+        <v>5.2263283353486489</v>
       </c>
       <c r="AO47" s="11">
-        <f t="shared" ref="AO47:AP47" si="154">AO46/AO48</f>
+        <f t="shared" ref="AO47:AP47" si="160">AO46/AO48</f>
         <v>0.51955307262569828</v>
       </c>
       <c r="AP47" s="11">
-        <f t="shared" si="154"/>
+        <f t="shared" si="160"/>
         <v>0.82238010657193605</v>
       </c>
       <c r="AQ47" s="11">
@@ -11045,79 +11266,79 @@
         <v>3.4296875</v>
       </c>
       <c r="AV47" s="11">
-        <f t="shared" ref="AV47" si="155">AV46/AV48</f>
+        <f t="shared" ref="AV47" si="161">AV46/AV48</f>
         <v>2.6326219512195124</v>
       </c>
       <c r="AW47" s="11">
-        <f t="shared" ref="AW47:BN47" si="156">AW46/AW48</f>
+        <f t="shared" ref="AW47:BN47" si="162">AW46/AW48</f>
         <v>1.7747109287579261</v>
       </c>
       <c r="AX47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>1.4924642787238207</v>
       </c>
       <c r="AY47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>1.7537384062085937</v>
       </c>
       <c r="AZ47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>1.4137064944384643</v>
       </c>
       <c r="BA47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>1.4264361606338916</v>
       </c>
       <c r="BB47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>0.92455430986950926</v>
       </c>
       <c r="BC47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>0.75206535707729028</v>
       </c>
       <c r="BD47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>1.123601687144691</v>
       </c>
       <c r="BE47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>1.1963726141866868</v>
       </c>
       <c r="BF47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>1.4227189965607931</v>
       </c>
       <c r="BG47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>1.867053854276663</v>
       </c>
       <c r="BH47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>1.6561805246776344</v>
       </c>
       <c r="BI47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>2.1080990254284755</v>
       </c>
       <c r="BJ47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>2.6940532991970207</v>
       </c>
       <c r="BK47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>2.724077122031507</v>
       </c>
       <c r="BL47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>2.581227863046045</v>
       </c>
       <c r="BM47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>2.6432908679604714</v>
       </c>
       <c r="BN47" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="162"/>
         <v>2.6900896535013326</v>
       </c>
       <c r="BO47" s="11">
@@ -11141,19 +11362,19 @@
         <v>5.7635038396459715</v>
       </c>
       <c r="BT47" s="11">
-        <f t="shared" ref="BT47:BV47" si="157">+BT46/BT48</f>
+        <f t="shared" ref="BT47:BV47" si="163">+BT46/BT48</f>
         <v>8.0537609674345241</v>
       </c>
       <c r="BU47" s="11">
-        <f t="shared" si="157"/>
+        <f t="shared" si="163"/>
         <v>9.6463099263974534</v>
       </c>
       <c r="BV47" s="11">
-        <f t="shared" si="157"/>
+        <f t="shared" si="163"/>
         <v>9.6839640001338285</v>
       </c>
       <c r="BW47" s="11">
-        <f t="shared" ref="BW47" si="158">+BW46/BW48</f>
+        <f t="shared" ref="BW47" si="164">+BW46/BW48</f>
         <v>11.802216196310804</v>
       </c>
       <c r="BX47" s="11">
@@ -11161,23 +11382,23 @@
         <v>13.64125920964501</v>
       </c>
       <c r="BY47" s="11">
-        <f t="shared" ref="BY47" si="159">+BY46/BY48</f>
+        <f t="shared" ref="BY47" si="165">+BY46/BY48</f>
         <v>16.335130409645007</v>
       </c>
       <c r="BZ47" s="11">
-        <f t="shared" ref="BZ47" si="160">+BZ46/BZ48</f>
+        <f t="shared" ref="BZ47" si="166">+BZ46/BZ48</f>
         <v>20.312424359378433</v>
       </c>
       <c r="CA47" s="11">
-        <f t="shared" ref="CA47" si="161">+CA46/CA48</f>
+        <f t="shared" ref="CA47" si="167">+CA46/CA48</f>
         <v>25.132944882419149</v>
       </c>
       <c r="CB47" s="11">
-        <f t="shared" ref="CB47" si="162">+CB46/CB48</f>
+        <f t="shared" ref="CB47" si="168">+CB46/CB48</f>
         <v>27.812844584594338</v>
       </c>
       <c r="CC47" s="11">
-        <f t="shared" ref="CC47" si="163">+CC46/CC48</f>
+        <f t="shared" ref="CC47" si="169">+CC46/CC48</f>
         <v>30.765732413405047</v>
       </c>
     </row>
@@ -11279,8 +11500,23 @@
         <v>7445</v>
       </c>
       <c r="AH48" s="4">
-        <f>+AG48</f>
-        <v>7445</v>
+        <v>7443</v>
+      </c>
+      <c r="AI48" s="4">
+        <f t="shared" ref="AI48:AL48" si="170">+AH48</f>
+        <v>7443</v>
+      </c>
+      <c r="AJ48" s="4">
+        <f t="shared" si="170"/>
+        <v>7443</v>
+      </c>
+      <c r="AK48" s="4">
+        <f t="shared" si="170"/>
+        <v>7443</v>
+      </c>
+      <c r="AL48" s="4">
+        <f t="shared" si="170"/>
+        <v>7443</v>
       </c>
       <c r="AO48" s="4">
         <v>537</v>
@@ -11396,23 +11632,23 @@
         <v>7465</v>
       </c>
       <c r="BY48" s="5">
-        <f t="shared" ref="BY48:CC48" si="164">+BX48</f>
+        <f t="shared" ref="BY48:CC48" si="171">+BX48</f>
         <v>7465</v>
       </c>
       <c r="BZ48" s="5">
-        <f t="shared" si="164"/>
+        <f t="shared" si="171"/>
         <v>7465</v>
       </c>
       <c r="CA48" s="5">
-        <f t="shared" si="164"/>
+        <f t="shared" si="171"/>
         <v>7465</v>
       </c>
       <c r="CB48" s="5">
-        <f t="shared" si="164"/>
+        <f t="shared" si="171"/>
         <v>7465</v>
       </c>
       <c r="CC48" s="5">
-        <f t="shared" si="164"/>
+        <f t="shared" si="171"/>
         <v>7465</v>
       </c>
     </row>
@@ -11435,43 +11671,43 @@
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
       <c r="G50" s="10">
-        <f t="shared" ref="G50:J50" si="165">G33/C33-1</f>
+        <f t="shared" ref="G50:J50" si="172">G33/C33-1</f>
         <v>0.13653555219364599</v>
       </c>
       <c r="H50" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="172"/>
         <v>0.13658341289150311</v>
       </c>
       <c r="I50" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="172"/>
         <v>0.14556278826338698</v>
       </c>
       <c r="J50" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="172"/>
         <v>0.12800664353293589</v>
       </c>
       <c r="K50" s="10">
-        <f t="shared" ref="K50:O50" si="166">K33/G33-1</f>
+        <f t="shared" ref="K50:O50" si="173">K33/G33-1</f>
         <v>0.12400544546967174</v>
       </c>
       <c r="L50" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="173"/>
         <v>0.16718148810491518</v>
       </c>
       <c r="M50" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="173"/>
         <v>0.19088546871876866</v>
       </c>
       <c r="N50" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="173"/>
         <v>0.21347251071437956</v>
       </c>
       <c r="O50" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="173"/>
         <v>0.21970716477364483</v>
       </c>
       <c r="P50" s="10">
-        <f t="shared" ref="P50" si="167">P33/L33-1</f>
+        <f t="shared" ref="P50" si="174">P33/L33-1</f>
         <v>0.2008543040208004</v>
       </c>
       <c r="Q50" s="10">
@@ -11479,15 +11715,15 @@
         <v>0.18352275451973332</v>
       </c>
       <c r="R50" s="10">
-        <f t="shared" ref="R50:S50" si="168">R33/N33-1</f>
+        <f t="shared" ref="R50:S50" si="175">R33/N33-1</f>
         <v>0.12378661813139202</v>
       </c>
       <c r="S50" s="10">
-        <f t="shared" si="168"/>
+        <f t="shared" si="175"/>
         <v>0.1060308493501334</v>
       </c>
       <c r="T50" s="10">
-        <f t="shared" ref="T50" si="169">T33/P33-1</f>
+        <f t="shared" ref="T50" si="176">T33/P33-1</f>
         <v>1.9699195793380753E-2</v>
       </c>
       <c r="U50" s="10">
@@ -11499,179 +11735,191 @@
         <v>8.3370288248336921E-2</v>
       </c>
       <c r="W50" s="10">
-        <f t="shared" ref="W50:AB50" si="170">W33/S33-1</f>
+        <f t="shared" ref="W50:AB50" si="177">W33/S33-1</f>
         <v>0.12758868361198683</v>
       </c>
       <c r="X50" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="177"/>
         <v>0.17580146738203117</v>
       </c>
       <c r="Y50" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="177"/>
         <v>0.17028964943148495</v>
       </c>
       <c r="Z50" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="177"/>
         <v>0.15195144957198026</v>
       </c>
       <c r="AA50" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="177"/>
         <v>0.16044729904276589</v>
       </c>
       <c r="AB50" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="177"/>
         <v>0.12273460174137374</v>
       </c>
       <c r="AC50" s="10">
-        <f t="shared" ref="AC50:AH50" si="171">AC33/Y33-1</f>
+        <f t="shared" ref="AC50:AH50" si="178">AC33/Y33-1</f>
         <v>0.13269100197225914</v>
       </c>
       <c r="AD50" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>0.18097548163826538</v>
       </c>
       <c r="AE50" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>0.18431043683769155</v>
       </c>
       <c r="AF50" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>0.16717888327205888</v>
       </c>
       <c r="AG50" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>0.18297034224873698</v>
       </c>
       <c r="AH50" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
+        <v>0.17747020577962092</v>
+      </c>
+      <c r="AI50" s="10">
+        <f t="shared" ref="AI50" si="179">AI33/AE33-1</f>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AJ50" s="10">
+        <f t="shared" ref="AJ50" si="180">AJ33/AF33-1</f>
+        <v>0.10000000000000031</v>
+      </c>
+      <c r="AK50" s="10">
+        <f t="shared" ref="AK50" si="181">AK33/AG33-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AI50" s="10"/>
-      <c r="AJ50" s="10"/>
-      <c r="AK50" s="10"/>
-      <c r="AL50" s="10"/>
+      <c r="AL50" s="10">
+        <f t="shared" ref="AL50" si="182">AL33/AH33-1</f>
+        <v>0.10000000000000009</v>
+      </c>
       <c r="AP50" s="18">
-        <f t="shared" ref="AP50:BP50" si="172">AP33/AO33-1</f>
+        <f t="shared" ref="AP50:BP50" si="183">AP33/AO33-1</f>
         <v>0.55790363482671168</v>
       </c>
       <c r="AQ50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.49701573521432452</v>
       </c>
       <c r="AR50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.36027546212395789</v>
       </c>
       <c r="AS50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.23874233946176382</v>
       </c>
       <c r="AT50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.27704882770488282</v>
       </c>
       <c r="AU50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.46050193700522146</v>
       </c>
       <c r="AV50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.30988351977857231</v>
       </c>
       <c r="AW50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.27522451135763348</v>
       </c>
       <c r="AX50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.36336647334990335</v>
       </c>
       <c r="AY50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.16250569706790907</v>
       </c>
       <c r="AZ50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.10193413486670155</v>
       </c>
       <c r="BA50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.12132352941176472</v>
       </c>
       <c r="BB50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.13474352194606021</v>
       </c>
       <c r="BC50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.14440612669711372</v>
       </c>
       <c r="BD50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>8.0168318175648068E-2</v>
       </c>
       <c r="BE50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.11294862772695291</v>
       </c>
       <c r="BF50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.15446456799602548</v>
       </c>
       <c r="BG50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.18187864324556946</v>
       </c>
       <c r="BH50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>-3.2820258192651441E-2</v>
       </c>
       <c r="BI50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>6.9254068484008391E-2</v>
       </c>
       <c r="BJ50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.11937455988733126</v>
       </c>
       <c r="BK50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>5.4044007263057026E-2</v>
       </c>
       <c r="BL50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>5.5966252051598442E-2</v>
       </c>
       <c r="BM50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.11540289534868786</v>
       </c>
       <c r="BN50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>7.7700874091647165E-2</v>
       </c>
       <c r="BO50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>-8.8266723658901425E-2</v>
       </c>
       <c r="BP50" s="18">
-        <f t="shared" si="172"/>
+        <f t="shared" si="183"/>
         <v>0.1318682606657291</v>
       </c>
       <c r="BQ50" s="10">
-        <f t="shared" ref="BQ50:BT50" si="173">+BQ33/BP33-1</f>
+        <f t="shared" ref="BQ50:BT50" si="184">+BQ33/BP33-1</f>
         <v>0.14278613662486661</v>
       </c>
       <c r="BR50" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="184"/>
         <v>0.14029539688292858</v>
       </c>
       <c r="BS50" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="184"/>
         <v>0.13645574247276371</v>
       </c>
       <c r="BT50" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="184"/>
         <v>0.17531727441177503</v>
       </c>
       <c r="BU50" s="10">
@@ -11683,31 +11931,31 @@
         <v>6.8820295556564215E-2</v>
       </c>
       <c r="BW50" s="10">
-        <f t="shared" ref="BW50:CC50" si="174">+BW33/BV33-1</f>
+        <f t="shared" ref="BW50:CC50" si="185">+BW33/BV33-1</f>
         <v>0.1566996201307127</v>
       </c>
       <c r="BX50" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="185"/>
         <v>0.14932156232406713</v>
       </c>
       <c r="BY50" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="185"/>
         <v>0.17049246780536964</v>
       </c>
       <c r="BZ50" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="185"/>
         <v>0.17302583287233553</v>
       </c>
       <c r="CA50" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="185"/>
         <v>0.12728764650206958</v>
       </c>
       <c r="CB50" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="185"/>
         <v>8.7894536853703187E-2</v>
       </c>
       <c r="CC50" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="185"/>
         <v>8.8538753878895093E-2</v>
       </c>
       <c r="CG50" t="s">
@@ -11770,6 +12018,10 @@
       <c r="AE51" s="10">
         <v>0.17</v>
       </c>
+      <c r="AG51" s="10"/>
+      <c r="AH51" s="10">
+        <v>0.17</v>
+      </c>
       <c r="BQ51" s="10"/>
       <c r="BR51" s="10"/>
       <c r="BS51" s="10"/>
@@ -11815,63 +12067,63 @@
       <c r="O52" s="18"/>
       <c r="P52" s="18"/>
       <c r="Q52" s="18">
-        <f t="shared" ref="Q52" si="175">Q78/M78-1</f>
+        <f t="shared" ref="Q52" si="186">Q78/M78-1</f>
         <v>0.12477838234395056</v>
       </c>
       <c r="R52" s="18">
-        <f t="shared" ref="R52" si="176">R78/N78-1</f>
+        <f t="shared" ref="R52" si="187">R78/N78-1</f>
         <v>9.666749733807567E-2</v>
       </c>
       <c r="S52" s="18">
-        <f t="shared" ref="S52:T52" si="177">S78/O78-1</f>
+        <f t="shared" ref="S52:T52" si="188">S78/O78-1</f>
         <v>7.5508960136535519E-2</v>
       </c>
       <c r="T52" s="18">
-        <f t="shared" si="177"/>
+        <f t="shared" si="188"/>
         <v>7.7701324485300205E-2</v>
       </c>
       <c r="U52" s="18">
-        <f t="shared" ref="U52:AD52" si="178">U78/Q78-1</f>
+        <f t="shared" ref="U52:AD52" si="189">U78/Q78-1</f>
         <v>7.6231112077399743E-2</v>
       </c>
       <c r="V52" s="18">
-        <f t="shared" si="178"/>
+        <f t="shared" si="189"/>
         <v>0.11165509833085441</v>
       </c>
       <c r="W52" s="18">
-        <f t="shared" si="178"/>
+        <f t="shared" si="189"/>
         <v>0.11507072905331883</v>
       </c>
       <c r="X52" s="18">
-        <f t="shared" si="178"/>
+        <f t="shared" si="189"/>
         <v>0.16171200726795543</v>
       </c>
       <c r="Y52" s="18">
-        <f t="shared" si="178"/>
+        <f t="shared" si="189"/>
         <v>0.13211787581121692</v>
       </c>
       <c r="Z52" s="18">
-        <f t="shared" si="178"/>
+        <f t="shared" si="189"/>
         <v>0.11839146674595358</v>
       </c>
       <c r="AA52" s="18">
-        <f t="shared" si="178"/>
+        <f t="shared" si="189"/>
         <v>0.13216638204440101</v>
       </c>
       <c r="AB52" s="18">
-        <f t="shared" si="178"/>
+        <f t="shared" si="189"/>
         <v>4.368510231567968E-2</v>
       </c>
       <c r="AC52" s="18">
-        <f t="shared" si="178"/>
+        <f t="shared" si="189"/>
         <v>5.8952111168112831E-2</v>
       </c>
       <c r="AD52" s="18">
-        <f t="shared" si="178"/>
+        <f t="shared" si="189"/>
         <v>0.11765585537684431</v>
       </c>
       <c r="AE52" s="18">
-        <f t="shared" ref="AE52" si="179">AE78/AA78-1</f>
+        <f t="shared" ref="AE52" si="190">AE78/AA78-1</f>
         <v>0.10493993427786452</v>
       </c>
       <c r="BQ52" s="10"/>
@@ -11913,87 +12165,87 @@
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
       <c r="K53" s="12">
-        <f t="shared" ref="K53:N54" si="180">K27/G27-1</f>
+        <f t="shared" ref="K53:N54" si="191">K27/G27-1</f>
         <v>0.11212422135957389</v>
       </c>
       <c r="L53" s="12">
-        <f t="shared" si="180"/>
+        <f t="shared" si="191"/>
         <v>0.12912227295788936</v>
       </c>
       <c r="M53" s="12">
-        <f t="shared" si="180"/>
+        <f t="shared" si="191"/>
         <v>0.15404922081239891</v>
       </c>
       <c r="N53" s="12">
-        <f t="shared" si="180"/>
+        <f t="shared" si="191"/>
         <v>0.25008509189925121</v>
       </c>
       <c r="O53" s="12">
-        <f t="shared" ref="O53:O54" si="181">O27/K27-1</f>
+        <f t="shared" ref="O53:O54" si="192">O27/K27-1</f>
         <v>0.22079714262521311</v>
       </c>
       <c r="P53" s="12">
-        <f t="shared" ref="P53:P54" si="182">P27/L27-1</f>
+        <f t="shared" ref="P53:P54" si="193">P27/L27-1</f>
         <v>0.19343967647719618</v>
       </c>
       <c r="Q53" s="12">
-        <f t="shared" ref="Q53:Q54" si="183">Q27/M27-1</f>
+        <f t="shared" ref="Q53:Q54" si="194">Q27/M27-1</f>
         <v>0.16506788665879579</v>
       </c>
       <c r="R53" s="12">
-        <f t="shared" ref="R53" si="184">R27/N27-1</f>
+        <f t="shared" ref="R53" si="195">R27/N27-1</f>
         <v>0.12994350282485878</v>
       </c>
       <c r="S53" s="12">
-        <f t="shared" ref="S53" si="185">S27/O27-1</f>
+        <f t="shared" ref="S53" si="196">S27/O27-1</f>
         <v>9.4820134317441296E-2</v>
       </c>
       <c r="T53" s="12">
-        <f t="shared" ref="T53" si="186">T27/P27-1</f>
+        <f t="shared" ref="T53" si="197">T27/P27-1</f>
         <v>6.6892570281124497E-2</v>
       </c>
       <c r="U53" s="12">
-        <f t="shared" ref="U53:Z53" si="187">U27/Q27-1</f>
+        <f t="shared" ref="U53:Z53" si="198">U27/Q27-1</f>
         <v>0.10937994806510853</v>
       </c>
       <c r="V53" s="12">
-        <f t="shared" si="187"/>
+        <f t="shared" si="198"/>
         <v>0.10186746987951811</v>
       </c>
       <c r="W53" s="12">
-        <f t="shared" si="187"/>
+        <f t="shared" si="198"/>
         <v>0.5320983905253569</v>
       </c>
       <c r="X53" s="12">
-        <f t="shared" si="187"/>
+        <f t="shared" si="198"/>
         <v>0.52064463004352435</v>
       </c>
       <c r="Y53" s="12">
-        <f t="shared" si="187"/>
+        <f t="shared" si="198"/>
         <v>0.54789906371317643</v>
       </c>
       <c r="Z53" s="12">
-        <f t="shared" si="187"/>
+        <f t="shared" si="198"/>
         <v>0.56508665463889352</v>
       </c>
       <c r="AA53" s="12">
-        <f t="shared" ref="AA53:AB55" si="188">AA27/W27-1</f>
+        <f t="shared" ref="AA53:AB55" si="199">AA27/W27-1</f>
         <v>0.12253230793625614</v>
       </c>
       <c r="AB53" s="12">
-        <f t="shared" si="188"/>
+        <f t="shared" si="199"/>
         <v>0.13858590546917315</v>
       </c>
       <c r="AC53" s="12">
-        <f t="shared" ref="AC53:AD53" si="189">AC27/Y27-1</f>
+        <f t="shared" ref="AC53:AD53" si="200">AC27/Y27-1</f>
         <v>0.10441485634197623</v>
       </c>
       <c r="AD53" s="12">
-        <f t="shared" si="189"/>
+        <f t="shared" si="200"/>
         <v>0.15667027631257202</v>
       </c>
       <c r="AE53" s="12">
-        <f t="shared" ref="AE53:AE55" si="190">AE27/AA27-1</f>
+        <f t="shared" ref="AE53:AE55" si="201">AE27/AA27-1</f>
         <v>0.16608397782250939</v>
       </c>
       <c r="AF53" s="12"/>
@@ -12008,11 +12260,11 @@
       <c r="BS53" s="10"/>
       <c r="BT53" s="10"/>
       <c r="BU53" s="10">
-        <f t="shared" ref="BU53:BV53" si="191">BU27/BT27-1</f>
+        <f t="shared" ref="BU53:BV53" si="202">BU27/BT27-1</f>
         <v>0.17525734953167027</v>
       </c>
       <c r="BV53" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="202"/>
         <v>9.3270626854365268E-2</v>
       </c>
       <c r="BW53" s="10">
@@ -12046,87 +12298,87 @@
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
       <c r="K54" s="12">
-        <f t="shared" si="180"/>
+        <f t="shared" si="191"/>
         <v>0.19741816505301979</v>
       </c>
       <c r="L54" s="12">
-        <f t="shared" si="180"/>
+        <f t="shared" si="191"/>
         <v>0.23017945909512183</v>
       </c>
       <c r="M54" s="12">
-        <f t="shared" si="180"/>
+        <f t="shared" si="191"/>
         <v>0.23100724696685937</v>
       </c>
       <c r="N54" s="12">
-        <f t="shared" si="180"/>
+        <f t="shared" si="191"/>
         <v>0.29945404233041661</v>
       </c>
       <c r="O54" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="192"/>
         <v>0.30232558139534893</v>
       </c>
       <c r="P54" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="193"/>
         <v>0.25518800082186144</v>
       </c>
       <c r="Q54" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="194"/>
         <v>0.25592009525069459</v>
       </c>
       <c r="R54" s="12">
-        <f t="shared" ref="R54:U54" si="192">R28/N28-1</f>
+        <f t="shared" ref="R54:U54" si="203">R28/N28-1</f>
         <v>0.19735251798561149</v>
       </c>
       <c r="S54" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="203"/>
         <v>0.20180936613055822</v>
       </c>
       <c r="T54" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="203"/>
         <v>0.17356905112675292</v>
       </c>
       <c r="U54" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="203"/>
         <v>0.16295359983146374</v>
       </c>
       <c r="V54" s="12">
-        <f t="shared" ref="V54:Z54" si="193">V28/R28-1</f>
+        <f t="shared" ref="V54:Z54" si="204">V28/R28-1</f>
         <v>0.15328782926360307</v>
       </c>
       <c r="W54" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="204"/>
         <v>-1.5350553505535047E-2</v>
       </c>
       <c r="X54" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="204"/>
         <v>7.904035707644308E-4</v>
       </c>
       <c r="Y54" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="204"/>
         <v>2.7172682396630066E-3</v>
       </c>
       <c r="Z54" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="204"/>
         <v>-8.6691951819281021E-3</v>
       </c>
       <c r="AA54" s="12">
-        <f t="shared" si="188"/>
+        <f t="shared" si="199"/>
         <v>0.20381751861290165</v>
       </c>
       <c r="AB54" s="12">
-        <f t="shared" si="188"/>
+        <f t="shared" si="199"/>
         <v>0.18671312427409981</v>
       </c>
       <c r="AC54" s="12">
-        <f t="shared" ref="AC54:AD54" si="194">AC28/Y28-1</f>
+        <f t="shared" ref="AC54:AD54" si="205">AC28/Y28-1</f>
         <v>0.20821101124610442</v>
       </c>
       <c r="AD54" s="12">
-        <f t="shared" si="194"/>
+        <f t="shared" si="205"/>
         <v>0.25616985495059907</v>
       </c>
       <c r="AE54" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="201"/>
         <v>0.28245890752116876</v>
       </c>
       <c r="AF54" s="12"/>
@@ -12141,11 +12393,11 @@
       <c r="BS54" s="10"/>
       <c r="BT54" s="10"/>
       <c r="BU54" s="10">
-        <f t="shared" ref="BU54:BV54" si="195">BU28/BT28-1</f>
+        <f t="shared" ref="BU54:BV54" si="206">BU28/BT28-1</f>
         <v>0.24883488681757648</v>
       </c>
       <c r="BV54" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="206"/>
         <v>0.1716246834599493</v>
       </c>
       <c r="BW54" s="10">
@@ -12181,87 +12433,87 @@
       <c r="I55" s="10"/>
       <c r="J55" s="10"/>
       <c r="K55" s="12">
-        <f t="shared" ref="K55:Z55" si="196">K29/G29-1</f>
+        <f t="shared" ref="K55:Z55" si="207">K29/G29-1</f>
         <v>6.4313302793496785E-2</v>
       </c>
       <c r="L55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>0.14465218378623868</v>
       </c>
       <c r="M55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>0.18541420387378382</v>
       </c>
       <c r="N55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>9.1092176607281194E-2</v>
       </c>
       <c r="O55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>0.12802768166089962</v>
       </c>
       <c r="P55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>0.15493982277476515</v>
       </c>
       <c r="Q55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>0.11874808223381406</v>
       </c>
       <c r="R55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>2.6622178049126699E-2</v>
       </c>
       <c r="S55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>-2.5437677689660321E-3</v>
       </c>
       <c r="T55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>-0.18482679645004296</v>
       </c>
       <c r="U55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>-9.0784421283598427E-2</v>
       </c>
       <c r="V55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>-3.8448240094046016E-2</v>
       </c>
       <c r="W55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>-0.15406540654065404</v>
       </c>
       <c r="X55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>2.8376764767858331E-2</v>
       </c>
       <c r="Y55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>-4.9472096530920107E-2</v>
       </c>
       <c r="Z55" s="12">
-        <f t="shared" si="196"/>
+        <f t="shared" si="207"/>
         <v>-0.11434735706580368</v>
       </c>
       <c r="AA55" s="12">
-        <f t="shared" si="188"/>
+        <f t="shared" si="199"/>
         <v>0.16829225039900697</v>
       </c>
       <c r="AB55" s="12">
-        <f t="shared" si="188"/>
+        <f t="shared" si="199"/>
         <v>6.8301345536503355E-4</v>
       </c>
       <c r="AC55" s="12">
-        <f t="shared" ref="AC55:AD55" si="197">AC29/Y29-1</f>
+        <f t="shared" ref="AC55:AD55" si="208">AC29/Y29-1</f>
         <v>6.0853697238971716E-2</v>
       </c>
       <c r="AD55" s="12">
-        <f t="shared" si="197"/>
+        <f t="shared" si="208"/>
         <v>9.2245229395046646E-2</v>
       </c>
       <c r="AE55" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="201"/>
         <v>4.4019429265330867E-2</v>
       </c>
       <c r="AF55" s="12"/>
@@ -12276,11 +12528,11 @@
       <c r="BS55" s="10"/>
       <c r="BT55" s="10"/>
       <c r="BU55" s="10">
-        <f t="shared" ref="BU55:BV55" si="198">BU29/BT29-1</f>
+        <f t="shared" ref="BU55:BV55" si="209">BU29/BT29-1</f>
         <v>0.10690847244560286</v>
       </c>
       <c r="BV55" s="10">
-        <f t="shared" si="198"/>
+        <f t="shared" si="209"/>
         <v>-8.5877480125592931E-2</v>
       </c>
       <c r="BW55" s="10">
@@ -12301,129 +12553,129 @@
         <v>22</v>
       </c>
       <c r="C56" s="9">
-        <f t="shared" ref="C56:D56" si="199">C37/C33</f>
+        <f t="shared" ref="C56:D56" si="210">C37/C33</f>
         <v>0.65943474075092834</v>
       </c>
       <c r="D56" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="210"/>
         <v>0.61741246034923469</v>
       </c>
       <c r="E56" s="9">
-        <f t="shared" ref="E56" si="200">E37/E33</f>
+        <f t="shared" ref="E56" si="211">E37/E33</f>
         <v>0.66733178502502366</v>
       </c>
       <c r="F56" s="9"/>
       <c r="G56" s="9">
-        <f t="shared" ref="G56:AH56" si="201">G37/G33</f>
+        <f t="shared" ref="G56:AH56" si="212">G37/G33</f>
         <v>0.6851913477537438</v>
       </c>
       <c r="H56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.66514929821709212</v>
       </c>
       <c r="I56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.68661660146769077</v>
       </c>
       <c r="J56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.67557121447164303</v>
       </c>
       <c r="K56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.70388114334930285</v>
       </c>
       <c r="L56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.67048936762930633</v>
       </c>
       <c r="M56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.68721526878626582</v>
       </c>
       <c r="N56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.69684954064829263</v>
       </c>
       <c r="O56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.6988768012004325</v>
       </c>
       <c r="P56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.67213114754098358</v>
       </c>
       <c r="Q56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.68365072933549431</v>
       </c>
       <c r="R56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.68323532247180174</v>
       </c>
       <c r="S56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.69171222217788597</v>
       </c>
       <c r="T56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.66845507801391546</v>
       </c>
       <c r="U56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.69487485101311086</v>
       </c>
       <c r="V56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.70109807969531401</v>
       </c>
       <c r="W56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.71155581506449384</v>
       </c>
       <c r="X56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.68360206385037081</v>
       </c>
       <c r="Y56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.70084710142584628</v>
       </c>
       <c r="Z56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.69589197707293715</v>
       </c>
       <c r="AA56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.69354273080734929</v>
       </c>
       <c r="AB56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.68693991268382348</v>
       </c>
       <c r="AC56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.6871663859789342</v>
       </c>
       <c r="AD56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.68584921704320978</v>
       </c>
       <c r="AE56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.69045871795862135</v>
       </c>
       <c r="AF56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.68036125158416694</v>
       </c>
       <c r="AG56" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="212"/>
         <v>0.67632652076345823</v>
       </c>
       <c r="AH56" s="9">
-        <f t="shared" si="201"/>
-        <v>0.7</v>
+        <f t="shared" si="212"/>
+        <v>0.67196995789216396</v>
       </c>
       <c r="AI56" s="9"/>
       <c r="AJ56" s="9"/>
@@ -12432,167 +12684,167 @@
       <c r="AM56" s="9"/>
       <c r="AN56" s="9"/>
       <c r="AO56" s="9">
-        <f t="shared" ref="AO56:CC56" si="202">AO37/AO33</f>
+        <f t="shared" ref="AO56:CC56" si="213">AO37/AO33</f>
         <v>0.78613693998309386</v>
       </c>
       <c r="AP56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.8035811177428106</v>
       </c>
       <c r="AQ56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.8307357738310982</v>
       </c>
       <c r="AR56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.83133493205435649</v>
       </c>
       <c r="AS56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.83587868358786832</v>
       </c>
       <c r="AT56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.85228229745662798</v>
       </c>
       <c r="AU56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.86299158113251062</v>
       </c>
       <c r="AV56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.90447261841873572</v>
       </c>
       <c r="AW56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.91735708367854185</v>
       </c>
       <c r="AX56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.85749734136830913</v>
       </c>
       <c r="AY56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.86922808851716327</v>
       </c>
       <c r="AZ56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.86341714104996836</v>
       </c>
       <c r="BA56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.8169927727833598</v>
       </c>
       <c r="BB56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.82334482865753256</v>
       </c>
       <c r="BC56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.81767340844305691</v>
       </c>
       <c r="BD56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.84417412285111093</v>
       </c>
       <c r="BE56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.82724357526760306</v>
       </c>
       <c r="BF56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.79083369195258402</v>
       </c>
       <c r="BG56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.80804369414101296</v>
       </c>
       <c r="BH56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.79199822030562828</v>
       </c>
       <c r="BI56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.80162921707957235</v>
       </c>
       <c r="BJ56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.77729007906438097</v>
       </c>
       <c r="BK56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.76221803236439101</v>
       </c>
       <c r="BL56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.7398938971598864</v>
       </c>
       <c r="BM56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.68981838701876019</v>
       </c>
       <c r="BN56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.64695447745244705</v>
       </c>
       <c r="BO56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.61579934364744493</v>
       </c>
       <c r="BP56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.64522475691460168</v>
       </c>
       <c r="BQ56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.65247372236317502</v>
       </c>
       <c r="BR56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.65901957200638894</v>
       </c>
       <c r="BS56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.67781001992797962</v>
       </c>
       <c r="BT56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.68925800771024703</v>
       </c>
       <c r="BU56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.68401674484289099</v>
       </c>
       <c r="BV56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.68920085883491022</v>
       </c>
       <c r="BW56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.69764443827971379</v>
       </c>
       <c r="BX56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.68823742386165188</v>
       </c>
       <c r="BY56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.67</v>
       </c>
       <c r="BZ56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.67</v>
       </c>
       <c r="CA56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.67</v>
       </c>
       <c r="CB56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.67</v>
       </c>
       <c r="CC56" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="213"/>
         <v>0.67</v>
       </c>
     </row>
@@ -12601,129 +12853,129 @@
         <v>455</v>
       </c>
       <c r="C57" s="9">
-        <f t="shared" ref="C57:D57" si="203">+C42/C33</f>
+        <f t="shared" ref="C57:D57" si="214">+C42/C33</f>
         <v>0.34228441754916794</v>
       </c>
       <c r="D57" s="9">
-        <f t="shared" si="203"/>
+        <f t="shared" si="214"/>
         <v>0.3159126605278556</v>
       </c>
       <c r="E57" s="9">
-        <f t="shared" ref="E57" si="204">+E42/E33</f>
+        <f t="shared" ref="E57" si="215">+E42/E33</f>
         <v>0.3382617513329626</v>
       </c>
       <c r="F57" s="9"/>
       <c r="G57" s="9">
-        <f t="shared" ref="G57:AB57" si="205">+G42/G33</f>
+        <f t="shared" ref="G57:AB57" si="216">+G42/G33</f>
         <v>0.38378460142187265</v>
       </c>
       <c r="H57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.37638866309001245</v>
       </c>
       <c r="I57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.37049199051997372</v>
       </c>
       <c r="J57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.35250966266137301</v>
       </c>
       <c r="K57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.42730257845723207</v>
       </c>
       <c r="L57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.41547497446373849</v>
       </c>
       <c r="M57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.40876612477820939</v>
       </c>
       <c r="N57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.41374154966198645</v>
       </c>
       <c r="O57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.44658737339188381</v>
       </c>
       <c r="P57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.43007655428394681</v>
       </c>
       <c r="Q57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.41256077795786061</v>
       </c>
       <c r="R57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.3959124650535043</v>
       </c>
       <c r="S57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.42931247755476637</v>
       </c>
       <c r="T57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.3867328947617874</v>
       </c>
       <c r="U57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.42287681858599618</v>
       </c>
       <c r="V57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.4316503230169606</v>
       </c>
       <c r="W57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.47587451563246458</v>
       </c>
       <c r="X57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.43585940019348596</v>
       </c>
       <c r="Y57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.44587603866921011</v>
       </c>
       <c r="Z57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.43142737960974553</v>
       </c>
       <c r="AA57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.46583822520393381</v>
       </c>
       <c r="AB57" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="216"/>
         <v>0.45457548253676472</v>
       </c>
       <c r="AC57" s="9">
-        <f t="shared" ref="AC57:AH57" si="206">+AC42/AC33</f>
+        <f t="shared" ref="AC57:AH57" si="217">+AC42/AC33</f>
         <v>0.45671224274255701</v>
       </c>
       <c r="AD57" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="217"/>
         <v>0.44901296424693554</v>
       </c>
       <c r="AE57" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="217"/>
         <v>0.48872838695557014</v>
       </c>
       <c r="AF57" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="217"/>
         <v>0.47094360980891564</v>
       </c>
       <c r="AG57" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="217"/>
         <v>0.46326279468185216</v>
       </c>
       <c r="AH57" s="9">
-        <f t="shared" si="206"/>
-        <v>0.46316374720372572</v>
+        <f t="shared" si="217"/>
+        <v>0.45110935816103193</v>
       </c>
       <c r="AI57" s="9"/>
       <c r="AJ57" s="9"/>
@@ -12751,91 +13003,91 @@
       <c r="BF57" s="9"/>
       <c r="BG57" s="9"/>
       <c r="BH57" s="9">
-        <f t="shared" ref="BH57:CC57" si="207">BH42/BH33</f>
+        <f t="shared" ref="BH57:CC57" si="218">BH42/BH33</f>
         <v>0.35410784263394768</v>
       </c>
       <c r="BI57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.38661097240893672</v>
       </c>
       <c r="BJ57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.38833049769097694</v>
       </c>
       <c r="BK57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.37920323372624554</v>
       </c>
       <c r="BL57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.34379375457616668</v>
       </c>
       <c r="BM57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.32114518673776099</v>
       </c>
       <c r="BN57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.30104723231459712</v>
       </c>
       <c r="BO57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.24955461790904829</v>
       </c>
       <c r="BP57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.30372472067183731</v>
       </c>
       <c r="BQ57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.31766944545125048</v>
       </c>
       <c r="BR57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.3413698020549415</v>
       </c>
       <c r="BS57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.37030381428521486</v>
       </c>
       <c r="BT57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.41594878872971303</v>
       </c>
       <c r="BU57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.4205527815604983</v>
       </c>
       <c r="BV57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.41772880636104098</v>
       </c>
       <c r="BW57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.44644299573273716</v>
       </c>
       <c r="BX57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.45621956240859851</v>
       </c>
       <c r="BY57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.46583089693458635</v>
       </c>
       <c r="BZ57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.49072502560115139</v>
       </c>
       <c r="CA57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.50619688887411651</v>
       </c>
       <c r="CB57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.51491400706211232</v>
       </c>
       <c r="CC57" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="218"/>
         <v>0.52325412424976847</v>
       </c>
     </row>
@@ -12844,129 +13096,129 @@
         <v>89</v>
       </c>
       <c r="C58" s="9">
-        <f t="shared" ref="C58:D58" si="208">+C45/C44</f>
+        <f t="shared" ref="C58:D58" si="219">+C45/C44</f>
         <v>0.13667938557871051</v>
       </c>
       <c r="D58" s="9">
-        <f t="shared" si="208"/>
+        <f t="shared" si="219"/>
         <v>0.18921521425132404</v>
       </c>
       <c r="E58" s="9">
-        <f t="shared" ref="E58" si="209">+E45/E44</f>
+        <f t="shared" ref="E58" si="220">+E45/E44</f>
         <v>0.15992752241083349</v>
       </c>
       <c r="F58" s="9"/>
       <c r="G58" s="9">
-        <f t="shared" ref="G58:AB58" si="210">+G45/G44</f>
+        <f t="shared" ref="G58:AB58" si="221">+G45/G44</f>
         <v>0.15828472331704241</v>
       </c>
       <c r="H58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.17294994675186368</v>
       </c>
       <c r="I58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.16281242700303666</v>
       </c>
       <c r="J58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.16540008940545373</v>
       </c>
       <c r="K58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.13836516993301909</v>
       </c>
       <c r="L58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.15673228990565524</v>
       </c>
       <c r="M58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.10321420283128337</v>
       </c>
       <c r="N58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.15186807523834064</v>
       </c>
       <c r="O58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>9.2574546871954783E-4</v>
       </c>
       <c r="P58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.16655562958027981</v>
       </c>
       <c r="Q58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.17147102526002972</v>
       </c>
       <c r="R58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.18289647093278666</v>
       </c>
       <c r="S58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.18616725384758021</v>
       </c>
       <c r="T58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.19243817296818919</v>
       </c>
       <c r="U58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.19291668504388479</v>
       </c>
       <c r="V58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.18789177821814212</v>
       </c>
       <c r="W58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.18300102624248643</v>
       </c>
       <c r="X58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.17552589911784663</v>
       </c>
       <c r="Y58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.17914468514984846</v>
       </c>
       <c r="Z58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.1913394495412844</v>
       </c>
       <c r="AA58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.18507383791998414</v>
       </c>
       <c r="AB58" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="221"/>
         <v>0.17902264600715137</v>
       </c>
       <c r="AC58" s="9">
-        <f t="shared" ref="AC58:AH58" si="211">+AC45/AC44</f>
+        <f t="shared" ref="AC58:AH58" si="222">+AC45/AC44</f>
         <v>0.17697676642126398</v>
       </c>
       <c r="AD58" s="9">
-        <f t="shared" si="211"/>
+        <f t="shared" si="222"/>
         <v>0.16504169732646554</v>
       </c>
       <c r="AE58" s="9">
-        <f t="shared" si="211"/>
+        <f t="shared" si="222"/>
         <v>0.19107314655549401</v>
       </c>
       <c r="AF58" s="9">
-        <f t="shared" si="211"/>
+        <f t="shared" si="222"/>
         <v>0.25572828216851728</v>
       </c>
       <c r="AG58" s="9">
-        <f t="shared" si="211"/>
+        <f t="shared" si="222"/>
         <v>0.19222165734621249</v>
       </c>
       <c r="AH58" s="9">
-        <f t="shared" si="211"/>
-        <v>0.18</v>
+        <f t="shared" si="222"/>
+        <v>0.18800372329557063</v>
       </c>
       <c r="AI58" s="9"/>
       <c r="AJ58" s="9"/>
@@ -12975,167 +13227,167 @@
       <c r="AM58" s="9"/>
       <c r="AN58" s="9"/>
       <c r="AO58" s="9">
-        <f t="shared" ref="AO58:CC58" si="212">+AO45/AO44</f>
+        <f t="shared" ref="AO58:CC58" si="223">+AO45/AO44</f>
         <v>0.31951219512195123</v>
       </c>
       <c r="AP58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.30998509687034276</v>
       </c>
       <c r="AQ58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.31988472622478387</v>
       </c>
       <c r="AR58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.31977159172019987</v>
       </c>
       <c r="AS58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.31788079470198677</v>
       </c>
       <c r="AT58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.32263895164934481</v>
       </c>
       <c r="AU58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.35039952648712636</v>
       </c>
       <c r="AV58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.35001881821603315</v>
       </c>
       <c r="AW58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.35815459328207205</v>
       </c>
       <c r="AX58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.35001278663370555</v>
       </c>
       <c r="AY58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.34379205326156242</v>
       </c>
       <c r="AZ58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.32557343375556319</v>
       </c>
       <c r="BA58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.31744937526928046</v>
       </c>
       <c r="BB58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.31992699743139108</v>
       </c>
       <c r="BC58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.32959659602323871</v>
       </c>
       <c r="BD58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.26305027664180902</v>
       </c>
       <c r="BE58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.31009747015660938</v>
       </c>
       <c r="BF58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.30028356798169248</v>
       </c>
       <c r="BG58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.25753758293440832</v>
       </c>
       <c r="BH58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.26063222668850183</v>
       </c>
       <c r="BI58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.24940172303765157</v>
       </c>
       <c r="BJ58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.17530547540166008</v>
       </c>
       <c r="BK58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.18583977512297961</v>
       </c>
       <c r="BL58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.19181576223569421</v>
       </c>
       <c r="BM58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.20560346369914481</v>
       </c>
       <c r="BN58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.22140402552773686</v>
       </c>
       <c r="BO58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.1415560136139207</v>
       </c>
       <c r="BP58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.14605886052901645</v>
       </c>
       <c r="BQ58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.5456763722103416</v>
       </c>
       <c r="BR58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.10181285478850027</v>
       </c>
       <c r="BS58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.16507655177615205</v>
       </c>
       <c r="BT58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.13826615285083402</v>
       </c>
       <c r="BU58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.13113383343685794</v>
       </c>
       <c r="BV58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.18978625253328257</v>
       </c>
       <c r="BW58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.18231326597827197</v>
       </c>
       <c r="BX58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.17629644009803683</v>
       </c>
       <c r="BY58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.18</v>
       </c>
       <c r="BZ58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.18</v>
       </c>
       <c r="CA58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.15</v>
       </c>
       <c r="CB58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.15</v>
       </c>
       <c r="CC58" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="223"/>
         <v>0.15</v>
       </c>
     </row>
@@ -13144,129 +13396,129 @@
         <v>156</v>
       </c>
       <c r="C59" s="9">
-        <f t="shared" ref="C59:D59" si="213">(C31-C34)/C31</f>
+        <f t="shared" ref="C59:D59" si="224">(C31-C34)/C31</f>
         <v>0.78906295161570028</v>
       </c>
       <c r="D59" s="9">
-        <f t="shared" si="213"/>
+        <f t="shared" si="224"/>
         <v>0.63715395523768414</v>
       </c>
       <c r="E59" s="9">
-        <f t="shared" ref="E59" si="214">(E31-E34)/E31</f>
+        <f t="shared" ref="E59" si="225">(E31-E34)/E31</f>
         <v>0.77725271879854996</v>
       </c>
       <c r="F59" s="9"/>
       <c r="G59" s="9">
-        <f t="shared" ref="G59:AB59" si="215">(G31-G34)/G31</f>
+        <f t="shared" ref="G59:AB59" si="226">(G31-G34)/G31</f>
         <v>0.79039827498731607</v>
       </c>
       <c r="H59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.72796494111202414</v>
       </c>
       <c r="I59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.78728498519311951</v>
       </c>
       <c r="J59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.75918884664131814</v>
       </c>
       <c r="K59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.77238499019173579</v>
       </c>
       <c r="L59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.68869475847893113</v>
       </c>
       <c r="M59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.74651810584958223</v>
       </c>
       <c r="N59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.7736297391488014</v>
       </c>
       <c r="O59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.77199206301485179</v>
       </c>
       <c r="P59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.69531738774724483</v>
       </c>
       <c r="Q59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.73603593228146957</v>
       </c>
       <c r="R59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.75735130318556476</v>
       </c>
       <c r="S59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.72670097198399086</v>
       </c>
       <c r="T59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.65550644790216139</v>
       </c>
       <c r="U59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.74717731588401337</v>
       </c>
       <c r="V59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.77030795704028954</v>
       </c>
       <c r="W59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.77270679111683294</v>
       </c>
       <c r="X59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.68512750118789922</v>
       </c>
       <c r="Y59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.74596018735363001</v>
       </c>
       <c r="Z59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.89120072633729286</v>
       </c>
       <c r="AA59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.78431115767417492</v>
       </c>
       <c r="AB59" s="9">
-        <f t="shared" si="215"/>
+        <f t="shared" si="226"/>
         <v>0.76225414637153954</v>
       </c>
       <c r="AC59" s="9">
-        <f t="shared" ref="AC59:AH59" si="216">(AC31-AC34)/AC31</f>
+        <f t="shared" ref="AC59:AH59" si="227">(AC31-AC34)/AC31</f>
         <v>0.80174946145309745</v>
       </c>
       <c r="AD59" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="227"/>
         <v>0.8066059757236228</v>
       </c>
       <c r="AE59" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="227"/>
         <v>0.81648034166561989</v>
       </c>
       <c r="AF59" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="227"/>
         <v>0.78694304297611084</v>
       </c>
       <c r="AG59" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="227"/>
         <v>0.81887467691695937</v>
       </c>
       <c r="AH59" s="9">
-        <f t="shared" si="216"/>
-        <v>1</v>
+        <f t="shared" si="227"/>
+        <v>0.82952303585934783</v>
       </c>
       <c r="AI59" s="9"/>
       <c r="AJ59" s="9"/>
@@ -13301,63 +13553,63 @@
       <c r="BM59" s="9"/>
       <c r="BN59" s="9"/>
       <c r="BO59" s="9">
-        <f t="shared" ref="BO59:CC59" si="217">(BO31-BO34)/BO31</f>
+        <f t="shared" ref="BO59:CC59" si="228">(BO31-BO34)/BO31</f>
         <v>0.70927774706513613</v>
       </c>
       <c r="BP59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.76218833743398473</v>
       </c>
       <c r="BQ59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.76091911251686128</v>
       </c>
       <c r="BR59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.75369689264254036</v>
       </c>
       <c r="BS59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.76459781602269217</v>
       </c>
       <c r="BT59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.74366153586402906</v>
       </c>
       <c r="BU59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.73788703734257277</v>
       </c>
       <c r="BV59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.72481800336944935</v>
       </c>
       <c r="BW59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.76422274713229277</v>
       </c>
       <c r="BX59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.78886873299346327</v>
       </c>
       <c r="BY59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.75</v>
       </c>
       <c r="BZ59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.75</v>
       </c>
       <c r="CA59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.75</v>
       </c>
       <c r="CB59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.75</v>
       </c>
       <c r="CC59" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="228"/>
         <v>0.75</v>
       </c>
       <c r="CF59" s="1"/>
@@ -13367,129 +13619,129 @@
         <v>157</v>
       </c>
       <c r="C60" s="9">
-        <f t="shared" ref="C60:D60" si="218">(C32-C35)/C32</f>
+        <f t="shared" ref="C60:D60" si="229">(C32-C35)/C32</f>
         <v>0.46915570640644888</v>
       </c>
       <c r="D60" s="9">
-        <f t="shared" si="218"/>
+        <f t="shared" si="229"/>
         <v>0.59771105094757571</v>
       </c>
       <c r="E60" s="9">
-        <f t="shared" ref="E60" si="219">(E32-E35)/E32</f>
+        <f t="shared" ref="E60" si="230">(E32-E35)/E32</f>
         <v>0.55504860146796275</v>
       </c>
       <c r="F60" s="9"/>
       <c r="G60" s="9">
-        <f t="shared" ref="G60:AB60" si="220">(G32-G35)/G32</f>
+        <f t="shared" ref="G60:AB60" si="231">(G32-G35)/G32</f>
         <v>0.58922890032972752</v>
       </c>
       <c r="H60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.60366736368023166</v>
       </c>
       <c r="I60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.60318537859007837</v>
       </c>
       <c r="J60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.59926581514633415</v>
       </c>
       <c r="K60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.65317783710364852</v>
       </c>
       <c r="L60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.65548780487804881</v>
       </c>
       <c r="M60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.64692143518704948</v>
       </c>
       <c r="N60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.64341882854413168</v>
       </c>
       <c r="O60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.65648748518441047</v>
       </c>
       <c r="P60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.65656402468577335</v>
       </c>
       <c r="Q60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.65521660311308372</v>
       </c>
       <c r="R60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.64398832168450859</v>
       </c>
       <c r="S60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.67569296995433525</v>
       </c>
       <c r="T60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.67435826662986476</v>
       </c>
       <c r="U60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.67299900721779493</v>
       </c>
       <c r="V60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.67144600366076879</v>
       </c>
       <c r="W60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.68837538431506518</v>
       </c>
       <c r="X60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.68293135866663568</v>
       </c>
       <c r="Y60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.68363928714993971</v>
       </c>
       <c r="Z60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.64577751892836344</v>
       </c>
       <c r="AA60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.66599089698487468</v>
       </c>
       <c r="AB60" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="231"/>
         <v>0.66407054462396797</v>
       </c>
       <c r="AC60" s="9">
-        <f t="shared" ref="AC60:AH60" si="221">(AC32-AC35)/AC32</f>
+        <f t="shared" ref="AC60:AH60" si="232">(AC32-AC35)/AC32</f>
         <v>0.65510438928160453</v>
       </c>
       <c r="AD60" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="232"/>
         <v>0.65095691762920493</v>
       </c>
       <c r="AE60" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="232"/>
         <v>0.65796505319751908</v>
       </c>
       <c r="AF60" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="232"/>
         <v>0.65331214711054886</v>
       </c>
       <c r="AG60" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="232"/>
         <v>0.64460079354543709</v>
       </c>
       <c r="AH60" s="9">
-        <f t="shared" si="221"/>
-        <v>1</v>
+        <f t="shared" si="232"/>
+        <v>0.63465845849422176</v>
       </c>
       <c r="AI60" s="9"/>
       <c r="AJ60" s="9"/>
@@ -13524,63 +13776,63 @@
       <c r="BM60" s="9"/>
       <c r="BN60" s="9"/>
       <c r="BO60" s="9">
-        <f t="shared" ref="BO60:CC60" si="222">(BO32-BO35)/BO32</f>
+        <f t="shared" ref="BO60:CC60" si="233">(BO32-BO35)/BO32</f>
         <v>0.37442270551683599</v>
       </c>
       <c r="BP60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.41739926739926742</v>
       </c>
       <c r="BQ60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.4999672938970412</v>
       </c>
       <c r="BR60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.55437146585471941</v>
       </c>
       <c r="BS60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.59904766985888447</v>
       </c>
       <c r="BT60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.64940111736450412</v>
       </c>
       <c r="BU60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.65280632159186858</v>
       </c>
       <c r="BV60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.67354771220519505</v>
       </c>
       <c r="BW60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.67373259624394921</v>
       </c>
       <c r="BX60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.65868912378660838</v>
       </c>
       <c r="BY60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.65</v>
       </c>
       <c r="BZ60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.65</v>
       </c>
       <c r="CA60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.65</v>
       </c>
       <c r="CB60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.65</v>
       </c>
       <c r="CC60" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="233"/>
         <v>0.65000000000000013</v>
       </c>
       <c r="CF60" s="1"/>
@@ -13685,208 +13937,211 @@
         <v>82</v>
       </c>
       <c r="G63" s="5">
-        <f t="shared" ref="G63:H63" si="223">+G64-G75</f>
+        <f t="shared" ref="G63:H63" si="234">+G64-G75</f>
         <v>69825</v>
       </c>
       <c r="H63" s="5">
-        <f t="shared" si="223"/>
+        <f t="shared" si="234"/>
         <v>64290</v>
       </c>
       <c r="I63" s="5">
-        <f t="shared" ref="I63:J63" si="224">+I64-I75</f>
+        <f t="shared" ref="I63:J63" si="235">+I64-I75</f>
         <v>73676</v>
       </c>
       <c r="J63" s="5">
-        <f t="shared" si="224"/>
+        <f t="shared" si="235"/>
         <v>76165</v>
       </c>
       <c r="K63" s="5">
-        <f t="shared" ref="K63:L63" si="225">+K64-K75</f>
+        <f t="shared" ref="K63:L63" si="236">+K64-K75</f>
         <v>77528</v>
       </c>
       <c r="L63" s="5">
-        <f t="shared" si="225"/>
+        <f t="shared" si="236"/>
         <v>75239</v>
       </c>
       <c r="M63" s="5">
-        <f t="shared" ref="M63:Y63" si="226">+M64-M75</f>
+        <f t="shared" ref="M63:Y63" si="237">+M64-M75</f>
         <v>72744</v>
       </c>
       <c r="N63" s="5">
-        <f t="shared" si="226"/>
+        <f t="shared" si="237"/>
         <v>78172</v>
       </c>
       <c r="O63" s="5">
-        <f t="shared" si="226"/>
+        <f t="shared" si="237"/>
         <v>83720</v>
       </c>
       <c r="P63" s="5">
-        <f t="shared" si="226"/>
+        <f t="shared" si="237"/>
         <v>79105</v>
       </c>
       <c r="Q63" s="5">
-        <f t="shared" si="226"/>
+        <f t="shared" si="237"/>
         <v>61674</v>
       </c>
       <c r="R63" s="5">
-        <f t="shared" si="226"/>
+        <f t="shared" si="237"/>
         <v>61867</v>
       </c>
       <c r="S63" s="5">
-        <f t="shared" si="226"/>
+        <f t="shared" si="237"/>
         <v>65479</v>
       </c>
       <c r="T63" s="5">
-        <f t="shared" si="226"/>
+        <f t="shared" si="237"/>
         <v>58489</v>
       </c>
       <c r="U63" s="5">
-        <f t="shared" si="226"/>
+        <f t="shared" si="237"/>
         <v>65632</v>
       </c>
       <c r="V63" s="5">
-        <f t="shared" si="226"/>
+        <f t="shared" si="237"/>
         <v>73904</v>
       </c>
       <c r="W63" s="5">
-        <f t="shared" si="226"/>
+        <f t="shared" si="237"/>
         <v>83872</v>
       </c>
       <c r="X63" s="5">
-        <f t="shared" si="226"/>
+        <f t="shared" si="237"/>
         <v>20165</v>
       </c>
       <c r="Y63" s="5">
-        <f t="shared" si="226"/>
+        <f t="shared" si="237"/>
         <v>29386</v>
       </c>
       <c r="Z63" s="5">
-        <f t="shared" ref="Z63:AG63" si="227">+Z64-Z75</f>
+        <f t="shared" ref="Z63:AH63" si="238">+Z64-Z75</f>
         <v>38513</v>
       </c>
       <c r="AA63" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="238"/>
         <v>49089</v>
       </c>
       <c r="AB63" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="238"/>
         <v>42166</v>
       </c>
       <c r="AC63" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="238"/>
         <v>52772</v>
       </c>
       <c r="AD63" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="238"/>
         <v>66819</v>
       </c>
       <c r="AE63" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="238"/>
         <v>70269</v>
       </c>
       <c r="AF63" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="238"/>
         <v>0</v>
       </c>
       <c r="AG63" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="238"/>
         <v>71693</v>
       </c>
-      <c r="AH63" s="5"/>
+      <c r="AH63" s="5">
+        <f t="shared" si="238"/>
+        <v>72897</v>
+      </c>
       <c r="AI63" s="5"/>
       <c r="AJ63" s="5"/>
       <c r="AK63" s="5"/>
       <c r="AL63" s="5"/>
       <c r="AS63" s="4">
-        <f t="shared" ref="AS63:BG63" si="228">AS64</f>
+        <f t="shared" ref="AS63:BG63" si="239">AS64</f>
         <v>3614</v>
       </c>
       <c r="AT63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>4750</v>
       </c>
       <c r="AU63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>6940</v>
       </c>
       <c r="AV63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>11312</v>
       </c>
       <c r="AW63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>18630</v>
       </c>
       <c r="AX63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>31608</v>
       </c>
       <c r="AY63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>41524</v>
       </c>
       <c r="AZ63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>45741</v>
       </c>
       <c r="BA63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>52843</v>
       </c>
       <c r="BB63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>62740</v>
       </c>
       <c r="BC63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>72802</v>
       </c>
       <c r="BD63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>48755</v>
       </c>
       <c r="BE63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>43393</v>
       </c>
       <c r="BF63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>33528</v>
       </c>
       <c r="BG63" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="239"/>
         <v>30250</v>
       </c>
       <c r="BH63" s="4">
-        <f t="shared" ref="BH63:BM63" si="229">BH64-BH75</f>
+        <f t="shared" ref="BH63:BM63" si="240">BH64-BH75</f>
         <v>30634</v>
       </c>
       <c r="BI63" s="4">
-        <f t="shared" si="229"/>
+        <f t="shared" si="240"/>
         <v>38603</v>
       </c>
       <c r="BJ63" s="4">
-        <f t="shared" si="229"/>
+        <f t="shared" si="240"/>
         <v>51716</v>
       </c>
       <c r="BK63" s="4">
-        <f t="shared" si="229"/>
+        <f t="shared" si="240"/>
         <v>60872</v>
       </c>
       <c r="BL63" s="4">
-        <f t="shared" si="229"/>
+        <f t="shared" si="240"/>
         <v>72266</v>
       </c>
       <c r="BM63" s="4">
-        <f t="shared" si="229"/>
+        <f t="shared" si="240"/>
         <v>77661</v>
       </c>
       <c r="BU63" s="5">
-        <f t="shared" ref="BU63" si="230">+BU64-BU75</f>
+        <f t="shared" ref="BU63" si="241">+BU64-BU75</f>
         <v>61867</v>
       </c>
       <c r="BV63" s="5">
-        <f t="shared" ref="BV63" si="231">+BV64-BV75</f>
+        <f t="shared" ref="BV63" si="242">+BV64-BV75</f>
         <v>73904</v>
       </c>
       <c r="BW63" s="5">
@@ -14015,6 +14270,10 @@
         <f>32105+46167+33683</f>
         <v>111955</v>
       </c>
+      <c r="AH64" s="4">
+        <f>76843+36348</f>
+        <v>113191</v>
+      </c>
       <c r="AS64" s="4">
         <f>3614</f>
         <v>3614</v>
@@ -14198,6 +14457,9 @@
       <c r="AG65" s="4">
         <v>60041</v>
       </c>
+      <c r="AH65" s="4">
+        <v>80876</v>
+      </c>
       <c r="AS65" s="4">
         <v>475</v>
       </c>
@@ -14264,15 +14526,15 @@
       <c r="BS65" s="5"/>
       <c r="BT65" s="5"/>
       <c r="BU65" s="5">
-        <f t="shared" ref="BU65:BU71" si="232">+R65</f>
+        <f t="shared" ref="BU65:BU71" si="243">+R65</f>
         <v>44261</v>
       </c>
       <c r="BV65" s="5">
-        <f t="shared" ref="BV65:BV71" si="233">+V65</f>
+        <f t="shared" ref="BV65:BV71" si="244">+V65</f>
         <v>48688</v>
       </c>
       <c r="BW65" s="4">
-        <f t="shared" ref="BW65:BW71" si="234">+AB65</f>
+        <f t="shared" ref="BW65:BW71" si="245">+AB65</f>
         <v>48188</v>
       </c>
     </row>
@@ -14362,6 +14624,9 @@
       <c r="AG66" s="4">
         <v>1219</v>
       </c>
+      <c r="AH66" s="4">
+        <v>1397</v>
+      </c>
       <c r="AS66" s="4">
         <v>102</v>
       </c>
@@ -14428,15 +14693,15 @@
       <c r="BS66" s="5"/>
       <c r="BT66" s="5"/>
       <c r="BU66" s="5">
-        <f t="shared" si="232"/>
+        <f t="shared" si="243"/>
         <v>3742</v>
       </c>
       <c r="BV66" s="5">
-        <f t="shared" si="233"/>
+        <f t="shared" si="244"/>
         <v>2500</v>
       </c>
       <c r="BW66" s="4">
-        <f t="shared" si="234"/>
+        <f t="shared" si="245"/>
         <v>909</v>
       </c>
     </row>
@@ -14526,6 +14791,9 @@
       <c r="AG67" s="4">
         <v>35797</v>
       </c>
+      <c r="AH67" s="4">
+        <v>48594</v>
+      </c>
       <c r="AS67" s="4">
         <v>121</v>
       </c>
@@ -14607,15 +14875,15 @@
       <c r="BS67" s="5"/>
       <c r="BT67" s="5"/>
       <c r="BU67" s="5">
-        <f t="shared" si="232"/>
+        <f t="shared" si="243"/>
         <v>16924</v>
       </c>
       <c r="BV67" s="5">
-        <f t="shared" si="233"/>
+        <f t="shared" si="244"/>
         <v>21807</v>
       </c>
       <c r="BW67" s="4">
-        <f t="shared" si="234"/>
+        <f t="shared" si="245"/>
         <v>26428</v>
       </c>
     </row>
@@ -14705,6 +14973,9 @@
       <c r="AG68" s="4">
         <v>283228</v>
       </c>
+      <c r="AH68" s="4">
+        <v>313076</v>
+      </c>
       <c r="AS68" s="4">
         <v>930</v>
       </c>
@@ -14771,15 +15042,15 @@
       <c r="BS68" s="5"/>
       <c r="BT68" s="5"/>
       <c r="BU68" s="5">
-        <f t="shared" si="232"/>
+        <f t="shared" si="243"/>
         <v>74398</v>
       </c>
       <c r="BV68" s="5">
-        <f t="shared" si="233"/>
+        <f t="shared" si="244"/>
         <v>95641</v>
       </c>
       <c r="BW68" s="4">
-        <f t="shared" si="234"/>
+        <f t="shared" si="245"/>
         <v>166902</v>
       </c>
     </row>
@@ -14869,6 +15140,9 @@
       <c r="AG69" s="4">
         <v>24403</v>
       </c>
+      <c r="AH69" s="4">
+        <v>24177</v>
+      </c>
       <c r="AS69" s="4">
         <v>0</v>
       </c>
@@ -14935,15 +15209,15 @@
       <c r="BS69" s="5"/>
       <c r="BT69" s="5"/>
       <c r="BU69" s="5">
-        <f t="shared" si="232"/>
+        <f t="shared" si="243"/>
         <v>13148</v>
       </c>
       <c r="BV69" s="5">
-        <f t="shared" si="233"/>
+        <f t="shared" si="244"/>
         <v>14346</v>
       </c>
       <c r="BW69" s="4">
-        <f t="shared" si="234"/>
+        <f t="shared" si="245"/>
         <v>22816</v>
       </c>
     </row>
@@ -15059,6 +15333,10 @@
         <f>119661+19325</f>
         <v>138986</v>
       </c>
+      <c r="AH70" s="4">
+        <f>119651+18609</f>
+        <v>138260</v>
+      </c>
       <c r="AS70" s="4">
         <v>0</v>
       </c>
@@ -15138,15 +15416,15 @@
       <c r="BS70" s="5"/>
       <c r="BT70" s="5"/>
       <c r="BU70" s="5">
-        <f t="shared" si="232"/>
+        <f t="shared" si="243"/>
         <v>78822</v>
       </c>
       <c r="BV70" s="5">
-        <f t="shared" si="233"/>
+        <f t="shared" si="244"/>
         <v>77252</v>
       </c>
       <c r="BW70" s="4">
-        <f t="shared" si="234"/>
+        <f t="shared" si="245"/>
         <v>144576</v>
       </c>
     </row>
@@ -15236,6 +15514,9 @@
       <c r="AG71" s="4">
         <v>38599</v>
       </c>
+      <c r="AH71" s="4">
+        <v>38805</v>
+      </c>
       <c r="AS71" s="4">
         <v>121</v>
       </c>
@@ -15309,15 +15590,15 @@
       <c r="BS71" s="5"/>
       <c r="BT71" s="5"/>
       <c r="BU71" s="5">
-        <f t="shared" si="232"/>
+        <f t="shared" si="243"/>
         <v>21897</v>
       </c>
       <c r="BV71" s="5">
-        <f t="shared" si="233"/>
+        <f t="shared" si="244"/>
         <v>30601</v>
       </c>
       <c r="BW71" s="4">
-        <f t="shared" si="234"/>
+        <f t="shared" si="245"/>
         <v>36943</v>
       </c>
     </row>
@@ -15330,200 +15611,203 @@
       <c r="E72" s="7"/>
       <c r="F72" s="7"/>
       <c r="G72" s="7">
-        <f t="shared" ref="G72:H72" si="235">SUM(G64:G71)</f>
+        <f t="shared" ref="G72:H72" si="246">SUM(G64:G71)</f>
         <v>278955</v>
       </c>
       <c r="H72" s="7">
-        <f t="shared" si="235"/>
+        <f t="shared" si="246"/>
         <v>286556</v>
       </c>
       <c r="I72" s="7">
-        <f t="shared" ref="I72:J72" si="236">SUM(I64:I71)</f>
+        <f t="shared" ref="I72:J72" si="247">SUM(I64:I71)</f>
         <v>285449</v>
       </c>
       <c r="J72" s="7">
-        <f t="shared" si="236"/>
+        <f t="shared" si="247"/>
         <v>301311</v>
       </c>
       <c r="K72" s="7">
-        <f t="shared" ref="K72:L72" si="237">SUM(K64:K71)</f>
+        <f t="shared" ref="K72:L72" si="248">SUM(K64:K71)</f>
         <v>301001</v>
       </c>
       <c r="L72" s="7">
-        <f t="shared" si="237"/>
+        <f t="shared" si="248"/>
         <v>304137</v>
       </c>
       <c r="M72" s="7">
-        <f t="shared" ref="M72:O72" si="238">SUM(M64:M71)</f>
+        <f t="shared" ref="M72:O72" si="249">SUM(M64:M71)</f>
         <v>308879</v>
       </c>
       <c r="N72" s="7">
-        <f t="shared" si="238"/>
+        <f t="shared" si="249"/>
         <v>333779</v>
       </c>
       <c r="O72" s="7">
-        <f t="shared" si="238"/>
+        <f t="shared" si="249"/>
         <v>335418</v>
       </c>
       <c r="P72" s="7">
-        <f t="shared" ref="P72" si="239">SUM(P64:P71)</f>
+        <f t="shared" ref="P72" si="250">SUM(P64:P71)</f>
         <v>340389</v>
       </c>
       <c r="Q72" s="7">
-        <f t="shared" ref="Q72:AG72" si="240">SUM(Q64:Q71)</f>
+        <f t="shared" ref="Q72:AH72" si="251">SUM(Q64:Q71)</f>
         <v>344607</v>
       </c>
       <c r="R72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>364840</v>
       </c>
       <c r="S72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>359784</v>
       </c>
       <c r="T72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>364552</v>
       </c>
       <c r="U72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>380088</v>
       </c>
       <c r="V72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>411976</v>
       </c>
       <c r="W72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>445785</v>
       </c>
       <c r="X72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>470558</v>
       </c>
       <c r="Y72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>484275</v>
       </c>
       <c r="Z72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>512163</v>
       </c>
       <c r="AA72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>523013</v>
       </c>
       <c r="AB72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>533898</v>
       </c>
       <c r="AC72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>562624</v>
       </c>
       <c r="AD72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>619003</v>
       </c>
       <c r="AE72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>636351</v>
       </c>
       <c r="AF72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>0</v>
       </c>
       <c r="AG72" s="7">
-        <f t="shared" si="240"/>
+        <f t="shared" si="251"/>
         <v>694228</v>
       </c>
-      <c r="AH72" s="7"/>
+      <c r="AH72" s="7">
+        <f t="shared" si="251"/>
+        <v>758376</v>
+      </c>
       <c r="AI72" s="7"/>
       <c r="AJ72" s="7"/>
       <c r="AK72" s="7"/>
       <c r="AL72" s="7"/>
       <c r="AS72" s="6">
-        <f t="shared" ref="AS72:BM72" si="241">SUM(AS64:AS71)</f>
+        <f t="shared" ref="AS72:BM72" si="252">SUM(AS64:AS71)</f>
         <v>5363</v>
       </c>
       <c r="AT72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>7210</v>
       </c>
       <c r="AU72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>10093</v>
       </c>
       <c r="AV72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>14387</v>
       </c>
       <c r="AW72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>22357</v>
       </c>
       <c r="AX72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>37156</v>
       </c>
       <c r="AY72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>52150</v>
       </c>
       <c r="AZ72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>59257</v>
       </c>
       <c r="BA72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>67646</v>
       </c>
       <c r="BB72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>79571</v>
       </c>
       <c r="BC72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>92389</v>
       </c>
       <c r="BD72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>70815</v>
       </c>
       <c r="BE72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>69597</v>
       </c>
       <c r="BF72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>63171</v>
       </c>
       <c r="BG72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>72793</v>
       </c>
       <c r="BH72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>77888</v>
       </c>
       <c r="BI72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>86113</v>
       </c>
       <c r="BJ72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>108704</v>
       </c>
       <c r="BK72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>121271</v>
       </c>
       <c r="BL72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>142431</v>
       </c>
       <c r="BM72" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="252"/>
         <v>172384</v>
       </c>
       <c r="BS72" s="7"/>
@@ -15632,6 +15916,9 @@
       <c r="AG74" s="4">
         <v>37513</v>
       </c>
+      <c r="AH74" s="4">
+        <v>42416</v>
+      </c>
       <c r="AS74" s="4">
         <v>324</v>
       </c>
@@ -15699,15 +15986,15 @@
       <c r="BS74" s="5"/>
       <c r="BT74" s="5"/>
       <c r="BU74" s="5">
-        <f t="shared" ref="BU74:BU82" si="242">+R74</f>
+        <f t="shared" ref="BU74:BU82" si="253">+R74</f>
         <v>19000</v>
       </c>
       <c r="BV74" s="5">
-        <f t="shared" ref="BV74:BV82" si="243">+V74</f>
+        <f t="shared" ref="BV74:BV82" si="254">+V74</f>
         <v>18095</v>
       </c>
       <c r="BW74" s="4">
-        <f t="shared" ref="BW74:BW82" si="244">+AB74</f>
+        <f t="shared" ref="BW74:BW82" si="255">+AB74</f>
         <v>22608</v>
       </c>
     </row>
@@ -15823,6 +16110,10 @@
         <f>8839+31423</f>
         <v>40262</v>
       </c>
+      <c r="AH75" s="4">
+        <f>9227+31067</f>
+        <v>40294</v>
+      </c>
       <c r="AS75" s="4">
         <v>0</v>
       </c>
@@ -15894,15 +16185,15 @@
       <c r="BS75" s="5"/>
       <c r="BT75" s="5"/>
       <c r="BU75" s="5">
-        <f t="shared" si="242"/>
+        <f t="shared" si="253"/>
         <v>49781</v>
       </c>
       <c r="BV75" s="5">
-        <f t="shared" si="243"/>
+        <f t="shared" si="254"/>
         <v>47237</v>
       </c>
       <c r="BW75" s="4">
-        <f t="shared" si="244"/>
+        <f t="shared" si="255"/>
         <v>44970</v>
       </c>
     </row>
@@ -15992,6 +16283,9 @@
       <c r="AG76" s="4">
         <v>11270</v>
       </c>
+      <c r="AH76" s="4">
+        <v>14945</v>
+      </c>
       <c r="AS76" s="4">
         <v>96</v>
       </c>
@@ -16058,15 +16352,15 @@
       <c r="BS76" s="5"/>
       <c r="BT76" s="5"/>
       <c r="BU76" s="5">
-        <f t="shared" si="242"/>
+        <f t="shared" si="253"/>
         <v>10661</v>
       </c>
       <c r="BV76" s="5">
-        <f t="shared" si="243"/>
+        <f t="shared" si="254"/>
         <v>11009</v>
       </c>
       <c r="BW76" s="4">
-        <f t="shared" si="244"/>
+        <f t="shared" si="255"/>
         <v>9176</v>
       </c>
     </row>
@@ -16182,6 +16476,10 @@
         <f>3563+2899+27941</f>
         <v>34403</v>
       </c>
+      <c r="AH77" s="4">
+        <f>2534+3054+28647</f>
+        <v>34235</v>
+      </c>
       <c r="AS77" s="4">
         <v>305</v>
       </c>
@@ -16251,15 +16549,15 @@
       <c r="BS77" s="5"/>
       <c r="BT77" s="5"/>
       <c r="BU77" s="5">
-        <f t="shared" si="242"/>
+        <f t="shared" si="253"/>
         <v>30366</v>
       </c>
       <c r="BV77" s="5">
-        <f t="shared" si="243"/>
+        <f t="shared" si="254"/>
         <v>30145</v>
       </c>
       <c r="BW77" s="4">
-        <f t="shared" si="244"/>
+        <f t="shared" si="255"/>
         <v>32958</v>
       </c>
     </row>
@@ -16375,6 +16673,10 @@
         <f>50924+2753</f>
         <v>53677</v>
       </c>
+      <c r="AH78" s="4">
+        <f>72965+2747</f>
+        <v>75712</v>
+      </c>
       <c r="AS78" s="4">
         <v>0</v>
       </c>
@@ -16454,15 +16756,15 @@
       <c r="BS78" s="5"/>
       <c r="BT78" s="5"/>
       <c r="BU78" s="5">
-        <f t="shared" si="242"/>
+        <f t="shared" si="253"/>
         <v>48408</v>
       </c>
       <c r="BV78" s="5">
-        <f t="shared" si="243"/>
+        <f t="shared" si="254"/>
         <v>53813</v>
       </c>
       <c r="BW78" s="4">
-        <f t="shared" si="244"/>
+        <f t="shared" si="255"/>
         <v>48045</v>
       </c>
     </row>
@@ -16552,6 +16854,9 @@
       <c r="AG79" s="4">
         <v>24552</v>
       </c>
+      <c r="AH79" s="4">
+        <v>26738</v>
+      </c>
       <c r="AS79" s="4">
         <v>188</v>
       </c>
@@ -16619,15 +16924,15 @@
       <c r="BS79" s="5"/>
       <c r="BT79" s="5"/>
       <c r="BU79" s="5">
-        <f t="shared" si="242"/>
+        <f t="shared" si="253"/>
         <v>13067</v>
       </c>
       <c r="BV79" s="5">
-        <f t="shared" si="243"/>
+        <f t="shared" si="254"/>
         <v>14745</v>
       </c>
       <c r="BW79" s="4">
-        <f t="shared" si="244"/>
+        <f t="shared" si="255"/>
         <v>20286</v>
       </c>
     </row>
@@ -16717,6 +17022,9 @@
       <c r="AG80" s="4">
         <v>16703</v>
       </c>
+      <c r="AH80" s="4">
+        <v>16532</v>
+      </c>
       <c r="AS80" s="4">
         <v>0</v>
       </c>
@@ -16783,15 +17091,15 @@
       <c r="BS80" s="5"/>
       <c r="BT80" s="5"/>
       <c r="BU80" s="5">
-        <f t="shared" si="242"/>
+        <f t="shared" si="253"/>
         <v>11489</v>
       </c>
       <c r="BV80" s="5">
-        <f t="shared" si="243"/>
+        <f t="shared" si="254"/>
         <v>12728</v>
       </c>
       <c r="BW80" s="4">
-        <f t="shared" si="244"/>
+        <f t="shared" si="255"/>
         <v>17254</v>
       </c>
     </row>
@@ -16881,6 +17189,9 @@
       <c r="AG81" s="4">
         <v>61481</v>
       </c>
+      <c r="AH81" s="4">
+        <v>65117</v>
+      </c>
       <c r="AS81" s="4">
         <v>0</v>
       </c>
@@ -16961,15 +17272,15 @@
       <c r="BS81" s="5"/>
       <c r="BT81" s="5"/>
       <c r="BU81" s="5">
-        <f t="shared" si="242"/>
+        <f t="shared" si="253"/>
         <v>15526</v>
       </c>
       <c r="BV81" s="5">
-        <f t="shared" si="243"/>
+        <f t="shared" si="254"/>
         <v>17981</v>
       </c>
       <c r="BW81" s="4">
-        <f t="shared" si="244"/>
+        <f t="shared" si="255"/>
         <v>35906</v>
       </c>
     </row>
@@ -17059,6 +17370,9 @@
       <c r="AG82" s="4">
         <v>414367</v>
       </c>
+      <c r="AH82" s="4">
+        <v>442387</v>
+      </c>
       <c r="AS82" s="4">
         <v>4450</v>
       </c>
@@ -17126,15 +17440,15 @@
       <c r="BS82" s="5"/>
       <c r="BT82" s="5"/>
       <c r="BU82" s="5">
-        <f t="shared" si="242"/>
+        <f t="shared" si="253"/>
         <v>166542</v>
       </c>
       <c r="BV82" s="5">
-        <f t="shared" si="243"/>
+        <f t="shared" si="254"/>
         <v>206223</v>
       </c>
       <c r="BW82" s="4">
-        <f t="shared" si="244"/>
+        <f t="shared" si="255"/>
         <v>302695</v>
       </c>
     </row>
@@ -17159,7 +17473,7 @@
         <v>285449</v>
       </c>
       <c r="J83" s="7">
-        <f t="shared" ref="J83" si="245">SUM(J74:J82)</f>
+        <f t="shared" ref="J83" si="256">SUM(J74:J82)</f>
         <v>301311</v>
       </c>
       <c r="K83" s="7">
@@ -17167,180 +17481,183 @@
         <v>301001</v>
       </c>
       <c r="L83" s="7">
-        <f t="shared" ref="L83" si="246">SUM(L74:L82)</f>
+        <f t="shared" ref="L83" si="257">SUM(L74:L82)</f>
         <v>304137</v>
       </c>
       <c r="M83" s="7">
-        <f t="shared" ref="M83:P83" si="247">SUM(M74:M82)</f>
+        <f t="shared" ref="M83:P83" si="258">SUM(M74:M82)</f>
         <v>308879</v>
       </c>
       <c r="N83" s="7">
-        <f t="shared" si="247"/>
+        <f t="shared" si="258"/>
         <v>333779</v>
       </c>
       <c r="O83" s="7">
-        <f t="shared" si="247"/>
+        <f t="shared" si="258"/>
         <v>335418</v>
       </c>
       <c r="P83" s="7">
-        <f t="shared" si="247"/>
+        <f t="shared" si="258"/>
         <v>340389</v>
       </c>
       <c r="Q83" s="7">
-        <f t="shared" ref="Q83:W83" si="248">SUM(Q74:Q82)</f>
+        <f t="shared" ref="Q83:W83" si="259">SUM(Q74:Q82)</f>
         <v>344607</v>
       </c>
       <c r="R83" s="7">
-        <f t="shared" si="248"/>
+        <f t="shared" si="259"/>
         <v>364840</v>
       </c>
       <c r="S83" s="7">
-        <f t="shared" si="248"/>
+        <f t="shared" si="259"/>
         <v>359784</v>
       </c>
       <c r="T83" s="7">
-        <f t="shared" si="248"/>
+        <f t="shared" si="259"/>
         <v>364552</v>
       </c>
       <c r="U83" s="7">
-        <f t="shared" si="248"/>
+        <f t="shared" si="259"/>
         <v>380088</v>
       </c>
       <c r="V83" s="7">
-        <f t="shared" si="248"/>
+        <f t="shared" si="259"/>
         <v>411976</v>
       </c>
       <c r="W83" s="7">
-        <f t="shared" si="248"/>
+        <f t="shared" si="259"/>
         <v>445785</v>
       </c>
       <c r="X83" s="7">
-        <f t="shared" ref="X83:AG83" si="249">SUM(X74:X82)</f>
+        <f t="shared" ref="X83:AH83" si="260">SUM(X74:X82)</f>
         <v>470558</v>
       </c>
       <c r="Y83" s="7">
-        <f t="shared" si="249"/>
+        <f t="shared" si="260"/>
         <v>484275</v>
       </c>
       <c r="Z83" s="7">
-        <f t="shared" si="249"/>
+        <f t="shared" si="260"/>
         <v>512163</v>
       </c>
       <c r="AA83" s="7">
-        <f t="shared" si="249"/>
+        <f t="shared" si="260"/>
         <v>523013</v>
       </c>
       <c r="AB83" s="7">
-        <f t="shared" si="249"/>
+        <f t="shared" si="260"/>
         <v>533898</v>
       </c>
       <c r="AC83" s="7">
-        <f t="shared" si="249"/>
+        <f t="shared" si="260"/>
         <v>562624</v>
       </c>
       <c r="AD83" s="7">
-        <f t="shared" si="249"/>
+        <f t="shared" si="260"/>
         <v>619003</v>
       </c>
       <c r="AE83" s="7">
-        <f t="shared" si="249"/>
+        <f t="shared" si="260"/>
         <v>636351</v>
       </c>
       <c r="AF83" s="7">
-        <f t="shared" si="249"/>
+        <f t="shared" si="260"/>
         <v>0</v>
       </c>
       <c r="AG83" s="7">
-        <f t="shared" si="249"/>
+        <f t="shared" si="260"/>
         <v>694228</v>
       </c>
-      <c r="AH83" s="7"/>
+      <c r="AH83" s="7">
+        <f t="shared" si="260"/>
+        <v>758376</v>
+      </c>
       <c r="AI83" s="7"/>
       <c r="AJ83" s="7"/>
       <c r="AK83" s="7"/>
       <c r="AL83" s="7"/>
       <c r="AS83" s="6">
-        <f t="shared" ref="AS83:BM83" si="250">SUM(AS74:AS82)</f>
+        <f t="shared" ref="AS83:BM83" si="261">SUM(AS74:AS82)</f>
         <v>5363</v>
       </c>
       <c r="AT83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>7210</v>
       </c>
       <c r="AU83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>10093</v>
       </c>
       <c r="AV83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>14387</v>
       </c>
       <c r="AW83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>22357</v>
       </c>
       <c r="AX83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>37156</v>
       </c>
       <c r="AY83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>52150</v>
       </c>
       <c r="AZ83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>59257</v>
       </c>
       <c r="BA83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>67646</v>
       </c>
       <c r="BB83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>79571</v>
       </c>
       <c r="BC83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>92389</v>
       </c>
       <c r="BD83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>70815</v>
       </c>
       <c r="BE83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>69597</v>
       </c>
       <c r="BF83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>63171</v>
       </c>
       <c r="BG83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>72793</v>
       </c>
       <c r="BH83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>77888</v>
       </c>
       <c r="BI83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>86113</v>
       </c>
       <c r="BJ83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>108704</v>
       </c>
       <c r="BK83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>121271</v>
       </c>
       <c r="BL83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>142431</v>
       </c>
       <c r="BM83" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="261"/>
         <v>172384</v>
       </c>
       <c r="BS83" s="7"/>
@@ -17367,108 +17684,117 @@
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
       <c r="G85" s="5">
-        <f t="shared" ref="G85:H85" si="251">G46</f>
+        <f t="shared" ref="G85:H85" si="262">G46</f>
         <v>10678</v>
       </c>
       <c r="H85" s="5">
-        <f t="shared" si="251"/>
+        <f t="shared" si="262"/>
         <v>11649</v>
       </c>
       <c r="I85" s="5">
-        <f t="shared" ref="I85:J85" si="252">I46</f>
+        <f t="shared" ref="I85:J85" si="263">I46</f>
         <v>10752</v>
       </c>
       <c r="J85" s="5">
-        <f t="shared" si="252"/>
+        <f t="shared" si="263"/>
         <v>11202</v>
       </c>
       <c r="K85" s="5">
-        <f t="shared" ref="K85:AE85" si="253">K46</f>
+        <f t="shared" ref="K85:AH85" si="264">K46</f>
         <v>13893</v>
       </c>
       <c r="L85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>15463</v>
       </c>
       <c r="M85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>15457</v>
       </c>
       <c r="N85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>16458</v>
       </c>
       <c r="O85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>20505</v>
       </c>
       <c r="P85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>18765</v>
       </c>
       <c r="Q85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>16728</v>
       </c>
       <c r="R85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>16740</v>
       </c>
       <c r="S85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>17556</v>
       </c>
       <c r="T85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>16425</v>
       </c>
       <c r="U85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>18299</v>
       </c>
       <c r="V85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>20081</v>
       </c>
       <c r="W85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>22291</v>
       </c>
       <c r="X85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>21870</v>
       </c>
       <c r="Y85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>21939</v>
       </c>
       <c r="Z85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>22036</v>
       </c>
       <c r="AA85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>24667</v>
       </c>
       <c r="AB85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>24108</v>
       </c>
       <c r="AC85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>25824</v>
       </c>
       <c r="AD85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>27233</v>
       </c>
       <c r="AE85" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="264"/>
         <v>27747</v>
       </c>
-      <c r="AF85" s="5"/>
-      <c r="AG85" s="5"/>
-      <c r="AH85" s="5"/>
+      <c r="AF85" s="5">
+        <f t="shared" si="264"/>
+        <v>28487</v>
+      </c>
+      <c r="AG85" s="5">
+        <f t="shared" si="264"/>
+        <v>31778</v>
+      </c>
+      <c r="AH85" s="5">
+        <f t="shared" si="264"/>
+        <v>35766</v>
+      </c>
       <c r="AI85" s="5"/>
       <c r="AJ85" s="5"/>
       <c r="AK85" s="5"/>
@@ -17569,16 +17895,19 @@
       <c r="AE86" s="4">
         <v>27747</v>
       </c>
+      <c r="AH86" s="4">
+        <v>35766</v>
+      </c>
       <c r="BS86" s="5"/>
       <c r="BT86" s="5"/>
       <c r="BU86" s="5"/>
       <c r="BV86" s="5"/>
       <c r="BW86" s="4">
-        <f t="shared" ref="BW86:BW91" si="254">SUM(W86:Z86)</f>
+        <f t="shared" ref="BW86:BW91" si="265">SUM(W86:Z86)</f>
         <v>88136</v>
       </c>
       <c r="BX86" s="4">
-        <f t="shared" ref="BX86:BX91" si="255">SUM(AA86:AD86)</f>
+        <f t="shared" ref="BX86:BX91" si="266">SUM(AA86:AD86)</f>
         <v>101832</v>
       </c>
     </row>
@@ -17665,16 +17994,19 @@
       <c r="AE87" s="4">
         <v>13061</v>
       </c>
+      <c r="AH87" s="4">
+        <v>11022</v>
+      </c>
       <c r="BS87" s="5"/>
       <c r="BT87" s="5"/>
       <c r="BU87" s="5"/>
       <c r="BV87" s="5"/>
       <c r="BW87" s="4">
-        <f t="shared" si="254"/>
+        <f t="shared" si="265"/>
         <v>22287</v>
       </c>
       <c r="BX87" s="4">
-        <f t="shared" si="255"/>
+        <f t="shared" si="266"/>
         <v>34153</v>
       </c>
     </row>
@@ -17761,16 +18093,19 @@
       <c r="AE88" s="4">
         <v>2983</v>
       </c>
+      <c r="AH88" s="4">
+        <v>3122</v>
+      </c>
       <c r="BS88" s="5"/>
       <c r="BT88" s="5"/>
       <c r="BU88" s="5"/>
       <c r="BV88" s="5"/>
       <c r="BW88" s="4">
-        <f t="shared" si="254"/>
+        <f t="shared" si="265"/>
         <v>10734</v>
       </c>
       <c r="BX88" s="4">
-        <f t="shared" si="255"/>
+        <f t="shared" si="266"/>
         <v>11974</v>
       </c>
     </row>
@@ -17857,16 +18192,19 @@
       <c r="AE89" s="4">
         <v>-1007</v>
       </c>
+      <c r="AH89" s="4">
+        <v>-3743</v>
+      </c>
       <c r="BS89" s="5"/>
       <c r="BT89" s="5"/>
       <c r="BU89" s="5"/>
       <c r="BV89" s="5"/>
       <c r="BW89" s="4">
-        <f t="shared" si="254"/>
+        <f t="shared" si="265"/>
         <v>305</v>
       </c>
       <c r="BX89" s="4">
-        <f t="shared" si="255"/>
+        <f t="shared" si="266"/>
         <v>609</v>
       </c>
     </row>
@@ -17953,16 +18291,19 @@
       <c r="AE90" s="4">
         <v>2491</v>
       </c>
+      <c r="AH90" s="4">
+        <v>4650</v>
+      </c>
       <c r="BS90" s="5"/>
       <c r="BT90" s="5"/>
       <c r="BU90" s="5"/>
       <c r="BV90" s="5"/>
       <c r="BW90" s="4">
-        <f t="shared" si="254"/>
+        <f t="shared" si="265"/>
         <v>-4738</v>
       </c>
       <c r="BX90" s="4">
-        <f t="shared" si="255"/>
+        <f t="shared" si="266"/>
         <v>-7056</v>
       </c>
     </row>
@@ -18074,16 +18415,20 @@
         <f>16490-192-1162-394-614-5418-2944-5507-477</f>
         <v>-218</v>
       </c>
+      <c r="AH91" s="4">
+        <f>-21084-178-2842-1350+2365+22428-307+7013-1421</f>
+        <v>4624</v>
+      </c>
       <c r="BS91" s="5"/>
       <c r="BT91" s="5"/>
       <c r="BU91" s="5"/>
       <c r="BV91" s="5"/>
       <c r="BW91" s="4">
-        <f t="shared" si="254"/>
+        <f t="shared" si="265"/>
         <v>1824</v>
       </c>
       <c r="BX91" s="4">
-        <f t="shared" si="255"/>
+        <f t="shared" si="266"/>
         <v>-5350</v>
       </c>
     </row>
@@ -18096,108 +18441,117 @@
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
       <c r="G92" s="5">
-        <f t="shared" ref="G92:H92" si="256">SUM(G86:G91)</f>
+        <f t="shared" ref="G92:H92" si="267">SUM(G86:G91)</f>
         <v>13818</v>
       </c>
       <c r="H92" s="5">
-        <f t="shared" si="256"/>
+        <f t="shared" si="267"/>
         <v>10680</v>
       </c>
       <c r="I92" s="5">
-        <f t="shared" ref="I92:J92" si="257">SUM(I86:I91)</f>
+        <f t="shared" ref="I92:J92" si="268">SUM(I86:I91)</f>
         <v>17504</v>
       </c>
       <c r="J92" s="5">
-        <f t="shared" si="257"/>
+        <f t="shared" si="268"/>
         <v>18673</v>
       </c>
       <c r="K92" s="5">
-        <f t="shared" ref="K92:L92" si="258">SUM(K86:K91)</f>
+        <f t="shared" ref="K92:L92" si="269">SUM(K86:K91)</f>
         <v>19335</v>
       </c>
       <c r="L92" s="5">
-        <f t="shared" si="258"/>
+        <f t="shared" si="269"/>
         <v>12516</v>
       </c>
       <c r="M92" s="5">
-        <f t="shared" ref="M92:O92" si="259">SUM(M86:M91)</f>
+        <f t="shared" ref="M92:O92" si="270">SUM(M86:M91)</f>
         <v>22179</v>
       </c>
       <c r="N92" s="5">
-        <f t="shared" si="259"/>
+        <f t="shared" si="270"/>
         <v>22710</v>
       </c>
       <c r="O92" s="5">
-        <f t="shared" si="259"/>
+        <f t="shared" si="270"/>
         <v>24540</v>
       </c>
       <c r="P92" s="5">
-        <f t="shared" ref="P92" si="260">SUM(P86:P91)</f>
+        <f t="shared" ref="P92" si="271">SUM(P86:P91)</f>
         <v>14480</v>
       </c>
       <c r="Q92" s="5">
-        <f t="shared" ref="Q92:U92" si="261">SUM(Q86:Q91)</f>
+        <f t="shared" ref="Q92:U92" si="272">SUM(Q86:Q91)</f>
         <v>25386</v>
       </c>
       <c r="R92" s="5">
-        <f t="shared" si="261"/>
+        <f t="shared" si="272"/>
         <v>24629</v>
       </c>
       <c r="S92" s="5">
-        <f t="shared" si="261"/>
+        <f t="shared" si="272"/>
         <v>23198</v>
       </c>
       <c r="T92" s="5">
-        <f t="shared" si="261"/>
+        <f t="shared" si="272"/>
         <v>11173</v>
       </c>
       <c r="U92" s="5">
-        <f t="shared" si="261"/>
+        <f t="shared" si="272"/>
         <v>24441</v>
       </c>
       <c r="V92" s="5">
-        <f t="shared" ref="V92:AE92" si="262">SUM(V86:V91)</f>
+        <f t="shared" ref="V92:AH92" si="273">SUM(V86:V91)</f>
         <v>28770</v>
       </c>
       <c r="W92" s="5">
-        <f t="shared" si="262"/>
+        <f t="shared" si="273"/>
         <v>30583</v>
       </c>
       <c r="X92" s="5">
-        <f t="shared" si="262"/>
+        <f t="shared" si="273"/>
         <v>18853</v>
       </c>
       <c r="Y92" s="5">
-        <f t="shared" si="262"/>
+        <f t="shared" si="273"/>
         <v>31917</v>
       </c>
       <c r="Z92" s="5">
-        <f t="shared" si="262"/>
+        <f t="shared" si="273"/>
         <v>37195</v>
       </c>
       <c r="AA92" s="5">
-        <f t="shared" si="262"/>
+        <f t="shared" si="273"/>
         <v>34180</v>
       </c>
       <c r="AB92" s="5">
-        <f t="shared" si="262"/>
+        <f t="shared" si="273"/>
         <v>22291</v>
       </c>
       <c r="AC92" s="5">
-        <f t="shared" si="262"/>
+        <f t="shared" si="273"/>
         <v>37044</v>
       </c>
       <c r="AD92" s="5">
-        <f t="shared" si="262"/>
+        <f t="shared" si="273"/>
         <v>42647</v>
       </c>
       <c r="AE92" s="5">
-        <f t="shared" si="262"/>
+        <f t="shared" si="273"/>
         <v>45057</v>
       </c>
-      <c r="AF92" s="5"/>
-      <c r="AG92" s="5"/>
-      <c r="AH92" s="5"/>
+      <c r="AF92" s="5">
+        <f t="shared" si="273"/>
+        <v>0</v>
+      </c>
+      <c r="AG92" s="5">
+        <f t="shared" si="273"/>
+        <v>0</v>
+      </c>
+      <c r="AH92" s="5">
+        <f t="shared" si="273"/>
+        <v>55441</v>
+      </c>
       <c r="AI92" s="5"/>
       <c r="AJ92" s="5"/>
       <c r="AK92" s="5"/>
@@ -18323,12 +18677,21 @@
       <c r="AE94" s="4">
         <v>-19394</v>
       </c>
+      <c r="AF94" s="4">
+        <v>-29900</v>
+      </c>
+      <c r="AG94" s="4">
+        <v>-30900</v>
+      </c>
+      <c r="AH94" s="4">
+        <v>-35802</v>
+      </c>
       <c r="BS94" s="5"/>
       <c r="BT94" s="5"/>
       <c r="BU94" s="5"/>
       <c r="BV94" s="5"/>
       <c r="BW94" s="4">
-        <f t="shared" ref="BW94:BW97" si="263">SUM(W94:Z94)</f>
+        <f t="shared" ref="BW94:BW97" si="274">SUM(W94:Z94)</f>
         <v>-44477</v>
       </c>
       <c r="BX94" s="4">
@@ -18420,13 +18783,16 @@
       </c>
       <c r="AE95" s="4">
         <v>-578</v>
+      </c>
+      <c r="AH95" s="4">
+        <v>-452</v>
       </c>
       <c r="BS95" s="5"/>
       <c r="BT95" s="5"/>
       <c r="BU95" s="5"/>
       <c r="BV95" s="5"/>
       <c r="BW95" s="4">
-        <f t="shared" si="263"/>
+        <f t="shared" si="274"/>
         <v>-69132</v>
       </c>
       <c r="BX95" s="4">
@@ -18545,12 +18911,16 @@
         <f>-17671+6031+3262</f>
         <v>-8378</v>
       </c>
+      <c r="AH96" s="4">
+        <f>-18829+4181+6487</f>
+        <v>-8161</v>
+      </c>
       <c r="BS96" s="5"/>
       <c r="BT96" s="5"/>
       <c r="BU96" s="5"/>
       <c r="BV96" s="5"/>
       <c r="BW96" s="4">
-        <f t="shared" si="263"/>
+        <f t="shared" si="274"/>
         <v>17937</v>
       </c>
       <c r="BX96" s="4">
@@ -18642,13 +19012,16 @@
       </c>
       <c r="AE97" s="4">
         <v>-6209</v>
+      </c>
+      <c r="AH97" s="4">
+        <v>-10416</v>
       </c>
       <c r="BS97" s="5"/>
       <c r="BT97" s="5"/>
       <c r="BU97" s="5"/>
       <c r="BV97" s="5"/>
       <c r="BW97" s="4">
-        <f t="shared" si="263"/>
+        <f t="shared" si="274"/>
         <v>-1298</v>
       </c>
       <c r="BX97" s="4">
@@ -18662,110 +19035,122 @@
       </c>
       <c r="C98" s="5"/>
       <c r="D98" s="5">
-        <f t="shared" ref="D98" si="264">SUM(D94:D97)</f>
+        <f t="shared" ref="D98" si="275">SUM(D94:D97)</f>
         <v>-4200</v>
       </c>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="5">
-        <f t="shared" ref="G98:H98" si="265">SUM(G94:G97)</f>
+        <f t="shared" ref="G98:H98" si="276">SUM(G94:G97)</f>
         <v>-1776</v>
       </c>
       <c r="H98" s="5">
-        <f t="shared" si="265"/>
+        <f t="shared" si="276"/>
         <v>-6036</v>
       </c>
       <c r="I98" s="5">
-        <f t="shared" ref="I98:J98" si="266">SUM(I94:I97)</f>
+        <f t="shared" ref="I98:J98" si="277">SUM(I94:I97)</f>
         <v>51</v>
       </c>
       <c r="J98" s="5">
-        <f t="shared" si="266"/>
+        <f t="shared" si="277"/>
         <v>-4462</v>
       </c>
       <c r="K98" s="5">
-        <f t="shared" ref="K98:L98" si="267">SUM(K94:K97)</f>
+        <f t="shared" ref="K98:L98" si="278">SUM(K94:K97)</f>
         <v>-5371</v>
       </c>
       <c r="L98" s="5">
-        <f t="shared" si="267"/>
+        <f t="shared" si="278"/>
         <v>-1669</v>
       </c>
       <c r="M98" s="5">
-        <f t="shared" ref="M98:P98" si="268">SUM(M94:M97)</f>
+        <f t="shared" ref="M98:P98" si="279">SUM(M94:M97)</f>
         <v>-9684</v>
       </c>
       <c r="N98" s="5">
-        <f t="shared" si="268"/>
+        <f t="shared" si="279"/>
         <v>-10853</v>
       </c>
       <c r="O98" s="5">
-        <f t="shared" si="268"/>
+        <f t="shared" si="279"/>
         <v>-3250</v>
       </c>
       <c r="P98" s="5">
-        <f t="shared" si="268"/>
+        <f t="shared" si="279"/>
         <v>-1161</v>
       </c>
       <c r="Q98" s="5">
-        <f t="shared" ref="Q98:AE98" si="269">SUM(Q94:Q97)</f>
+        <f t="shared" ref="Q98:AH98" si="280">SUM(Q94:Q97)</f>
         <v>-16171</v>
       </c>
       <c r="R98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-9729</v>
       </c>
       <c r="S98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-3132</v>
       </c>
       <c r="T98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-7150</v>
       </c>
       <c r="U98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-3264</v>
       </c>
       <c r="V98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-9134</v>
       </c>
       <c r="W98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>503</v>
       </c>
       <c r="X98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-71925</v>
       </c>
       <c r="Y98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-10700</v>
       </c>
       <c r="Z98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-14848</v>
       </c>
       <c r="AA98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-15201</v>
       </c>
       <c r="AB98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-14112</v>
       </c>
       <c r="AC98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-12714</v>
       </c>
       <c r="AD98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-30572</v>
       </c>
       <c r="AE98" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="280"/>
         <v>-34559</v>
+      </c>
+      <c r="AF98" s="5">
+        <f t="shared" si="280"/>
+        <v>-29900</v>
+      </c>
+      <c r="AG98" s="5">
+        <f t="shared" si="280"/>
+        <v>-30900</v>
+      </c>
+      <c r="AH98" s="5">
+        <f t="shared" si="280"/>
+        <v>-54831</v>
       </c>
       <c r="BS98" s="5"/>
       <c r="BT98" s="5"/>
@@ -18863,16 +19248,19 @@
       <c r="AE100" s="4">
         <v>0</v>
       </c>
+      <c r="AH100" s="4">
+        <v>0</v>
+      </c>
       <c r="BS100" s="5"/>
       <c r="BT100" s="5"/>
       <c r="BU100" s="5"/>
       <c r="BV100" s="5"/>
       <c r="BW100" s="4">
-        <f t="shared" ref="BW100:BW106" si="270">SUM(W100:Z100)</f>
+        <f t="shared" ref="BW100:BW106" si="281">SUM(W100:Z100)</f>
         <v>0</v>
       </c>
       <c r="BX100" s="4">
-        <f t="shared" ref="BX100:BX106" si="271">SUM(AA100:AD100)</f>
+        <f t="shared" ref="BX100:BX106" si="282">SUM(AA100:AD100)</f>
         <v>0</v>
       </c>
     </row>
@@ -18965,16 +19353,19 @@
       <c r="AE101" s="4">
         <v>0</v>
       </c>
+      <c r="AH101" s="4">
+        <v>0</v>
+      </c>
       <c r="BS101" s="5"/>
       <c r="BT101" s="5"/>
       <c r="BU101" s="5"/>
       <c r="BV101" s="5"/>
       <c r="BW101" s="4">
-        <f t="shared" si="270"/>
+        <f t="shared" si="281"/>
         <v>575</v>
       </c>
       <c r="BX101" s="4">
-        <f t="shared" si="271"/>
+        <f t="shared" si="282"/>
         <v>-8962</v>
       </c>
     </row>
@@ -19085,16 +19476,20 @@
         <f>689-5650</f>
         <v>-4961</v>
       </c>
+      <c r="AH102" s="4">
+        <f>520-4579</f>
+        <v>-4059</v>
+      </c>
       <c r="BS102" s="5"/>
       <c r="BT102" s="5"/>
       <c r="BU102" s="5"/>
       <c r="BV102" s="5"/>
       <c r="BW102" s="4">
-        <f t="shared" si="270"/>
+        <f t="shared" si="281"/>
         <v>-15252</v>
       </c>
       <c r="BX102" s="4">
-        <f t="shared" si="271"/>
+        <f t="shared" si="282"/>
         <v>-16364</v>
       </c>
     </row>
@@ -19181,16 +19576,19 @@
       <c r="AE103" s="4">
         <v>-6169</v>
       </c>
+      <c r="AH103" s="4">
+        <v>-6758</v>
+      </c>
       <c r="BS103" s="5"/>
       <c r="BT103" s="5"/>
       <c r="BU103" s="5"/>
       <c r="BV103" s="5"/>
       <c r="BW103" s="4">
-        <f t="shared" si="270"/>
+        <f t="shared" si="281"/>
         <v>-21771</v>
       </c>
       <c r="BX103" s="4">
-        <f t="shared" si="271"/>
+        <f t="shared" si="282"/>
         <v>-24082</v>
       </c>
     </row>
@@ -19277,16 +19675,19 @@
       <c r="AE104" s="4">
         <v>-669</v>
       </c>
+      <c r="AH104" s="4">
+        <v>-962</v>
+      </c>
       <c r="BS104" s="5"/>
       <c r="BT104" s="5"/>
       <c r="BU104" s="5"/>
       <c r="BV104" s="5"/>
       <c r="BW104" s="4">
-        <f t="shared" si="270"/>
+        <f t="shared" si="281"/>
         <v>-1309</v>
       </c>
       <c r="BX104" s="4">
-        <f t="shared" si="271"/>
+        <f t="shared" si="282"/>
         <v>-2291</v>
       </c>
     </row>
@@ -19299,7 +19700,7 @@
       <c r="E105" s="5"/>
       <c r="F105" s="5"/>
       <c r="G105" s="5">
-        <f t="shared" ref="G105" si="272">SUM(G100:G104)</f>
+        <f t="shared" ref="G105" si="283">SUM(G100:G104)</f>
         <v>-10209</v>
       </c>
       <c r="H105" s="5">
@@ -19315,23 +19716,23 @@
         <v>-12262</v>
       </c>
       <c r="K105" s="5">
-        <f t="shared" ref="K105:L105" si="273">SUM(K100:K104)</f>
+        <f t="shared" ref="K105:L105" si="284">SUM(K100:K104)</f>
         <v>-10289</v>
       </c>
       <c r="L105" s="5">
-        <f t="shared" si="273"/>
+        <f t="shared" si="284"/>
         <v>-13634</v>
       </c>
       <c r="M105" s="5">
-        <f t="shared" ref="M105:O105" si="274">SUM(M100:M104)</f>
+        <f t="shared" ref="M105:O105" si="285">SUM(M100:M104)</f>
         <v>-13192</v>
       </c>
       <c r="N105" s="5">
-        <f t="shared" si="274"/>
+        <f t="shared" si="285"/>
         <v>-11371</v>
       </c>
       <c r="O105" s="5">
-        <f t="shared" si="274"/>
+        <f t="shared" si="285"/>
         <v>-16276</v>
       </c>
       <c r="P105" s="5">
@@ -19355,48 +19756,60 @@
         <v>-11349</v>
       </c>
       <c r="U105" s="5">
-        <f t="shared" ref="U105:AE105" si="275">SUM(U100:U104)</f>
+        <f t="shared" ref="U105:AH105" si="286">SUM(U100:U104)</f>
         <v>-10290</v>
       </c>
       <c r="V105" s="5">
-        <f t="shared" si="275"/>
+        <f t="shared" si="286"/>
         <v>-11413</v>
       </c>
       <c r="W105" s="5">
-        <f t="shared" si="275"/>
+        <f t="shared" si="286"/>
         <v>14761</v>
       </c>
       <c r="X105" s="5">
-        <f t="shared" si="275"/>
+        <f t="shared" si="286"/>
         <v>-10147</v>
       </c>
       <c r="Y105" s="5">
-        <f t="shared" si="275"/>
+        <f t="shared" si="286"/>
         <v>-18808</v>
       </c>
       <c r="Z105" s="5">
-        <f t="shared" si="275"/>
+        <f t="shared" si="286"/>
         <v>-23563</v>
       </c>
       <c r="AA105" s="5">
-        <f t="shared" si="275"/>
+        <f t="shared" si="286"/>
         <v>-16576</v>
       </c>
       <c r="AB105" s="5">
-        <f t="shared" si="275"/>
+        <f t="shared" si="286"/>
         <v>-11243</v>
       </c>
       <c r="AC105" s="5">
-        <f t="shared" si="275"/>
+        <f t="shared" si="286"/>
         <v>-13036</v>
       </c>
       <c r="AD105" s="5">
-        <f t="shared" si="275"/>
+        <f t="shared" si="286"/>
         <v>-10844</v>
       </c>
       <c r="AE105" s="5">
-        <f t="shared" si="275"/>
+        <f t="shared" si="286"/>
         <v>-11799</v>
+      </c>
+      <c r="AF105" s="5">
+        <f t="shared" si="286"/>
+        <v>0</v>
+      </c>
+      <c r="AG105" s="5">
+        <f t="shared" si="286"/>
+        <v>0</v>
+      </c>
+      <c r="AH105" s="5">
+        <f t="shared" si="286"/>
+        <v>-11779</v>
       </c>
       <c r="BS105" s="5"/>
       <c r="BT105" s="5"/>
@@ -19490,12 +19903,15 @@
       <c r="AE106" s="4">
         <v>-92</v>
       </c>
+      <c r="AH106" s="4">
+        <v>-1</v>
+      </c>
       <c r="BW106" s="4">
-        <f t="shared" si="270"/>
+        <f t="shared" si="281"/>
         <v>-210</v>
       </c>
       <c r="BX106" s="4">
-        <f t="shared" si="271"/>
+        <f t="shared" si="282"/>
         <v>63</v>
       </c>
     </row>
@@ -19504,39 +19920,39 @@
         <v>67</v>
       </c>
       <c r="G107" s="5">
-        <f t="shared" ref="G107:H107" si="276">G105+G106+G98+G92</f>
+        <f t="shared" ref="G107:H107" si="287">G105+G106+G98+G92</f>
         <v>1761</v>
       </c>
       <c r="H107" s="5">
-        <f t="shared" si="276"/>
+        <f t="shared" si="287"/>
         <v>-4253</v>
       </c>
       <c r="I107" s="5">
-        <f t="shared" ref="I107:J107" si="277">I105+I106+I98+I92</f>
+        <f t="shared" ref="I107:J107" si="288">I105+I106+I98+I92</f>
         <v>2846</v>
       </c>
       <c r="J107" s="5">
-        <f t="shared" si="277"/>
+        <f t="shared" si="288"/>
         <v>1866</v>
       </c>
       <c r="K107" s="5">
-        <f t="shared" ref="K107:L107" si="278">K105+K106+K98+K92</f>
+        <f t="shared" ref="K107:L107" si="289">K105+K106+K98+K92</f>
         <v>3629</v>
       </c>
       <c r="L107" s="5">
-        <f t="shared" si="278"/>
+        <f t="shared" si="289"/>
         <v>-2773</v>
       </c>
       <c r="M107" s="5">
-        <f t="shared" ref="M107:O107" si="279">M105+M106+M98+M92</f>
+        <f t="shared" ref="M107:O107" si="290">M105+M106+M98+M92</f>
         <v>-730</v>
       </c>
       <c r="N107" s="5">
-        <f t="shared" si="279"/>
+        <f t="shared" si="290"/>
         <v>522</v>
       </c>
       <c r="O107" s="5">
-        <f t="shared" si="279"/>
+        <f t="shared" si="290"/>
         <v>4941</v>
       </c>
       <c r="P107" s="5">
@@ -19560,48 +19976,60 @@
         <v>-7238</v>
       </c>
       <c r="U107" s="5">
-        <f t="shared" ref="U107:AE107" si="280">U105+U106+U98+U92</f>
+        <f t="shared" ref="U107:AH107" si="291">U105+U106+U98+U92</f>
         <v>10916</v>
       </c>
       <c r="V107" s="5">
-        <f t="shared" si="280"/>
+        <f t="shared" si="291"/>
         <v>8142</v>
       </c>
       <c r="W107" s="5">
-        <f t="shared" si="280"/>
+        <f t="shared" si="291"/>
         <v>45748</v>
       </c>
       <c r="X107" s="5">
-        <f t="shared" si="280"/>
+        <f t="shared" si="291"/>
         <v>-63147</v>
       </c>
       <c r="Y107" s="5">
-        <f t="shared" si="280"/>
+        <f t="shared" si="291"/>
         <v>2329</v>
       </c>
       <c r="Z107" s="5">
-        <f t="shared" si="280"/>
+        <f t="shared" si="291"/>
         <v>-1319</v>
       </c>
       <c r="AA107" s="5">
-        <f t="shared" si="280"/>
+        <f t="shared" si="291"/>
         <v>2525</v>
       </c>
       <c r="AB107" s="5">
-        <f t="shared" si="280"/>
+        <f t="shared" si="291"/>
         <v>-3358</v>
       </c>
       <c r="AC107" s="5">
-        <f t="shared" si="280"/>
+        <f t="shared" si="291"/>
         <v>11346</v>
       </c>
       <c r="AD107" s="5">
-        <f t="shared" si="280"/>
+        <f t="shared" si="291"/>
         <v>1414</v>
       </c>
       <c r="AE107" s="5">
-        <f t="shared" si="280"/>
+        <f t="shared" si="291"/>
         <v>-1393</v>
+      </c>
+      <c r="AF107" s="5">
+        <f t="shared" si="291"/>
+        <v>-29900</v>
+      </c>
+      <c r="AG107" s="5">
+        <f t="shared" si="291"/>
+        <v>-30900</v>
+      </c>
+      <c r="AH107" s="5">
+        <f t="shared" si="291"/>
+        <v>-11170</v>
       </c>
       <c r="BW107" s="6">
         <f>BW105+BW106</f>
@@ -19617,39 +20045,39 @@
         <v>72</v>
       </c>
       <c r="G109" s="5">
-        <f t="shared" ref="G109:J109" si="281">G92+G94</f>
+        <f t="shared" ref="G109:J109" si="292">G92+G94</f>
         <v>10433</v>
       </c>
       <c r="H109" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="292"/>
         <v>7135</v>
       </c>
       <c r="I109" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="292"/>
         <v>13737</v>
       </c>
       <c r="J109" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="292"/>
         <v>13929</v>
       </c>
       <c r="K109" s="5">
-        <f t="shared" ref="K109:O109" si="282">K92+K94</f>
+        <f t="shared" ref="K109:O109" si="293">K92+K94</f>
         <v>14428</v>
       </c>
       <c r="L109" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="293"/>
         <v>8342</v>
       </c>
       <c r="M109" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="293"/>
         <v>17090</v>
       </c>
       <c r="N109" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="293"/>
         <v>16258</v>
       </c>
       <c r="O109" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="293"/>
         <v>18730</v>
       </c>
       <c r="P109" s="5">
@@ -19657,11 +20085,11 @@
         <v>8615</v>
       </c>
       <c r="Q109" s="5">
-        <f t="shared" ref="Q109:R109" si="283">Q92+Q94</f>
+        <f t="shared" ref="Q109:R109" si="294">Q92+Q94</f>
         <v>20046</v>
       </c>
       <c r="R109" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>17758</v>
       </c>
       <c r="S109" s="5">
@@ -19673,48 +20101,60 @@
         <v>4899</v>
       </c>
       <c r="U109" s="5">
-        <f t="shared" ref="U109:AE109" si="284">U92+U94</f>
+        <f t="shared" ref="U109:AH109" si="295">U92+U94</f>
         <v>17834</v>
       </c>
       <c r="V109" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="295"/>
         <v>19827</v>
       </c>
       <c r="W109" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="295"/>
         <v>20666</v>
       </c>
       <c r="X109" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="295"/>
         <v>9118</v>
       </c>
       <c r="Y109" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="295"/>
         <v>20965</v>
       </c>
       <c r="Z109" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="295"/>
         <v>23322</v>
       </c>
       <c r="AA109" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="295"/>
         <v>19257</v>
       </c>
       <c r="AB109" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="295"/>
         <v>6487</v>
       </c>
       <c r="AC109" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="295"/>
         <v>20299</v>
       </c>
       <c r="AD109" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="295"/>
         <v>25568</v>
       </c>
       <c r="AE109" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="295"/>
         <v>25663</v>
+      </c>
+      <c r="AF109" s="5">
+        <f t="shared" si="295"/>
+        <v>-29900</v>
+      </c>
+      <c r="AG109" s="5">
+        <f t="shared" si="295"/>
+        <v>-30900</v>
+      </c>
+      <c r="AH109" s="5">
+        <f t="shared" si="295"/>
+        <v>19639</v>
       </c>
       <c r="BW109" s="4">
         <f>BW92+BW94</f>
@@ -19730,91 +20170,91 @@
         <v>103</v>
       </c>
       <c r="J110" s="4">
-        <f t="shared" ref="J110" si="285">SUM(G109:J109)</f>
+        <f t="shared" ref="J110" si="296">SUM(G109:J109)</f>
         <v>45234</v>
       </c>
       <c r="K110" s="4">
-        <f t="shared" ref="K110" si="286">SUM(H109:K109)</f>
+        <f t="shared" ref="K110" si="297">SUM(H109:K109)</f>
         <v>49229</v>
       </c>
       <c r="L110" s="4">
-        <f t="shared" ref="L110" si="287">SUM(I109:L109)</f>
+        <f t="shared" ref="L110" si="298">SUM(I109:L109)</f>
         <v>50436</v>
       </c>
       <c r="M110" s="4">
-        <f t="shared" ref="M110" si="288">SUM(J109:M109)</f>
+        <f t="shared" ref="M110" si="299">SUM(J109:M109)</f>
         <v>53789</v>
       </c>
       <c r="N110" s="4">
-        <f t="shared" ref="N110" si="289">SUM(K109:N109)</f>
+        <f t="shared" ref="N110" si="300">SUM(K109:N109)</f>
         <v>56118</v>
       </c>
       <c r="O110" s="4">
-        <f t="shared" ref="O110:T110" si="290">SUM(L109:O109)</f>
+        <f t="shared" ref="O110:T110" si="301">SUM(L109:O109)</f>
         <v>60420</v>
       </c>
       <c r="P110" s="4">
-        <f t="shared" si="290"/>
+        <f t="shared" si="301"/>
         <v>60693</v>
       </c>
       <c r="Q110" s="4">
-        <f t="shared" si="290"/>
+        <f t="shared" si="301"/>
         <v>63649</v>
       </c>
       <c r="R110" s="4">
-        <f t="shared" si="290"/>
+        <f t="shared" si="301"/>
         <v>65149</v>
       </c>
       <c r="S110" s="4">
-        <f t="shared" si="290"/>
+        <f t="shared" si="301"/>
         <v>63334</v>
       </c>
       <c r="T110" s="4">
-        <f t="shared" si="290"/>
+        <f t="shared" si="301"/>
         <v>59618</v>
       </c>
       <c r="U110" s="4">
-        <f t="shared" ref="U110:AE110" si="291">SUM(R109:U109)</f>
+        <f t="shared" ref="U110:AE110" si="302">SUM(R109:U109)</f>
         <v>57406</v>
       </c>
       <c r="V110" s="4">
-        <f t="shared" si="291"/>
+        <f t="shared" si="302"/>
         <v>59475</v>
       </c>
       <c r="W110" s="4">
-        <f t="shared" si="291"/>
+        <f t="shared" si="302"/>
         <v>63226</v>
       </c>
       <c r="X110" s="4">
-        <f t="shared" si="291"/>
+        <f t="shared" si="302"/>
         <v>67445</v>
       </c>
       <c r="Y110" s="4">
-        <f t="shared" si="291"/>
+        <f t="shared" si="302"/>
         <v>70576</v>
       </c>
       <c r="Z110" s="4">
-        <f t="shared" si="291"/>
+        <f t="shared" si="302"/>
         <v>74071</v>
       </c>
       <c r="AA110" s="4">
-        <f t="shared" si="291"/>
+        <f t="shared" si="302"/>
         <v>72662</v>
       </c>
       <c r="AB110" s="4">
-        <f t="shared" si="291"/>
+        <f t="shared" si="302"/>
         <v>70031</v>
       </c>
       <c r="AC110" s="4">
-        <f t="shared" si="291"/>
+        <f t="shared" si="302"/>
         <v>69365</v>
       </c>
       <c r="AD110" s="4">
-        <f t="shared" si="291"/>
+        <f t="shared" si="302"/>
         <v>71611</v>
       </c>
       <c r="AE110" s="4">
-        <f t="shared" si="291"/>
+        <f t="shared" si="302"/>
         <v>78017</v>
       </c>
     </row>
@@ -19823,75 +20263,75 @@
         <v>463</v>
       </c>
       <c r="N111" s="12">
-        <f t="shared" ref="N111" si="292">+N110/J110-1</f>
+        <f t="shared" ref="N111" si="303">+N110/J110-1</f>
         <v>0.24061546624220709</v>
       </c>
       <c r="O111" s="12">
-        <f t="shared" ref="O111" si="293">+O110/K110-1</f>
+        <f t="shared" ref="O111" si="304">+O110/K110-1</f>
         <v>0.22732535700501733</v>
       </c>
       <c r="P111" s="12">
-        <f t="shared" ref="P111" si="294">+P110/L110-1</f>
+        <f t="shared" ref="P111" si="305">+P110/L110-1</f>
         <v>0.20336664287413742</v>
       </c>
       <c r="Q111" s="12">
-        <f t="shared" ref="Q111" si="295">+Q110/M110-1</f>
+        <f t="shared" ref="Q111" si="306">+Q110/M110-1</f>
         <v>0.18330885497034699</v>
       </c>
       <c r="R111" s="12">
-        <f t="shared" ref="R111" si="296">+R110/N110-1</f>
+        <f t="shared" ref="R111" si="307">+R110/N110-1</f>
         <v>0.16092875726148481</v>
       </c>
       <c r="S111" s="12">
-        <f t="shared" ref="S111:Y111" si="297">+S110/O110-1</f>
+        <f t="shared" ref="S111:Y111" si="308">+S110/O110-1</f>
         <v>4.8229063224098034E-2</v>
       </c>
       <c r="T111" s="12">
-        <f t="shared" si="297"/>
+        <f t="shared" si="308"/>
         <v>-1.7712092004020241E-2</v>
       </c>
       <c r="U111" s="12">
-        <f t="shared" si="297"/>
+        <f t="shared" si="308"/>
         <v>-9.8084808873666551E-2</v>
       </c>
       <c r="V111" s="12">
-        <f t="shared" si="297"/>
+        <f t="shared" si="308"/>
         <v>-8.7092664507513518E-2</v>
       </c>
       <c r="W111" s="12">
-        <f t="shared" si="297"/>
+        <f t="shared" si="308"/>
         <v>-1.7052452079451275E-3</v>
       </c>
       <c r="X111" s="12">
-        <f t="shared" si="297"/>
+        <f t="shared" si="308"/>
         <v>0.13128585326579212</v>
       </c>
       <c r="Y111" s="12">
-        <f t="shared" si="297"/>
+        <f t="shared" si="308"/>
         <v>0.22941852768003335</v>
       </c>
       <c r="Z111" s="12">
-        <f t="shared" ref="Z111:AE111" si="298">+Z110/V110-1</f>
+        <f t="shared" ref="Z111:AE111" si="309">+Z110/V110-1</f>
         <v>0.24541403951240026</v>
       </c>
       <c r="AA111" s="12">
-        <f t="shared" si="298"/>
+        <f t="shared" si="309"/>
         <v>0.14924240027836655</v>
       </c>
       <c r="AB111" s="12">
-        <f t="shared" si="298"/>
+        <f t="shared" si="309"/>
         <v>3.8342353028393505E-2</v>
       </c>
       <c r="AC111" s="12">
-        <f t="shared" si="298"/>
+        <f t="shared" si="309"/>
         <v>-1.7158807526637898E-2</v>
       </c>
       <c r="AD111" s="12">
-        <f t="shared" si="298"/>
+        <f t="shared" si="309"/>
         <v>-3.3211378272198333E-2</v>
       </c>
       <c r="AE111" s="12">
-        <f t="shared" si="298"/>
+        <f t="shared" si="309"/>
         <v>7.369739341058601E-2</v>
       </c>
       <c r="BX111" s="12">
@@ -19904,91 +20344,91 @@
         <v>464</v>
       </c>
       <c r="J112" s="4">
-        <f t="shared" ref="J112" si="299">SUM(G94:J94)</f>
+        <f t="shared" ref="J112" si="310">SUM(G94:J94)</f>
         <v>-15441</v>
       </c>
       <c r="K112" s="4">
-        <f t="shared" ref="K112" si="300">SUM(H94:K94)</f>
+        <f t="shared" ref="K112" si="311">SUM(H94:K94)</f>
         <v>-16963</v>
       </c>
       <c r="L112" s="4">
-        <f t="shared" ref="L112" si="301">SUM(I94:L94)</f>
+        <f t="shared" ref="L112" si="312">SUM(I94:L94)</f>
         <v>-17592</v>
       </c>
       <c r="M112" s="4">
-        <f t="shared" ref="M112" si="302">SUM(J94:M94)</f>
+        <f t="shared" ref="M112" si="313">SUM(J94:M94)</f>
         <v>-18914</v>
       </c>
       <c r="N112" s="4">
-        <f t="shared" ref="N112" si="303">SUM(K94:N94)</f>
+        <f t="shared" ref="N112" si="314">SUM(K94:N94)</f>
         <v>-20622</v>
       </c>
       <c r="O112" s="4">
-        <f t="shared" ref="O112:W112" si="304">SUM(L94:O94)</f>
+        <f t="shared" ref="O112:W112" si="315">SUM(L94:O94)</f>
         <v>-21525</v>
       </c>
       <c r="P112" s="4">
-        <f t="shared" si="304"/>
+        <f t="shared" si="315"/>
         <v>-23216</v>
       </c>
       <c r="Q112" s="4">
-        <f t="shared" si="304"/>
+        <f t="shared" si="315"/>
         <v>-23467</v>
       </c>
       <c r="R112" s="4">
-        <f t="shared" si="304"/>
+        <f t="shared" si="315"/>
         <v>-23886</v>
       </c>
       <c r="S112" s="4">
-        <f t="shared" si="304"/>
+        <f t="shared" si="315"/>
         <v>-24359</v>
       </c>
       <c r="T112" s="4">
-        <f t="shared" si="304"/>
+        <f t="shared" si="315"/>
         <v>-24768</v>
       </c>
       <c r="U112" s="4">
-        <f t="shared" si="304"/>
+        <f t="shared" si="315"/>
         <v>-26035</v>
       </c>
       <c r="V112" s="4">
-        <f t="shared" si="304"/>
+        <f t="shared" si="315"/>
         <v>-28107</v>
       </c>
       <c r="W112" s="4">
-        <f t="shared" si="304"/>
+        <f t="shared" si="315"/>
         <v>-31741</v>
       </c>
       <c r="X112" s="4">
-        <f t="shared" ref="X112:AE112" si="305">SUM(U94:X94)</f>
+        <f t="shared" ref="X112:AE112" si="316">SUM(U94:X94)</f>
         <v>-35202</v>
       </c>
       <c r="Y112" s="4">
-        <f t="shared" si="305"/>
+        <f t="shared" si="316"/>
         <v>-39547</v>
       </c>
       <c r="Z112" s="4">
-        <f t="shared" si="305"/>
+        <f t="shared" si="316"/>
         <v>-44477</v>
       </c>
       <c r="AA112" s="4">
-        <f t="shared" si="305"/>
+        <f t="shared" si="316"/>
         <v>-49483</v>
       </c>
       <c r="AB112" s="4">
-        <f t="shared" si="305"/>
+        <f t="shared" si="316"/>
         <v>-55552</v>
       </c>
       <c r="AC112" s="4">
-        <f t="shared" si="305"/>
+        <f t="shared" si="316"/>
         <v>-61345</v>
       </c>
       <c r="AD112" s="4">
-        <f t="shared" si="305"/>
+        <f t="shared" si="316"/>
         <v>-64551</v>
       </c>
       <c r="AE112" s="4">
-        <f t="shared" si="305"/>
+        <f t="shared" si="316"/>
         <v>-69022</v>
       </c>
       <c r="BW112" s="4">
@@ -20009,75 +20449,75 @@
         <v>463</v>
       </c>
       <c r="N113" s="12">
-        <f t="shared" ref="N113" si="306">+N112/J112-1</f>
+        <f t="shared" ref="N113" si="317">+N112/J112-1</f>
         <v>0.33553526326015159</v>
       </c>
       <c r="O113" s="12">
-        <f t="shared" ref="O113" si="307">+O112/K112-1</f>
+        <f t="shared" ref="O113" si="318">+O112/K112-1</f>
         <v>0.26893827742734189</v>
       </c>
       <c r="P113" s="12">
-        <f t="shared" ref="P113" si="308">+P112/L112-1</f>
+        <f t="shared" ref="P113" si="319">+P112/L112-1</f>
         <v>0.31969076853115053</v>
       </c>
       <c r="Q113" s="12">
-        <f t="shared" ref="Q113" si="309">+Q112/M112-1</f>
+        <f t="shared" ref="Q113" si="320">+Q112/M112-1</f>
         <v>0.24072115892989321</v>
       </c>
       <c r="R113" s="12">
-        <f t="shared" ref="R113" si="310">+R112/N112-1</f>
+        <f t="shared" ref="R113" si="321">+R112/N112-1</f>
         <v>0.15827756764620315</v>
       </c>
       <c r="S113" s="12">
-        <f t="shared" ref="S113:W113" si="311">+S112/O112-1</f>
+        <f t="shared" ref="S113:W113" si="322">+S112/O112-1</f>
         <v>0.13166085946573758</v>
       </c>
       <c r="T113" s="12">
-        <f t="shared" si="311"/>
+        <f t="shared" si="322"/>
         <v>6.6850447966919413E-2</v>
       </c>
       <c r="U113" s="12">
-        <f t="shared" si="311"/>
+        <f t="shared" si="322"/>
         <v>0.10943026377466225</v>
       </c>
       <c r="V113" s="12">
-        <f t="shared" si="311"/>
+        <f t="shared" si="322"/>
         <v>0.17671439336850048</v>
       </c>
       <c r="W113" s="12">
-        <f t="shared" si="311"/>
+        <f t="shared" si="322"/>
         <v>0.3030502073155712</v>
       </c>
       <c r="X113" s="12">
-        <f t="shared" ref="X113:AE113" si="312">+X112/T112-1</f>
+        <f t="shared" ref="X113:AE113" si="323">+X112/T112-1</f>
         <v>0.42126937984496116</v>
       </c>
       <c r="Y113" s="12">
-        <f t="shared" si="312"/>
+        <f t="shared" si="323"/>
         <v>0.51899366237756861</v>
       </c>
       <c r="Z113" s="12">
-        <f t="shared" si="312"/>
+        <f t="shared" si="323"/>
         <v>0.58241719144697046</v>
       </c>
       <c r="AA113" s="12">
-        <f t="shared" si="312"/>
+        <f t="shared" si="323"/>
         <v>0.55896159541287305</v>
       </c>
       <c r="AB113" s="12">
-        <f t="shared" si="312"/>
+        <f t="shared" si="323"/>
         <v>0.57809215385489465</v>
       </c>
       <c r="AC113" s="12">
-        <f t="shared" si="312"/>
+        <f t="shared" si="323"/>
         <v>0.55119225225680846</v>
       </c>
       <c r="AD113" s="12">
-        <f t="shared" si="312"/>
+        <f t="shared" si="323"/>
         <v>0.45133439755379179</v>
       </c>
       <c r="AE113" s="12">
-        <f t="shared" si="312"/>
+        <f t="shared" si="323"/>
         <v>0.39486288220196841</v>
       </c>
       <c r="BX113" s="12">
@@ -20292,95 +20732,95 @@
         <v>2</v>
       </c>
       <c r="AS119" s="4">
-        <f t="shared" ref="AS119:BO119" si="313">AS118*AS48</f>
+        <f t="shared" ref="AS119:BO119" si="324">AS118*AS48</f>
         <v>20734.741379310344</v>
       </c>
       <c r="AT119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>36544.838709677417</v>
       </c>
       <c r="AU119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>49327.24832214765</v>
       </c>
       <c r="AV119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>114885.89743906935</v>
       </c>
       <c r="AW119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>184709.73040305718</v>
       </c>
       <c r="AX119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>372704.58101536665</v>
       </c>
       <c r="AY119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>298261.112605042</v>
       </c>
       <c r="AZ119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>266298.08220699872</v>
       </c>
       <c r="BA119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>222567.08981033842</v>
       </c>
       <c r="BB119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>236906.16184222695</v>
       </c>
       <c r="BC119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>252642.2008830022</v>
       </c>
       <c r="BD119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>260731.99813293503</v>
       </c>
       <c r="BE119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>247113.52251981141</v>
       </c>
       <c r="BF119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>265170.46442666667</v>
       </c>
       <c r="BG119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>298326.78203723987</v>
       </c>
       <c r="BH119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>151214.58181818182</v>
       </c>
       <c r="BI119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>242693.07615855773</v>
       </c>
       <c r="BJ119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>213717.28455478634</v>
       </c>
       <c r="BK119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>198199.0335202195</v>
       </c>
       <c r="BL119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>206380.61592027853</v>
       </c>
       <c r="BM119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>290064.69972083991</v>
       </c>
       <c r="BN119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>377052.05051894463</v>
       </c>
       <c r="BO119" s="4">
-        <f t="shared" si="313"/>
+        <f t="shared" si="324"/>
         <v>436539.84856262838</v>
       </c>
     </row>
@@ -20389,95 +20829,95 @@
         <v>5</v>
       </c>
       <c r="AS120" s="4">
-        <f t="shared" ref="AS120:BO120" si="314">AS119-AS63</f>
+        <f t="shared" ref="AS120:BO120" si="325">AS119-AS63</f>
         <v>17120.741379310344</v>
       </c>
       <c r="AT120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>31794.838709677417</v>
       </c>
       <c r="AU120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>42387.24832214765</v>
       </c>
       <c r="AV120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>103573.89743906935</v>
       </c>
       <c r="AW120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>166079.73040305718</v>
       </c>
       <c r="AX120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>341096.58101536665</v>
       </c>
       <c r="AY120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>256737.112605042</v>
       </c>
       <c r="AZ120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>220557.08220699872</v>
       </c>
       <c r="BA120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>169724.08981033842</v>
       </c>
       <c r="BB120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>174166.16184222695</v>
       </c>
       <c r="BC120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>179840.2008830022</v>
       </c>
       <c r="BD120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>211976.99813293503</v>
       </c>
       <c r="BE120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>203720.52251981141</v>
       </c>
       <c r="BF120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>231642.46442666667</v>
       </c>
       <c r="BG120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>268076.78203723987</v>
       </c>
       <c r="BH120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>120580.58181818182</v>
       </c>
       <c r="BI120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>204090.07615855773</v>
       </c>
       <c r="BJ120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>162001.28455478634</v>
       </c>
       <c r="BK120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>137327.0335202195</v>
       </c>
       <c r="BL120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>134114.61592027853</v>
       </c>
       <c r="BM120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>212403.69972083991</v>
       </c>
       <c r="BN120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>377052.05051894463</v>
       </c>
       <c r="BO120" s="4">
-        <f t="shared" si="314"/>
+        <f t="shared" si="325"/>
         <v>436539.84856262838</v>
       </c>
     </row>
@@ -20486,95 +20926,95 @@
         <v>223</v>
       </c>
       <c r="AS121" s="24">
-        <f t="shared" ref="AS121:BO121" si="315">AS120/AS46</f>
+        <f t="shared" ref="AS121:BO121" si="326">AS120/AS46</f>
         <v>13.85173250753264</v>
       </c>
       <c r="AT121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>21.21069960618907</v>
       </c>
       <c r="AU121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>19.310819281160661</v>
       </c>
       <c r="AV121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>29.986652414322336</v>
       </c>
       <c r="AW121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>34.905365784585371</v>
       </c>
       <c r="AX121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>44.733977838080875</v>
       </c>
       <c r="AY121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>27.710427696172907</v>
       </c>
       <c r="AZ121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>27.989477437436385</v>
       </c>
       <c r="BA121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>21.427103877078451</v>
       </c>
       <c r="BB121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>17.311018968514755</v>
       </c>
       <c r="BC121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>21.950470021115855</v>
       </c>
       <c r="BD121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>17.298596224329607</v>
       </c>
       <c r="BE121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>16.16957873798011</v>
       </c>
       <c r="BF121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>16.469425128095747</v>
       </c>
       <c r="BG121" s="24">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>15.161856345073236</v>
       </c>
       <c r="BH121" s="25">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>8.0931996656273455</v>
       </c>
       <c r="BI121" s="25">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>10.844894848746359</v>
       </c>
       <c r="BJ121" s="25">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>6.9978956611138807</v>
       </c>
       <c r="BK121" s="25">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>5.9266770325069915</v>
       </c>
       <c r="BL121" s="25">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>6.1343189827689946</v>
       </c>
       <c r="BM121" s="25">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>9.5673032620530574</v>
       </c>
       <c r="BN121" s="25">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>16.98126691222053</v>
       </c>
       <c r="BO121" s="25">
-        <f t="shared" si="315"/>
+        <f t="shared" si="326"/>
         <v>24.376806374951329</v>
       </c>
     </row>
